--- a/latam_transit_boards.xlsx
+++ b/latam_transit_boards.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Agency Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$M$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,22 +106,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Appointed by Jefe de Gobierno Jorge Macri (January 2024)</t>
+          <t>Appointed by Jefe de Gobierno Jorge Macri (January 2024); confirmed as sitting Presidente on the official GCBA SBASE/SBASAU governance page as of August 2026, with no reported change since the January 2024 appointment.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/; https://www.linkedin.com/in/javierignacioibanez/</t>
+          <t>https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/; https://buenosaires.gob.ar/subte/noticias/subterraneos-de-buenos-aires-tiene-nuevo-presidente; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -643,14 +643,14 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Appointed by GCBA; previously served as director (2016-2018), vice president (2018-2023), president (2023-2024), returned to vice president (January 2024)</t>
+          <t>Appointed by GCBA; previously served as director (2016-2018), vice president (2018-2022), president (2022-2024), returned to vice president (January 2024). Confirmed as sitting Vicepresidente on the official GCBA SBASE/SBASAU governance page as of August 2026.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://enelsubte.com/noticias/mauro-alabuenas-es-el-nuevo-presidente-de-sbase/; https://www.enelsubte.com/noticias/el-presidente-de-sbase-mauro-alabuenas-en-un-dialogo-exclusivo-con-enelsubte/; https://buenosaires.gob.ar/subte/noticias/subterraneos-de-buenos-aires-tiene-nuevo-presidente</t>
+          <t>https://enelsubte.com/noticias/mauro-alabuenas-es-el-nuevo-presidente-de-sbase/; https://www.enelsubte.com/noticias/el-presidente-de-sbase-mauro-alabuenas-en-un-dialogo-exclusivo-con-enelsubte/; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Guillermo Seefeld</t>
+          <t>Mario Sebastián Sabugo</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -742,49 +742,49 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Appointed by GCBA; has served on SBASE board across multiple administrations (continuity director from pre-2016, reappointed January 2024)</t>
+          <t>Appointed by GCBA Asamblea; appears as a current Director on the official GCBA SBASE/SBASAU governance page as of August 2026. He did not appear in the March 2026 snapshot or in press coverage of the January 2024 board appointments, and his exact appointment date/method could not be independently verified in public news sources — flagged as a gap.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>PRO party figure and longtime transport official. Former Secretary of Traffic and Transportation of GCBA (under Mayor Jorge Telerman). Former Undersecretary of Land Transportation at the national level (during the Menem administration). Brother of actor Martín Seefeld. Has been the longest-serving member of the SBASE board, continuing across multiple city government administrations.</t>
+          <t>Architecture historian and academic. Doctor in Architecture (Doctor Arquitecto) and Profesor Titular Consulto at the Facultad de Arquitectura, Diseño y Urbanismo (FADU), Universidad de Buenos Aires, where he leads the History of Architecture chair (Cátedra Sabugo/Caride) and is a principal researcher at the Instituto de Arte Americano (IAA). Specialist in the history of Hispanic-Arab, Spanish, and Hispanic-American architecture. Previously served as Subsecretario de Planeamiento (Undersecretary of Planning) in the GCBA Ministerio de Planeamiento y Obras Públicas, approximately 2006-2008 (per Boletín Oficial CABA resignation/final-report notices).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Not publicly confirmed</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Transit Ops/Management</t>
+          <t>Doctor in Architecture (Doctor Arquitecto), Universidad de Buenos Aires (FADU-UBA).</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Seefeld held the top transit management position for Buenos Aires city (Secretary of Traffic and Transportation) and also served as national Undersecretary of Land Transportation. These roles involved direct oversight and management of transit systems, including the Subte. His decades-long career has been specifically focused on transit and transportation.</t>
+          <t>Sabugo's public-sector role (Subsecretario de Planeamiento) was general city/urban-environmental planning, not a transit-specific planning post — the city government's transit/mobility planning function sits in a separate Subsecretaría de Planificación de la Movilidad y la Seguridad Vial. His primary career is as an architecture-history academic. No evidence of direct experience managing transit systems, rail/bus operations, or transit capital projects was found, so this does not meet the bar for Transit Ops/Management under the 'general planners don't count unless transit-focused' rule.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://enelsubte.com/noticias/nuevo-directorio-en-sbase/; https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/; https://boletinoficial.buenosaires.gob.ar/normativaba/norma/830045</t>
+          <t>https://buenosaires.gob.ar/gcaba_historico/nosotros; https://www.iaa.fadu.uba.ar/?tag=dr-arq-mario-sabugo; https://boletinoficial.buenosaires.gob.ar/normativaba/norma/111578</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Appointed by GCBA (joined board circa 2020, reappointed January 2024)</t>
+          <t>Appointed by GCBA (joined board circa 2020, reappointed January 2024); confirmed as a sitting Director on the official GCBA SBASE/SBASAU governance page as of August 2026.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Former Director of Legal Affairs of the AFI (Agencia Federal de Inteligencia, Argentina's intelligence agency) during the Macri national administration. His appointment to the SBASE board was controversial — he appeared in a leaked video of a meeting where judicial cases against union leaders were allegedly being coordinated (the 'Gestapo' affair), prompting opposition legislators and subway unions to demand his removal. Despite the controversy, he was retained on the board.</t>
+          <t>Former Director of Legal Affairs of the AFI (Agencia Federal de Inteligencia, Argentina's intelligence agency) during the Macri national administration. His appointment to the SBASE board was controversial — he appeared in a leaked video of a meeting where judicial cases against union leaders were allegedly being coordinated (the 'Gestapo' affair), prompting opposition legislators and subway unions to demand his removal. Despite the controversy, he was retained on the board and remains a director as of the current snapshot.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Not publicly confirmed (legal background implied by AFI Legal Affairs role)</t>
+          <t>Not publicly confirmed (legal background implied by AFI Legal Affairs role).</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.enelsubte.com/noticias/polemica-por-la-aparicion-de-un-director-de-sbase-en-el-video-de-la-gestapo/; https://www.enelsubte.com/noticias/escandalo-de-espionaje-oposicion-y-sindicatos-piden-que-se-remueva-a-de-stefano-del-directorio-de-sbase/; https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/</t>
+          <t>https://www.enelsubte.com/noticias/polemica-por-la-aparicion-de-un-director-de-sbase-en-el-video-de-la-gestapo/; https://www.enelsubte.com/noticias/escandalo-de-espionaje-oposicion-y-sindicatos-piden-que-se-remueva-a-de-stefano-del-directorio-de-sbase/; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -844,14 +844,14 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Eduardo José Moreno</t>
+          <t>Guillermo Seefeld</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -876,32 +876,32 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Appointed by GCBA (January 2024)</t>
+          <t>Appointed by GCBA; has served on the SBASE/SBASAU board continuously since 2012, across multiple city administrations (reappointed through the January 2024 cycle). Confirmed as a sitting Director on the official GCBA SBASE/SBASAU governance page as of August 2026.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Extensive career in public transportation in Argentina. Former Executive Director of Transportes Integrados Metropolitanos. Has held various transport-related positions with the Province of Buenos Aires and national government over several decades. Career specifically focused on the transport sector.</t>
+          <t>CORRECTED FROM PRIOR SNAPSHOT — PLEASE READ NOTES. Described in the agency's own cited source (enelSubte, 'Quién es quién en el nuevo Directorio de SBASE') as a 'dirigente del PRO' (PRO party figure) and, as of that article, 'el único director que continúa de la gestión anterior' (the only director carried over from the prior administration), having joined SBASE in 2012 — making him the board's longest-tenured member. He is the brother of actor Martín Seefeld, owns a parador (beach resort/bar) in Pinamar, was a regular at paddle-tennis matches with Mauricio Macri, and was at one point mentioned as a possible mayoral candidate for Pinamar. He was also named, alongside other board members, in reporting on corruption allegations tied to Subte graffiti-cleaning contracts. No professional, technical, or prior transit-management background is documented for him in any source found. (The March 2026 snapshot incorrectly attributed to Seefeld the background of 'Secretario de Tránsito y Transporte del GCBA durante la gestión de Jorge Telerman' and 'Subsecretario de Transporte Terrestre de la Nación' — those roles belong to Gustavo Álvarez, a different SBASE director who served on an earlier iteration of the board (c. 2016) and is not currently on it.)</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Not publicly confirmed (CV available at argentina.gob.ar suggests professional transport background)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Transit Ops/Management</t>
+          <t>Not publicly confirmed.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Moreno has decades of direct experience in the Argentine transport sector, including as Executive Director of Transportes Integrados Metropolitanos (integrated metropolitan transport). This represents significant, direct transit management experience.</t>
+          <t>With the Telerman/Menem-era transport-official background now correctly reattributed away from him, no qualifying transit, finance, law, or other professional/technical credential is documented for Seefeld. He is best characterized as a long-tenured political appointee (PRO party figure) with a private business background (resort ownership) and no confirmed transit-sector expertise, so he defaults to the residual 'Other Management/Policy' bucket used for government appointees lacking any documented transit background — the same default applied to other thinly-documented appointees in this dataset. He has not held elected office, so 'Elected Official' does not apply.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/; https://www.argentina.gob.ar/sites/default/files/morenoeduardocv.pdf</t>
+          <t>https://enelsubte.com/noticias/nuevo-directorio-en-sbase/; https://buenosaires.gob.ar/gcaba_historico/nosotros; https://enelsubte.com/noticias/denuncian-un-escandalo-de-corrupcion-detras-de-contratos-de-limpieza-de-grafitis-en-el-subte/</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -911,14 +911,14 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -933,27 +933,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bernarda Balestra</t>
+          <t>Víctor José Colombano</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Directora</t>
+          <t>Director Titular</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Appointed by GCBA (on board since at least January 2024)</t>
+          <t>Designated Director Titular of SBASE via Acta de Asamblea General Ordinaria dated 15 January 2026, effective from 17 January 2026 — verified directly from the primary-source text of GCABA Oficina de Integridad Pública dictamen IF-2026-33966889-GCABA-OFIP (D.N.I. 18.069.067). Confirmed as a sitting Director on the official GCBA SBASE/SBASAU governance page as of August 2026.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Limited public information available. Listed as a director of SBASE in official appointment announcements. No detailed professional background was found in public sources.</t>
+          <t>Longtime Peronist political figure in Buenos Aires City politics (Comuna 7): described in party-aligned and political-news sources as 'congresal Metropolitano del PJ CABA y congresal nacional PJ' (a delegate to the Justicialist Party's internal metropolitan and national congresses — NOT an elected legislative seat) and a leader of NEP (Nuevo Espacio de Participación Peronista) within the former Frente de Todos coalition. Public administration career includes: Director General de Emergencia Habitacional of the City of Buenos Aires (through 2004, per Boletín Oficial CABA resignation notice matching the same D.N.I.), roles tied to the Mercado Central de Buenos Aires and the Instituto de Vivienda de la Ciudad, and head of the national 'El Estado en tu Barrio' program from October 2022. At the time of his SBASE designation, he simultaneously declared employment as an empleado (employee, seniority/title unspecified) at ADIF S.A. (Administración de Infraestructuras Ferroviarias, the national rail-infrastructure agency) and an ad-honorem post as Secretario Administrativo y de Relaciones Institucionales of ALAF (Asociación Latinoamericana de Ferrocarriles), a rail-industry trade association — both per his own conflict-of-interest declaration.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Not publicly confirmed</t>
+          <t>Not publicly confirmed in sources reviewed.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -963,89 +963,89 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Classified as Other Management/Policy by default given the absence of any public information linking her to transit operations, labor representation, community advocacy, or elected office. Government-appointed board members without transit backgrounds typically fall in this category.</t>
+          <t>Colombano's declared simultaneous roles at the time of appointment — an unspecified-seniority ADIF employee position and an ad-honorem trade-association administrative secretaryship — do not rise to 'significant direct experience managing transit systems, rail/bus operations, or transit capital projects' as required for Transit Ops/Management; the OFIP dictamen itself characterizes the ALAF role as administrative/institutional support with no fixed hours, not operational management. The bulk of his documented career is in party political organizing and public housing/market administration, unrelated to transit. He has not been confirmed to hold elected public office (no listing found on the Honorable Cámara de Diputados de la Nación roster); his 'congresal' role is an internal party position, not an elected legislative seat, so 'Elected Official' does not apply.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/</t>
+          <t>https://buenosaires.gob.ar/sites/default/files/2026-07/IF-2026-33966889-GCABA-OFIP.pdf; https://buenosaires.gob.ar/gcaba_historico/nosotros; https://www.parlamentario.com/tag/victor-jose-colombano/; https://www.ambito.com/perfil/1000700-victor-jose-colombano</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>STC Metro (Sistema de Transporte Colectivo)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Jorge Kogan</t>
+          <t>Héctor Ulises García Nieto</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Director (probable — appeared as signatory on Resolution 134/2025)</t>
+          <t>President of Consejo de Administración / Secretary of Mobility (SEMOVI)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Likely appointed by GCBA after resigning as Secretary of Transport of Buenos Aires city (September 2024)</t>
+          <t>Ex officio — appointed as Secretary of Mobility by Jefa de Gobierno Clara Brugada (October 5, 2024)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Engineer with deep transit and transport experience spanning decades. Former Secretary of Transport of Argentina (1999-2001, under President de la Rúa). Former Secretary of Transport of Buenos Aires city (2024, under Jorge Macri, resigned after 10 months). Director of the reform and concession of Railways and Subways of Buenos Aires (1990-1995). Former Vice President of Mercer Management Consulting (1995-1999). Has advised governments of Mexico, Poland, and South Africa on railway restructuring. Former board member of Aerolíneas Argentinas.</t>
+          <t>Economist and Morena party official. Former Director General of Transport and Executive Secretary at the extinct Secretaría de Transporte y Vialidad (SETRAVI). Former coordinator and general administrator of the Central de Abasto. Served as Morena party leader in CDMX.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Engineering degree, Universidad de Buenos Aires (UBA)</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Transit Ops/Management</t>
+          <t>Bachelor's in Economics from UNAM; master's and doctoral studies at UNAM Faculty of Political and Social Sciences</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Kogan has one of the most extensive transit-specific careers of any board member. He directed the concession of Buenos Aires railways and subways, served as national Secretary of Transport, and has international railway consulting experience. This is deep, direct transit operations and management expertise.</t>
+          <t>Although he heads the mobility secretariat and has transportation policy experience (SETRAVI, SEMOVI), his background is as an economist and political party leader, not as a transit operations manager. His SETRAVI role was in transport regulation/policy, not operations. He never held elected office, so the 'political operative' clause pointing toward Elected Official does not apply to him.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://boletinoficial.buenosaires.gob.ar/normativaba/norma/830045; https://www.ambito.com/portada-principal/jorge-kogan-deja-su-cargo-n3119250; https://www.iprofesional.com/politica/414509-renuncio-secretario-transporte-ciudad-buenos-aires-jorege-kogan-tras-10-meses-en-cargo; https://www.republicanosunidos.com.ar/pages/referentes/jorge-kogan.html</t>
+          <t>https://www.excelsior.com.mx/comunidad/hector-ulises-garcia-nieto-perfil-secretario-movilidad-cdmx/1669168; https://www.milenio.com/politica/hector-garcia-nieto-quien-es-nuevo-secretario-semovi-brugada; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1067,42 +1067,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ulises García Nieto</t>
+          <t>Adrián Rubalcava Suárez</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>President of Consejo de Administración / Secretary of Mobility (SEMOVI)</t>
+          <t>Director General of STC Metro (administrator/executive who reports to and implements resolutions of the Consejo de Administración — see notes: not confirmed as a formal Article 7 voting Council seat, but included here as the agency's chief executive)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Secretary of Mobility by Jefa de Gobierno Clara Brugada (October 2024)</t>
+          <t>Appointed by Jefa de Gobierno Clara Brugada (May 6, 2025), succeeding Guillermo Calderón Aguilera; confirmed still active in the role as of August 26, 2026 (signed a framework agreement with CIDESI)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Economist and Morena party official. Former Director General of Transport and Executive Secretary at the extinct Secretaría de Transporte y Vialidad (SETRAVI). Former coordinator and general administrator of the Central de Abasto. Served as Morena party leader in CDMX.</t>
+          <t>Career politician and lawyer. Mayor of Cuajimalpa de Morelos (2012-2015, 2018-2024, PVEM/coalition). Local legislator. Head of the Unit of Policies and Strategies for Peace Construction at the Federal Citizen Security Secretariat (2024-2025). Has been affiliated with PRD, PRI, Partido Verde (PVEM), and now aligned with Morena. No transit or transportation operations experience. Led the STC through the April 2026 SNTSTC work-stoppage negotiation; an April 2026 opinion piece speculated his tenure was ending, but he remained in post through at least August 2026.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's in Economics from UNAM; master's and doctoral studies at UNAM Faculty of Political and Social Sciences</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Law degree and studies in Public Administration from Universidad Anáhuac del Norte; Master's in Public Administration from INAP (National Institute of Public Administration); pursuing doctorate in Public Administration</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Although he heads the mobility secretariat and has transportation policy experience (SETRAVI, SEMOVI), his background is as an economist and political party leader, not as a transit operations manager. His SETRAVI role was in transport regulation/policy, not operations.</t>
+          <t>Applying the capacity test as primary: he sits on the Council in his capacity as appointed Director General, an executive post held by gubernatorial appointment, not by virtue of any elected office — so he is classified as Other Management/Policy. See classification_note for the conflicting reading.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.excelsior.com.mx/comunidad/hector-ulises-garcia-nieto-perfil-secretario-movilidad-cdmx/1669168; https://www.milenio.com/politica/hector-garcia-nieto-quien-es-nuevo-secretario-semovi-brugada; https://www.unotv.com/estados/ciudad-de-mexico/quien-es-hector-ulises-garcia-nieto-proximo-secretario-de-movilidad-de-la-cdmx/</t>
+          <t>https://www.nmas.com.mx/ciudad-de-mexico/quien-es-adrian-rubalcava-nuevo-director-metro-cdmx-sustituto-guillermo-calderon/; https://www.milenio.com/politica/grado-estudios-adrian-rubalcava-cv-nuevo-director-metro-cdmx; https://www.infobae.com/mexico/2026/04/14/termina-paro-en-el-metro-cdmx-adrian-rubalcava-anuncia-acuerdo-con-el-sindicato/; https://www.cronica.com.mx/nacional/2026/07/28/adrian-rubalcaba-destaca-avances-en-seguridad-mantenimiento-y-modernizacion-del-metro-de-la-ciudad-de-mexico/; https://www.razon.com.mx/ciudad/2026/08/26/stc-y-cidesi-reafirman-colaboracion-interinstitucional/; https://reportemh.com/rubalcava-tiene-los-dias-contados-en-el-metro/</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1134,42 +1134,42 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Adrián Rubalcava Suárez</t>
+          <t>César Cravioto Romero</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Director General of STC Metro</t>
+          <t>Board Member / Secretary of Government (Secretario de Gobierno)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Appointed by Jefa de Gobierno Clara Brugada (May 6, 2025)</t>
+          <t>Ex officio — appointed as Secretary of Government by Jefa de Gobierno Clara Brugada (October 5, 2024)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Career politician and lawyer. Mayor of Cuajimalpa de Morelos (2012-2015, 2018-2024). Local legislator. Head of the Unit of Policies and Strategies for Peace Construction at the Federal Citizen Security Secretariat (2024-2025). Has been affiliated with PRD, PRI, Partido Verde, and now aligned with Morena. No transit or transportation operations experience.</t>
+          <t>Career politician and communications professional. Former senator for Morena. Former Commissioner for Reconstruction under Claudia Sheinbaum (2018-2021). Former Director of Political Concertation under AMLO's CDMX government (2001-2005). Local legislator and coordinator of Morena faction in ALDF.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Law degree from Universidad Anáhuac del Norte; Master's in Public Administration from INAP (National Institute of Public Administration); pursuing doctorate in Public Administration</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+          <t>Bachelor's in Communications Science from Universidad Iberoamericana; diploma in Public Policy from UNAM</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Elected Official</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Former elected mayor of Cuajimalpa (multiple terms), former local legislator. His appointment to STC is a political appointment by the Jefa de Gobierno. He is a career elected official who moved into an appointed position.</t>
+          <t>Applying the capacity test as primary: he sits on the Council ex officio as Secretary of Government, an appointed cabinet post, not by virtue of currently holding elected office — so he is classified as Other Management/Policy. See classification_note for the conflicting reading.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://www.nmas.com.mx/ciudad-de-mexico/quien-es-adrian-rubalcava-nuevo-director-metro-cdmx-sustituto-guillermo-calderon/; https://www.milenio.com/politica/grado-estudios-adrian-rubalcava-cv-nuevo-director-metro-cdmx; https://www.elfinanciero.com.mx/cdmx/2025/05/06/metro-de-cdmx-estrena-director-adrian-rubalcava-reemplaza-a-guillermo-calderon/</t>
+          <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-cesar-cravioto-proximo-secretario-de-gobierno-de-la-cdmx/; https://www.milenio.com/politica/comunidad/cesar-cravioto-romero-quien-es-nuevo-secretario-gobierno-brugada; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1201,42 +1201,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>César Cravioto Romero</t>
+          <t>Juan Pablo de Botton Falcón</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Secretary of Government (Secretario de Gobierno)</t>
+          <t>Board Member / Secretary of Administration and Finance (Secretario de Administración y Finanzas) — this cabinet post absorbed the former Oficial Mayor seat referenced in Article 7 when that office was eliminated in CDMX in 2019 and merged into this secretariat</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Secretary of Government by Jefa de Gobierno Clara Brugada (October 2024)</t>
+          <t>Ex officio — appointed as Secretary of Administration and Finance by Jefa de Gobierno Clara Brugada (October 5, 2024)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Career politician and communications professional. Former senator for Morena. Former Commissioner for Reconstruction under Claudia Sheinbaum (2018-2021). Former Director of Political Concertation under AMLO's CDMX government (2001-2005). Local legislator and coordinator of Morena faction in ALDF.</t>
+          <t>Economist and senior financial official. Former Undersecretary of Expenditures at SHCP (federal finance ministry). Former Director General of Nacional Financiera (Nafin) and Bancomext (2018-2022). Former coordinator at SAT (tax administration). Private sector experience at Citibanamex in data science.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's in Communications Science from Universidad Iberoamericana; diploma in Public Policy from UNAM</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Elected Official</t>
+          <t>Bachelor's in Economics from CIDE; exchange studies at UCLA</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Former senator and local legislator who served in elected positions before being appointed to cabinet. His career is defined by elected office and political party leadership within Morena.</t>
+          <t>Finance and economics professional with extensive experience in federal and city public finance. No transit operations background — expertise is in fiscal policy, banking, and financial management. No elected-office history, so the contested capacity/clause tension does not arise for him.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-cesar-cravioto-proximo-secretario-de-gobierno-de-la-cdmx/; https://www.milenio.com/politica/comunidad/cesar-cravioto-romero-quien-es-nuevo-secretario-gobierno-brugada; https://politica.expansion.mx/cdmx/2024/08/19/quien-es-cesar-cravioto-romero</t>
+          <t>https://www.excelsior.com.mx/comunidad/juan-pablo-botton-finanzas-cdmx-quien-es-clara-brugada/1669170; https://www.milenio.com/politica/juan-pablo-de-botton-quien-es-secretario-administracion-finanzas; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1268,27 +1268,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Juan Pablo de Botton Falcón</t>
+          <t>Raúl Basulto Luviano</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Secretary of Administration and Finance (Secretario de Administración y Finanzas)</t>
+          <t>Board Member / Secretary of Works and Services (Secretario de Obras y Servicios)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Secretary of Administration and Finance by Jefa de Gobierno Clara Brugada (October 2024)</t>
+          <t>Ex officio — appointed as Secretary of Works and Services by Jefa de Gobierno Clara Brugada (October 5, 2024)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Economist and senior financial official. Former Undersecretary of Expenditures at SHCP (federal finance ministry). Former Director General of Nacional Financiera (Nafin) and Bancomext (2018-2022). Former coordinator at SAT (tax administration). Private sector experience at Citibanamex in data science.</t>
+          <t>Architect specializing in urban construction. Former Director General of Works and Urban Development in Iztapalapa (2018-2023), where he oversaw construction of 13 'Utopías' community centers. Former advisor in the ALDF. Started career in social housing programs (Programa de Mejoramiento Barrial) and civil protection.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Bachelor's in Economics from CIDE; exchange studies at UCLA</t>
+          <t>Architecture from UAM Xochimilco; postgraduate studies at the Institute for Advanced Architecture of Catalonia</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Finance and economics professional with extensive experience in federal and city public finance. No transit operations background — expertise is in fiscal policy, banking, and financial management.</t>
+          <t>Architect and public works administrator. His experience is in urban construction and community infrastructure, not transit operations. The Secretary of Works oversees infrastructure broadly, not transit-specific projects.</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://www.excelsior.com.mx/comunidad/juan-pablo-botton-finanzas-cdmx-quien-es-clara-brugada/1669170; https://www.milenio.com/politica/juan-pablo-de-botton-quien-es-secretario-administracion-finanzas; https://politica.expansion.mx/cdmx/2024/08/19/quien-es-juan-pablo-botton-responsable-finanzas-cdmx</t>
+          <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-raul-basulto-luviano-proximo-secretario-de-obras-y-servicios-sobse/; https://www.milenio.com/politica/quien-es-raul-basulto-nuevo-secretario-de-obras-y-servicios-de-cdmx; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1335,52 +1335,52 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Raúl Basulto Luviano</t>
+          <t>Martín López Delgado</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Secretary of Works and Services (Secretario de Obras y Servicios)</t>
+          <t>Board Member / Director General of Servicio de Transportes Eléctricos (STE)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Secretary of Works and Services by Jefa de Gobierno Clara Brugada (October 2024)</t>
+          <t>Ex officio — appointed as Director General of STE (in post since June 2021, previously confirmed continuing under the Brugada administration)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Architect specializing in urban construction. Former Director General of Works and Urban Development in Iztapalapa (2018-2023), where he oversaw construction of 13 'Utopías' community centers. Former advisor in the ALDF. Started career in social housing programs (Programa de Mejoramiento Barrial) and civil protection.</t>
+          <t>Transportation engineer with extensive career at STE. Held multiple positions within STE including Section Chief, Department Chief, Director of Transportation, and Director General. Under his leadership, STE grew from 120,000 daily users (2019) to over 380,000 daily users (2025), operating 462 modern trolleybus units across 13 routes.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Architecture from UAM Xochimilco; postgraduate studies at the Institute for Advanced Architecture of Catalonia</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Transportation Engineering from UPIICSA-IPN; Master's in Public Administration from Universidad del Valle de México</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Architect and public works administrator. His experience is in urban construction and community infrastructure, not transit operations. The Secretary of Works oversees infrastructure broadly, not transit-specific projects.</t>
+          <t>Career transit professional who rose through the ranks of STE (electric transport operator). Has direct operational experience managing trolleybus, Cablebús, and light rail systems. His entire career has been in transit operations.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-raul-basulto-luviano-proximo-secretario-de-obras-y-servicios-sobse/; https://www.milenio.com/politica/quien-es-raul-basulto-nuevo-secretario-de-obras-y-servicios-de-cdmx; https://www.unotv.com/estados/ciudad-de-mexico/raul-basulto-luviano-trayectoria-profesional-proximo-secretario-de-obras-cdmx/</t>
+          <t>https://www.infobae.com/mexico/2023/12/13/quien-es-el-director-del-servicio-de-transportes-electricos-que-opera-el-trolebus-y-el-tren-ligero-de-cdmx/; https://www.pasajero7.com/rescate-del-servicio-transportes-electricos-una-apuesta-la-movilidad-sostenible-en-la-cdmx/; https://www.facebook.com/RTPCDMX/posts/el-mtro-daniel-arcos-rodr%C3%ADguez-director-general-de-rtp-junto-con-mart%C3%ADn-l%C3%B3pez-de/1156668116500832/</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1402,52 +1402,52 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Martín López Delgado</t>
+          <t>Daniel Arcos Rodríguez</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Director General of Servicio de Transportes Eléctricos (STE)</t>
+          <t>Board Member / Director General of RTP (Red de Transporte de Pasajeros) — holds the parastatal seat Article 7 labels 'Sistema de Movilidad 1' (RTP's 2016-2019 legal name; see notes for the naming history)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Director General of STE (since June 2021, continuing under Brugada administration)</t>
+          <t>Ex officio — appointed as Director General of RTP by Jefa de Gobierno Clara Brugada's administration; active in the role throughout 2025-2026 (confirmed via RTP institutional social media and news coverage of Centrobús launches and fleet expansions through August 2026)</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Transportation engineer with extensive career at STE. Held multiple positions within STE including Section Chief, Department Chief, Director of Transportation, and Director General. Under his leadership, STE grew from 120,000 daily users (2019) to over 380,000 daily users (2025), operating 462 modern trolleybus units across 13 routes.</t>
+          <t>Holds a maestría (referred to as 'Mtro.' in RTP institutional communications). Leads RTP's bus network, including the May 2026 launch of the 'Ruta de las Mujeres Indígenas' Centrobús service and a planned 500-unit fleet expansion announced August 2026. Detailed prior career history and specific field of professional background could not be verified — no biographical profile, LinkedIn record, or transparency CV was retrievable (rtp.cdmx.gob.mx was unreachable).</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Transportation Engineering from UPIICSA-IPN; Master's in Public Administration from Universidad del Valle de México</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Transit Ops/Management</t>
+          <t>Holds a master's degree (field unspecified in available sources) — could not verify further</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Career transit professional who rose through the ranks of STE (electric transport operator). Has direct operational experience managing trolleybus, Cablebús, and light rail systems. His entire career has been in transit operations.</t>
+          <t>Classified pending fuller verification. He runs a large public bus operator (RTP), which if his career has been transit-focused would argue for Transit Ops/Management, but no confirmed prior transit-operations career history could be found — provisionally classified as Other Management/Policy per context.md's default treatment of unverified government officials, with Low confidence. This is a change from the March 2026 file, which incorrectly attributed this Article 7 seat to Metrobús's Rosario Castro Escorcia — see notes.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://www.ste.cdmx.gob.mx/secretaria/estructura/1; https://www.infobae.com/mexico/2023/12/13/quien-es-el-director-del-servicio-de-transportes-electricos-que-opera-el-trolebus-y-el-tren-ligero-de-cdmx/; https://www.pasajero7.com/rescate-del-servicio-transportes-electricos-una-apuesta-la-movilidad-sostenible-en-la-cdmx/</t>
+          <t>https://www.rtp.cdmx.gob.mx/dependencia/directorio; https://www.nmas.com.mx/ciudad-de-mexico/nuevo-transporte-cdmx-como-sera-centrobus-rtp-cual-sera-ruta-cuando-se-estrena-2026/; https://heraldodemexico.com.mx/nacional/2026/8/16/gobierno-de-cdmx-rtp-van-por-500-unidades-de-transporte-esta-es-la-fecha-en-la-que-operaran-870026.html; https://es.wikipedia.org/wiki/Sistema_de_Movilidad_1; https://es.wikipedia.org/wiki/Red_de_Transporte_de_Pasajeros_de_la_Ciudad_de_M%C3%A9xico</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1469,52 +1469,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Rosario Castro Escorcia</t>
+          <t>Fernando Espino Arévalo</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Director General of Metrobús (Sistema de Movilidad 1)</t>
+          <t>Union Participant / President of the National Executive Committee, SNTSTC — NOT a formal Article 7 Council seat; participation in Consejo de Administración sessions stems from a 2013-2015 negotiated administrative agreement, not a statutory board membership (see notes)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Ex officio — appointed as Director General of Metrobús under Brugada administration</t>
+          <t>Elected by union membership — has led the SNTSTC since 1978 (48 years as of 2026). Union participation in Consejo de Administración sessions and two seats on the Comité de Incidentes Relevantes were granted via an administrative agreement announced by the STC Director General under instruction from then-Jefe de Gobierno Miguel Ángel Mancera (2013-2015), not via an Estatuto Orgánico amendment.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Details of background not fully verified. Serves as Director General of the Metrobús BRT system in Mexico City.</t>
+          <t>Entered STC Metro as a worker in 1970. Elected union general secretary in 1978. Served as federal and/or local deputy on six occasions between 1991 and 2015 (federal deputy 1991-1994, 55th Legislature; local ALDF deputy 2000-2003; federal deputy 2009-2012, LXI Legislature, for PRI; additional terms per SIL/Segob legislator records). Affiliated with PRI and later Partido Verde. Also serves as president of the union's oversight committee since 1995. Confirmed still active as union leader and in Council-adjacent negotiations as of April 2026 (led SNTSTC side of the strike-ending agreement with DG Rubalcava). Known for decades-long control of the union and controversies regarding nepotism.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Not verified</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Electrical engineering degree from Instituto Politécnico Nacional (IPN); associated with the porrista movement at IPN's Escuela Superior de Ingeniería Mecánica y Eléctrica</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Labor Representative</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Classified as Other Management/Policy pending verification of transit operations background. Insufficient public information available to confirm transit-specific expertise.</t>
+          <t>Explicitly recognized as the union's representative in Consejo de Administración sessions, representing the interests of the 12,400+ STC Metro workers through the SNTSTC, notwithstanding that this is a negotiated participation right rather than an Article 7 statutory seat. His own history of elected office (1991-2015) does not override this — he sits in a designated labor capacity, not as a political appointee, so no classification conflict arises the way it does for Rubalcava/Cravioto.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrobus.cdmx.gob.mx/</t>
+          <t>https://www.infobae.com/mexico/2026/04/15/protestas-de-sindicato-del-stc-metro-exhiben-mas-de-cuatro-decadas-de-control-de-fernando-espino/; https://politica.expansion.mx/cdmx/2026/04/13/quien-es-fernando-espino-arevalo-lider-sindical-metro; https://www.infobae.com/mexico/2026/04/14/termina-paro-en-el-metro-cdmx-adrian-rubalcava-anuncia-acuerdo-con-el-sindicato/; https://www.metro.cdmx.gob.mx/comunicacion/nota/aprobada-la-participacion-del-sindicato-del-metro-en-el-consejo-de-administracion; https://en.wikipedia.org/wiki/Fernando_Espino_Ar%C3%A9valo</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1536,52 +1536,52 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fernando Espino Arévalo</t>
+          <t>Federal Representative (SICT)</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Union Representative / President of the National Executive Committee, SNTSTC</t>
+          <t>Board Member / Representative of the Secretaría de Infraestructura, Comunicaciones y Transportes (formerly SCT)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Elected by union membership — has led the SNTSTC since 1978 (over 47 years). Union participation in the Consejo de Administración was formally approved.</t>
+          <t>Designated by the federal Secretary of Infrastructure, Communications and Transportation</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Entered STC Metro as a worker in 1970. Elected union general secretary in 1978. Has served as federal deputy and local legislator (multiple terms, 1991-2012). Affiliated with PRI and later Partido Verde. Also serves as president of the union's oversight committee since 1995. Known for decades-long control of the union and controversies regarding nepotism.</t>
+          <t>Specific individual not identified. Per Article 7 of the Estatuto Orgánico, the federal SICT (formerly SCT) designates a representative or alternate to sit on the Council.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Electrical engineering (institution not verified)</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Labor Representative</t>
+          <t>Not identified</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Explicitly designated as the union representative on the Consejo de Administración, representing the interests of the 12,400+ STC Metro workers through the SNTSTC.</t>
+          <t>Federal government representative on the board. Individual not publicly identified despite targeted searching.</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/mexico/2023/09/18/quien-es-fernando-espino-arevalo-el-poderoso-lider-absoluto-del-sindicato-del-metro/; https://www.eluniversal.com.mx/metropoli/perfil-quien-es-fernando-espino-arevalo-lider-del-sindicato-del-metro-desde-hace-44-anos/; https://www.proceso.com.mx/reportajes/2020/3/18/el-poder-de-fernando-espino-lider-del-sindicato-del-metro-240032.html</t>
+          <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1603,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Federal Representative (SCT/SICT)</t>
+          <t>Federal Representative (Banobras)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Representative of the Secretaría de Infraestructura, Comunicaciones y Transportes</t>
+          <t>Board Member / Representative of Banco Nacional de Obras y Servicios Públicos</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Designated by the federal Secretary of Infrastructure, Communications and Transportation</t>
+          <t>Designated by Banobras (national development bank for public works)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Specific individual not identified. Per the Estatuto Orgánico, the federal SCT (now SICT) designates a representative or alternate to sit on the Board.</t>
+          <t>Specific individual not identified. Per Article 7 of the Estatuto Orgánico, Banobras designates a representative or alternate to sit on the Council.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Federal government representative on the board. Individual not publicly identified.</t>
+          <t>Development bank representative providing financial oversight. Individual not publicly identified despite checking Banobras' own transparency filings.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229</t>
+          <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229; https://transparencia.banobras.gob.mx/</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Federal Representative (Banobras)</t>
+          <t>State of Mexico Representative</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Representative of Banco Nacional de Obras y Servicios Públicos</t>
+          <t>Board Member / Representative designated by the State of Mexico Government</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Designated by Banobras (national development bank for public works)</t>
+          <t>Designated by the Governor of the State of Mexico</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Specific individual not identified. Per the Estatuto Orgánico, Banobras designates a representative or alternate to sit on the Board.</t>
+          <t>Specific individual not identified. Per Article 7 of the Estatuto Orgánico, the State of Mexico government designates a representative, reflecting that Metro lines extend into the neighboring state.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Development bank representative providing financial oversight. Individual not publicly identified.</t>
+          <t>State government representative. Included because Metro lines serve municipalities in the State of Mexico. Individual not publicly identified.</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1715,74 +1715,74 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>STC Metro (Sistema de Transporte Colectivo)</t>
+          <t>Metro de Medellín (Empresa de Transporte Masivo del Valle de Aburrá)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>State of Mexico Representative</t>
+          <t>Andrés Julián Rendón Cardona</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Board Member / Representative designated by the State of Mexico Government</t>
+          <t>Governor of Antioquia</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Designated by the Governor of the State of Mexico</t>
+          <t>Ex-officio as Governor of Antioquia</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Specific individual not identified. Per the Estatuto Orgánico, the State of Mexico government designates a representative, reflecting that Metro lines extend into the neighboring state.</t>
+          <t>Economist and politician. Previously served as Secretary of Government of Antioquia (2008–2012) and as Mayor of Rionegro (2016–2019). Elected Governor of Antioquia in 2023 with 944,239 votes, the most-voted governor in the department's history. Continues in office for the 2024–2027 term as of August 2026; recent coverage notes his political alignment with President-elect/President Abelardo de la Espriella around the 2026 national election.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Not identified</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Economist and specialist in Economic Regulation from EAFIT University; Master's in Economics and Public Administration from Universidad de los Andes and American University in Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>State government representative. Included because Metro lines serve municipalities in the State of Mexico. Individual not publicly identified.</t>
+          <t>Currently serving as the elected Governor of Antioquia (2024–2027 term, confirmed still in office as of August 2026). Sits on the board in his ex-officio capacity as governor.</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.eltiempo.com/politica/elecciones-colombia-2026/de-la-espriella-presidente-electo-se-reunio-con-el-gobernador-andres-julian-rendon-antioquia-resistio-voto-por-el-tigre-y-salvamos-a-colombia-3567538; https://es.wikipedia.org/wiki/Andr%C3%A9s_Juli%C3%A1n_Rend%C3%B3n</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>President of the Board (Mayor of the District of Medellín)</t>
+          <t>Mayor of the District of Medellín (ex officio board member)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Civil engineer and politician. Previously served as Mayor of Medellín 2016–2019. Was a member of the Medellín City Council 2004–2007. Ran for President of Colombia in 2022. Elected again as Mayor of Medellín for 2024–2027 term.</t>
+          <t>Civil engineer and politician. Previously served as Mayor of Medellín 2016–2019. Was a member of the Medellín City Council 2004–2007. Ran for President of Colombia in 2022. Serving as Mayor of Medellín for the 2024–2027 term as of August 2026.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1827,19 +1827,19 @@
           <t>Civil engineering degree from Universidad de Medellín; specialization in Senior Management from Universidad de los Andes</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Elected Official</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Currently serving as elected Mayor of Medellín. Sits on the board in his capacity as mayor, which is an ex-officio position tied to his elected office.</t>
+          <t>Currently serving as elected Mayor of Medellín (2024–2027 term, confirmed still in office). Sits on the board in his capacity as mayor, an ex-officio position tied to his elected office. Note: whether he currently holds the board's presidency specifically was not re-verified this cycle (see notes) — his ex-officio board membership itself is confirmed.</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/en/who-we-are/corporate-governance/board-of-directors; https://es.wikipedia.org/wiki/Federico_Guti%C3%A9rrez</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.medellin.gov.co/es/sala-de-prensa/noticias/posesio_federico_gutierrez_medellin/; https://es.wikipedia.org/wiki/Federico_Guti%C3%A9rrez</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1871,27 +1871,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ana Cathalina Ochoa Yepes</t>
+          <t>Luis Fernando Agudelo Henao</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Director of the Administrative Department of Planning, District of Medellín</t>
+          <t>Director of the Administrative Department of Planning, Department of Antioquia</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Ex-officio as Director of Planning of Medellín (appointed by Mayor)</t>
+          <t>Ex-officio as Director of Planning of Antioquia (appointed by Governor); formalized by an Antioquia governor's decree dated 2026-07-16, replacing an intermediate holder (Eugenio Prieto Soto), who had replaced Manuel Alejandro Naranjo Giraldo</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>22 years of experience in public sector, including 17 years at EPM (Empresas Públicas de Medellín). Served as Deputy Manager of Strategic Planning at the Urban Development Agency (EDU) and as Director of the Office of the Administrative Department of Planning. Also served as Head of Gas Planning at EPM.</t>
+          <t>Public accountant who previously served as director of Antioquia Cómo Vamos (a civil-society monitoring/accountability organization) and as an advisor in the Antioquia Governor's office before being named Director of the Departamento Administrativo de Planeación.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Civil engineer with specialization in Administration; Master's in Administrative Engineering</t>
+          <t>Public accountant (contador público) from Universidad de Medellín; Master's in Public Management from UNP San Juan Bosco (Argentina); Doctorate in Political Studies from Universidad Externado de Colombia</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Appointed government planning official, not an elected official. Background is in civil engineering, urban planning, and public administration — not transit operations specifically.</t>
+          <t>Appointed government planning official, not elected. Background is in public accounting, civic-accountability work, and public administration/governance policy — not transit operations. Consistent with the classification applied to the two prior holders of this same ex-officio seat.</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/ana-cathalina-ochoa-yepes; https://www.minuto30.com/ana-cathalina-ochoa-yepes-directora-departamento-administrativo-de-planeacion-medellin/1550354/</t>
+          <t>https://www.antioquia.gov.co/perfiles-gabinete/luis-fernando-agudelo-henao; https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1938,42 +1938,42 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Andrés Julián Rendón Cardona</t>
+          <t>Luz Ángela González Gómez</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Governor of Antioquia</t>
+          <t>Director of the Administrative Department of Planning, District of Medellín</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Ex-officio as Governor of Antioquia</t>
+          <t>Ex-officio as Director of Planning of Medellín (appointed by Mayor); replaced Ana Cathalina Ochoa Yepes at an unconfirmed date between March and August 2026</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Economist and politician. Previously served as Secretary of Government of Antioquia (2008–2012) and as Mayor of Rionegro (2016–2019). Elected Governor of Antioquia in 2023 with 944,239 votes, the most-voted governor in the department's history. Born in Rionegro, Antioquia, 1978.</t>
+          <t>Over 18 years of experience in administrative processes, strategic procurement management, and project structuring in the Medellín public sector. Previously Manager of the Empresa de Desarrollo Urbano (EDU, Medellín's urban development agency), Technical Director of Planning at the Instituto Tecnológico Metropolitano (ITM), Sub-secretary of Planning at the Municipal Secretariat of Supplies and Services, Administrative Director of the Institute for the Development of Antioquia (IDEA), and Head of Logistics at the Metropolitan Area of the Aburrá Valley. Independently confirmed acting in this role as of August 19, 2026, when she presented the city's POT (territorial land-use plan) review to the Medellín City Council.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Economist and specialist in Economic Regulation from EAFIT University; Master's in Economics and Public Administration from Universidad de los Andes and American University in Washington, D.C.</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Elected Official</t>
+          <t>Business Administrator (Administradora de Negocios) from EAFIT University; specialization in Quality Management from EAFIT University</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Currently serving as the elected Governor of Antioquia. Sits on the board in his ex-officio capacity as governor.</t>
+          <t>Appointed government planning official, not elected. Background is in public administration, procurement, and urban-development agency management — general administrative/management experience, not direct transit-operations management. Consistent with the classification applied to the prior holder of this same ex-officio seat.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/andres-julian-rendon-cardona; https://www.lasillavacia.com/quien-es-quien/andres-julian-rendon-cardona/; https://es.wikipedia.org/wiki/Andr%C3%A9s_Juli%C3%A1n_Rend%C3%B3n</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/luz-angela-gonzalez-gomez; https://ifmnoticias.com/politica/concejo-de-medellin-recibio-mas-de-17-mil-folios-y-abre-la-discusion-para-actualizar-el-pot-despues-de-12-anos/; https://www.medellin.gov.co/es/departamento-administrativo-de-planeacion/</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2005,27 +2005,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Naranjo Giraldo</t>
+          <t>Sebastián Hinestroza Arango</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Director of the Administrative Department of Planning, Department of Antioquia</t>
+          <t>Independent Member (Presidential Appointee)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Ex-officio as Director of Planning of Antioquia (appointed by Governor)</t>
+          <t>Appointed by the President of the Republic as independent member (originally Decree 1561, September 2023); still listed as a filled seat on the current official board roster as of August 2026</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Economist and professor. Served as Director General of the Monitoring and Control Center and Subsecretary of Strategic Planning and Evaluation at the Municipality of Rionegro. Undergraduate professor of micro and macroeconomic policy at EAFIT University. May have transitioned to Secretary of Economic Development for Antioquia in 2026.</t>
+          <t>Over 12 years of administrative, technical, and professional experience in supervision and construction of infrastructure, industrial, and building projects in public and private sectors. Over 6 years as an entrepreneur; legal representative of Megaproyecto Vial Siglo XXI SAS (road paving/infrastructure), HR Constructora SAS, and Castellón Ingeniería SAS. Held a major paving contract with the Secretary of Infrastructure of Medellín worth 65 billion pesos.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Economist; Master's in Government and Public Policies from EAFIT University</t>
+          <t>CORRECTED per this audit: official Metro bio states he holds a degree as Administrador de Negocios (Business Administrator), with a specialization in Gerencia de Proyectos (Project Management). No specific university is named on the source page. (Prior file entry incorrectly described this as an unconfirmed engineering/construction degree.)</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2035,22 +2035,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Appointed government planning official (not elected). Background in economics, public policy, and government planning — not transit operations.</t>
+          <t>Construction and infrastructure entrepreneur/business administrator focused on road/highway paving projects, not transit systems. His experience is in general civil infrastructure and paving contracting, not rail/bus operations management.</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://antioquia.gov.co/manuel-alejandro-naranjo-giraldo; https://www.elcolombiano.com/antioquia/plan-de-desarrollo-de-antioquia-tiene-cinco-lineas-estrategicas-AI23901881</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/sebastian-hinestroza-arango; https://www.elespectador.com/investigacion/los-megacontratos-del-empresario-elegido-por-el-gobierno-de-gustavo-petro-en-el-metro-de-medellin-noticias-hoy/; https://www.elcolombiano.com/medellin/nueva-junta-directiva-del-metro-de-medellin-tiene-dos-contratistas-de-la-alcaldia-JD22476087</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2072,42 +2072,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ferney Camacho</t>
+          <t>Liliana Yanneth Bohórquez Avendaño</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Representative of the Ministry of Transport (Director of Infrastructure)</t>
+          <t>Representative of the Ministry of Transport</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Appointed by the President of the Republic as Ministry of Transport representative</t>
+          <t>Appointed as Ministry of Transport representative; appears to have replaced Ferney Camacho, but the transition date and formal appointment instrument were not found/confirmed</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Civil engineer with over 20 years of experience. Director of Infrastructure at the Ministry of Transport. Previously served as advisor to the Vice-Ministry of Transport (2012–2015), Secretary of Infrastructure of Cali, Secretary of Infrastructure of Palmira. Worked at the National Institute of Concessions and Superintendence of Domestic Public Services. Expertise in real estate project management, PPP projects, transport planning, and sustainability.</t>
+          <t>Civil engineer with roughly 25 years of experience in transit, transport, road safety, infrastructure, and project management. Career includes roles at Bogotá's Secretaría Distrital de Movilidad (traffic-signal coordination, road-safety advisory, Director of Traffic Behavior and Road Safety), advisor to the Superintendencia de Transporte and the National Road Safety Agency (ANSV), and currently (acting/'encargada') Director of Infrastructure at the Ministry of Transport. Also serves on the board of Sistema Integrado de Transporte Masivo Metrolínea S.A. (Bucaramanga's BRT operator).</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Civil engineer from Universidad Nacional de Colombia; specializations in Finance and Land Transport from the Polytechnic University of Madrid</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Civil Engineer from Universidad Nacional de Colombia; Master's in Seguros y Gerencia de Riesgos (Insurance and Risk Management) from Universidad Pontificia de Salamanca (Spain); Specialist in Diseño de Vías Urbanas, Tránsito y Transporte (Urban Road Design, Transit and Transport) from Universidad Distrital (Bogotá; the source page's rendering of the full institutional name was ambiguous/possibly garbled — not independently confirmed); Specialist in Investigación de Accidentes de Tránsito (Traffic Accident Investigation) from the Escuela Nacional de Policía General Santander</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>While he works in the Ministry of Transport and has transport planning expertise, his career has focused on road infrastructure, highway concessions, and general transport infrastructure — not specifically on managing transit systems (rail/bus operations). Classified as Other Management/Policy per the rule that general civil engineers do not qualify for Transit Ops unless they specifically worked in transit.</t>
+          <t>Ministry of Transport career civil servant whose specialization and role center on traffic engineering, road-design standards, and road-safety administration rather than direct management of transit operations or capital projects — closer to a general (non-transit) transport-infrastructure engineer under context.md's rule.</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ferney-camacho-90aa0119/; https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/ferney-camacho; https://www.cali.gov.co/publicaciones/145526/ferney-camacho-el-vallecaucano-que-asume-como-secretario-de-infraestructura-de-cali/</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/liliana-yanneth-bohorquez-avendano; https://www.linkedin.com/in/liliana-yanneth-boh%C3%B3rquez-avenda%C3%B1o-28305163/; https://www.utadeo.edu.co/es/comunidad/gestion-del-transporte/65/liliana-yanneth-bohorquez-avendano</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2144,17 +2144,17 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Representative of the Ministry of Finance (Subdirector of Domestic Financing)</t>
+          <t>Representative of the Ministry of Finance</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Appointed by the President of the Republic as Ministry of Finance representative</t>
+          <t>Appointed by the President of the Republic as Ministry of Finance representative (originally under the prior administration); still listed as a filled seat on the current official board roster as of August 2026</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Finance professional at the Ministry of Finance and Public Credit. Currently serves as Subdirector of Domestic Financing of the Nation (Subdirección de Financiamiento Interno de la Nación). Born in Bogotá.</t>
+          <t>Finance professional at the Ministry of Finance and Public Credit. Listed as Ministry of Finance representative on Metro's current board roster. Born in Bogotá.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -2174,59 +2174,59 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/en/who-we-are/corporate-government/board-of-directors/luis-alexander-lopez-ruiz; https://www.funcionpublica.gov.co/web/sigep/hdv/-/directorio/S76010-0004-4/view</t>
+          <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.funcionpublica.gov.co/web/sigep/hdv/-/directorio/S76010-0004-4/view</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Metro de Medellín (Empresa de Transporte Masivo del Valle de Aburrá)</t>
+          <t>Metro de Santiago (Metro S.A.)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Juan Carlos Tafur Hernández</t>
+          <t>Patricio Rey Sommer</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Independent Member (Presidential Appointee)</t>
+          <t>President (Presidente del Directorio)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Appointed by the President of the Republic as independent member (Decree 1561, September 2023)</t>
+          <t>Selected by the incoming government of President José Antonio Kast and ratified at the Ordinary Shareholders' Meeting on April 27, 2026, replacing Guillermo Muñoz Senda; confirmed in Metro S.A.'s CMF corporate filing (RUT 61.219.000) with an appointment date of 27/04/2026.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Economist with experience as economic, financial, administrative, and urban-regional affairs advisor. Worked at the International Labour Organization (ILO), Convenio Andrés Bello, Universidad Santo Tomás, Ministry of National Defense, Colombian Liberal Party, and Universidad del Rosario. Co-founder and president of Mela's Craft Beer.</t>
+          <t>Career split between the private and public sectors. In the private sector, held roles at Procter &amp; Gamble and Budnik, and managed the national network of Chile's Chamber of Construction (Cámara Chilena de la Construcción). Since 2019 has served as General Manager of Desarrollo País S.A., leading infrastructure and connectivity initiatives such as the Humboldt fiber-optic cable project and urban-regeneration agreements. In government, served as Regional Secretary (Seremi) of the Ministry of Social Development in the O'Higgins Region (c. 2010–2011) and subsequently as Intendente (regional governor, an appointed — not elected — position) of the O'Higgins Region, both under President Sebastián Piñera's first administration.</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Economist from Universidad de Los Andes; specialization and Master's in Planning and Administration of Regional Development from Universidad de los Andes / Universidad Santo Tomás</t>
+          <t>Computer Science Engineer; Master's in Engineering, Pontificia Universidad Católica de Chile.</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Economist and regional development specialist with no transit-specific experience. His background spans academia, international organizations, and entrepreneurship — not transit operations.</t>
+          <t>Career is in general business management (P&amp;G, Budnik, construction-industry trade association) and appointed regional-government administration (Seremi, Intendente), plus leadership of a diversified infrastructure/connectivity company. His infrastructure work (fiber-optic cable, urban regeneration) is not transit-specific, and his government posts were non-elected administrative appointments rather than transit operations roles, so he does not meet the bar for Transit Ops/Management. The Intendente role, though a top regional government post, is an appointed (not elected) position under Chilean law, so Elected Official does not apply either.</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/en/who-we-are/corporate-government/board-of-directors/juan-carlos-tafur-hernandez; https://www.elcolombiano.com/medellin/presidencia-nombra-representantes-en-la-junta-directiva-del-metro-de-medellin-HD22472140</t>
+          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.df.cl/empresas/juntas-de-accionistas/con-patricio-rey-de-presidente-metro-de-santiago-renueva-su-directorio; https://www.emol.com/noticias/Nacional/2026/04/28/1198526/nuevo-directorio-metro-de-santiago.html; https://www.theclinic.cl/2026/04/28/metro-oficializa-a-su-nuevo-directorio-kast-se-inclina-por-el-exintendente-patricio-rey-como-presidente-y-nicole-keller-vuelve-a-la-vicepresidencia/; https://www.ex-ante.cl/patricio-rey-quien-es-el-nuevo-presidente-de-metro-nombrado-por-el-gobierno-y-sus-desafios-en-el-cargo/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2251,49 +2251,49 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Metro de Medellín (Empresa de Transporte Masivo del Valle de Aburrá)</t>
+          <t>Metro de Santiago (Metro S.A.)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sebastián Hinestroza Arango</t>
+          <t>Nicole Keller Flaten</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Independent Member (Presidential Appointee)</t>
+          <t>Vice President (Vicepresidenta del Directorio)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Appointed by the President of the Republic as independent member (Decree 1561, September 2023)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026, replacing Marcela Munizaga Muñoz as vice president; confirmed via Metro S.A.'s CMF filing.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Over 12 years of administrative, technical, and professional experience in supervision and construction of infrastructure, industrial, and building projects in public and private sectors. Entrepreneur and legal representative of Megaproyecto Vial Siglo XXI SAS (road paving/infrastructure), HR Constructora SAS, and Castellón Ingeniería SAS. Held a major paving contract with the Secretary of Infrastructure of Medellín worth 65 billion pesos.</t>
+          <t>Journalist by training. Began her career as an economics/business journalist at El Mercurio, then worked in account management at communications firm EK. In government, served as chief of staff (jefa de gabinete) in the Ministry of Public Works subsecretariat (2010) and as chief of staff to Public Works Minister Loreto Silva (2012), both under Piñera's first administration. Previously served on Metro's board as Vice President from 2018–2022 (Piñera's second administration), where she chaired the Sustainability Committee and also directed the Metro Pago subsidiary. Currently managing partner at strategic communications firm EK; also a board counselor at the Chilean-American Chamber of Commerce (AmCham Chile) and a director at MetLife Chile.</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Engineering/construction background (specific degree not confirmed)</t>
+          <t>Journalism degree, Pontificia Universidad Católica de Chile; Marketing Management diploma, Universidad de Chile; communications-strategy studies, Columbia University.</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Construction and infrastructure entrepreneur focused on road/highway projects, not transit systems. His experience is in general civil infrastructure and paving, not rail/bus operations.</t>
+          <t>Core professional background is journalism/strategic communications, plus ministerial chief-of-staff roles — not direct experience managing transit operations or capital projects. Her 2018–2022 tenure as Metro Vice President is board governance experience rather than operational transit management, and her committee leadership there (Sustainability) was a board oversight function, not a line role running transit service. Classified as Other Management/Policy consistent with the finance/law/comms/policy 'complementary skills' bucket.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/en/who-we-are/corporate-government/board-of-directors/sebastian-hinestroza-arango; https://www.elespectador.com/investigacion/los-megacontratos-del-empresario-elegido-por-el-gobierno-de-gustavo-petro-en-el-metro-de-medellin-noticias-hoy/; https://www.elcolombiano.com/medellin/nueva-junta-directiva-del-metro-de-medellin-tiene-dos-contratistas-de-la-alcaldia-JD22476087</t>
+          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.df.cl/empresas/juntas-de-accionistas/con-patricio-rey-de-presidente-metro-de-santiago-renueva-su-directorio; https://www.emol.com/noticias/Nacional/2026/04/28/1198526/nuevo-directorio-metro-de-santiago.html; https://www.theclinic.cl/2026/04/28/metro-oficializa-a-su-nuevo-directorio-kast-se-inclina-por-el-exintendente-patricio-rey-como-presidente-y-nicole-keller-vuelve-a-la-vicepresidencia/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2318,64 +2318,64 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Metro de Medellín (Empresa de Transporte Masivo del Valle de Aburrá)</t>
+          <t>Metro de Santiago (Metro S.A.)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Mary Luz Escobar Rivera</t>
+          <t>Patricio Pérez Gómez</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Independent Member (Presidential Appointee)</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Appointed by the President of the Republic as independent member (Decree 1561, September 2023)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026; confirmed via Metro S.A.'s CMF filing (listed as 'Patricio Perez Gomez').</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Over 18 years of experience in entrepreneurship, innovation, competitiveness, and regional development. Former advisor and Director of Entrepreneurship and Innovation at iNNpulsa Colombia, Colciencias, and the Presidency of the Republic. Founder of Propulsor Latinoamérica, an entrepreneurship and innovation consulting firm.</t>
+          <t>Extensive transit and rail management career. Served as General Manager (Gerente General) of Empresa de Ferrocarriles del Estado (EFE), Chile's state railway, and directed its three passenger-service subsidiaries. Also served as Director of the Metropolitan Public Transport Directorate (Dirección de Transporte Público Metropolitano, DTPM) and as chief of staff at the Ministry of Transport. Additional executive experience includes Strategy and Innovation Manager at telecom company Entel, and senior consulting roles at Everis (NTT Data) and Steer Davies Gleave, an international transport-planning consultancy.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Not confirmed from available sources</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Civil Industrial Engineer and Master's in Engineering, Pontificia Universidad Católica de Chile; MBA, Universidad Adolfo Ibáñez; pursuing International Certification as a Business Director, Institute of Directors (IoD), London.</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Innovation and entrepreneurship policy expert with government experience at national agencies (iNNpulsa, Colciencias, Presidency). No transit operations background — her expertise is in economic development and innovation policy.</t>
+          <t>Directly meets the highest bar in this category: he ran EFE (the national state railway company) as General Manager, led the Santiago-region transit regulatory/operating body (DTPM) as Director, and consulted at Steer Davies Gleave, a specialist transport-planning firm. This is career-defining, direct transit operations and management experience, not incidental engineering credentials.</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrodemedellin.gov.co/en/who-we-are/corporate-government/board-of-directors/mary-luz-escobar-rivera; https://www.elcolombiano.com/medellin/presidencia-nombra-representantes-en-la-junta-directiva-del-metro-de-medellin-HD22472140; https://propulsor.com.co/author/mary-luz-escobar-rivera/</t>
+          <t>https://dikqcneh0bsn5.cloudfront.net/alumni/patricio-enrique-perez-gomez/; https://www.ing.uc.cl/transporte-y-logistica/team/patricio-enrique-perez-gomez/; https://www.latercera.com/pulso/noticia/empresa-de-ferrocarriles-del-estado-elige-nuevo-directorio-presidido-por-jorge-claude/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2407,52 +2407,52 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Guillermo Tadao Muñoz Senda</t>
+          <t>Rodrigo Troncoso Olchevskaia</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>President (Presidente del Directorio)</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (April 25, 2022)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026; confirmed via Metro S.A.'s CMF filing. Announced the same week as fellow Universidad del Desarrollo (UDD) academic Pablo Allard's appointment to the EFE board.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Chilean civil engineer specializing in transportation. Held various positions at the Metropolitan Transportation Planning Secretariat (Sectra) from 1997 to 2006. Served as infrastructure management manager at Empresa de los Ferrocarriles del Estado (EFE) and director of its subsidiaries until 2008. Executive Director of the Metropolitan Public Transportation Directorate (DTPM/Transantiago) from 2014. Advisor to the World Bank evaluating public transportation systems in Latin American cities.</t>
+          <t>Academic and researcher, Centro de Políticas Públicas, Facultad de Gobierno, Universidad del Desarrollo (UDD), where he also directs the Master's in Public Policy program. Research and public commentary focus heavily on transportation economics and public transit: peer-reviewed work on cost, production and efficiency in Santiago's local bus industry, traffic assignment/microeconomic modeling of urban transport, ride-hailing demand economics, and the effects of environmental restrictions on transport; frequent media commentator (e.g., TVN) on public-transit fare increases. Co-authors extensively with transport economist Louis de Grange.</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer, Universidad de Chile (thesis on optimal operation of public transport routes in Santiago, 1998)</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+          <t>Ingeniero Comercial (Commercial Engineer) and PhD in Economics, Pontificia Universidad Católica de Chile.</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Extensive direct experience managing transit systems: led DTPM/Transantiago (Santiago's integrated public transit system), held management roles at EFE (state railway company), worked at Sectra (transport planning), and consulted for the World Bank on public transit operations in Latin America. Career is entirely in transit planning and operations.</t>
+          <t>His entire academic specialization is public-transit economics — bus-industry cost and efficiency studies, transit fare policy, and urban transport modeling — which is functionally equivalent to the 'transit engineering professor' carve-out in the classification rules, even though his formal training is in economics rather than engineering.</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://es.wikipedia.org/wiki/Guillermo_Mu%C3%B1oz_Senda; https://www.linkedin.com/in/guillermo-mu%C3%B1oz-03194865/; https://cooperativa.cl/noticias/pais/transportes/metro/guillermo-munoz-ex-director-de-transantiago-es-el-nuevo-presidente-de/2022-04-27/020546.html</t>
+          <t>https://investigadores.udd.cl/entities/person/rtroncoso2; https://gobierno.udd.cl/noticias/2024/11/tvn-rodrigo-troncoso-comenta-el-alzas-en-el-precio-del-transporte/; https://www.udd.cl/noticias/2026/05/07/academicos-de-la-udd-asumen-en-directorios-de-efe-y-metro-de-santiago/; https://www.zoominfo.com/p/Rodrigo-vladislav-Troncoso-olchevskaia/11519311346; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2474,52 +2474,52 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Marcela Adriana Munizaga Muñoz</t>
+          <t>María Cecilia Guzmán Ossa</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Vice President (Vicepresidenta del Directorio)</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (April 25, 2022)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026; confirmed via Metro S.A.'s CMF filing.</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Full Professor and Vice Dean of the Faculty of Physical and Mathematical Sciences at Universidad de Chile. Leading researcher in transportation demand modeling and public transit data analytics. Developed the Adatrap software, a key tool for public transport management in Santiago. Principal researcher at the Complex Engineering Systems Institute (ISCI). Elected member of the Academy of Engineering of Chile.</t>
+          <t>Historian and cultural-management executive. Founding partner and executive director of G-V, a cultural-management consultancy in Santiago. Previously served as director of AdCultura (Asociación de Administradores Culturales de Chile), 2003–2007. Reported to currently direct Santiago's Teatro Municipal / municipal cultural administration. On Metro's board, sits on the Innovation and Sustainability committees.</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Civil Engineer, Universidad de Chile; PhD in Engineering Sciences, Pontificia Universidad Católica de Chile</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Transit Ops/Management</t>
+          <t>Degree in History, Pontificia Universidad Católica de Chile; Post-Title in Cultural Management, Pontificia Universidad Católica de Chile; Executive Strategic Leadership Program (PADE, 2017) and Senior MBA (2018), ESE Business School, Universidad de los Andes.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Transit engineering professor with deep specialization in public transportation systems. Her entire research career focuses on transit demand modeling and public transport data analytics. She developed Adatrap, a transit management tool used operationally in Santiago. Per classification rules, transit engineering professors count as Transit Ops/Management.</t>
+          <t>Career is entirely in cultural-sector management and organizational leadership (theater/cultural administration, a cultural-management consultancy), with an executive-education (MBA-equivalent) credential. No transit, engineering, or transportation-planning background; fits the general-management 'complementary skills' bucket rather than any of the other four categories.</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://ingenieria.uchile.cl/sobre-la-fcfm/organizacion/personas/equipo-directivo/marcela-munizaga-munoz; https://ingcivil.uchile.cl/noticias/221854/marcela-munizaga-miembro-de-numero-academia-de-ingenieria-de-chile</t>
+          <t>https://www.g-v.cl/equipo/; https://www.ese.cl/alumni/Maria-Cecilia-Guzman-Ossa/2018-06-29/172900.html; https://cl.linkedin.com/in/cecilia-guzman-ossa-6a530a140; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2541,27 +2541,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Susana Bernardita González Leiva</t>
+          <t>Cristina Torres Delgado</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Director (Directora)</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (initially April 25, 2022; reconfirmed April 29, 2024)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026; confirmed via Metro S.A.'s CMF filing.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Over 30 years of career at DIPRES (Chile's Budget Directorate, Ministry of Finance). Started as budget analyst in 1993, rose to lead the Budget Development Unit, then headed the Defense and Justice Sector (2004-2019), and the Social Development sector until becoming Subdirector of DIPRES in March 2022. Extensive experience in public finance, budget management, and implementation of public policies.</t>
+          <t>Lawyer and public-finance official. Career includes: legal advisor at the Budget Directorate (DIPRES) during Piñera's first administration (2012–2014); legislative program coordinator at the Instituto Libertad y Desarrollo think tank, focused on regulated markets (2014–2018); chief of staff at the Ministry of Energy (2018–2019); legal advisor and subdirector at DIPRES (2019–2021); and Director of the Budget Office (DIPRES) from April 2021 to March 2022 under Piñera's second administration — the third woman to hold that post. As of 2025–2026, directs the Centro de Políticas Públicas at the Facultad de Economía y Negocios of Universidad San Sebastián and sits on the board of Universidad Mayor.</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Commercial Engineer (Ingeniera Comercial) with specialization in Economics, Universidad de Chile; Master in Management and Public Policies, Universidad Adolfo Ibáñez</t>
+          <t>Lawyer (Abogada), Universidad Mayor; diploma in economic regulation, Universidad Adolfo Ibáñez; postgraduate studies in organizational design, public-sector labor management, administrative law, and public contracting.</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Finance and public budget management professional. Entire 30+ year career was in the national Budget Directorate (DIPRES), focused on government fiscal management and public policy implementation. No transit-specific experience.</t>
+          <t>Entire career is in law, public budget/finance administration (DIPRES), regulatory policy, and academic public-policy leadership — no transit-specific experience. Squarely fits the 'lawyers, finance executives, public policy experts' description of Other Management/Policy.</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46; https://www.dipres.gob.cl/598/w3-article-115570.html</t>
+          <t>https://es.wikipedia.org/wiki/Cristina_Torres_Delgado; https://www.linkedin.com/in/cristina-torres-delgado-4430aa54/; https://www.eldinamo.cl/politica/2026/03/27/cristina-torres-delgado-la-administracion-saliente-se-impuso-compromisos-que-sabia-que-no-iba-a-cumplir/; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Nicolás Darío Valenzuela Levi</t>
+          <t>Jorge Hermann Anguita</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (April 25, 2022)</t>
+          <t>Selected by the Kast government and ratified at the Ordinary Shareholders' Meeting on April 27, 2026; confirmed via Metro S.A.'s CMF filing.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Academic at the Architecture Department of Universidad Técnica Federico Santa María. Postdoctoral researcher at the Center for Sustainable Urban Development (CEDEUS). Former Director of the Communal Planning Secretariat (SECPLA) of the Municipality of Providencia (2012-2015). Research focuses on urban inequality, infrastructure networks, and territorial economics. Participated in President Boric's programmatic team on infrastructure policy. Affiliated with Revolución Democrática party.</t>
+          <t>Economist. Head of the Studies Division (Jefe de División de Estudios) at the Ministry of Economy under Piñera's first administration (March 2010–August 2013), and later Head of the Studies Division at the Ministry of Labor (from April 2019). Director of his own consultancy, Hermann Consultores, since October 2013. Professor of Macroeconomics and Free Competition at the Facultad de Economía y Negocios, Universidad de Chile, since March 2005.</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Architect, Pontificia Universidad Católica de Chile; MPhil in Development Studies, University of Cambridge; PhD in Urban/Territorial Economics, University of Cambridge</t>
+          <t>Ingeniero Comercial (Commercial Engineer) and Master's in Economics, Universidad de Chile.</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Urban planning academic and architect. While he has researched metro systems comparatively (Santiago and Medellín), his career is in urban planning, territorial economics, and municipal government — not direct transit operations or management. His municipal planning role and academic work are in general urban policy, not transit-specific management.</t>
+          <t>Career is in macroeconomic policy analysis, government studies-division leadership (Economy, Labor ministries), academic economics, and private consulting — general economic/policy expertise with no transit-specific experience, matching the finance/economics wing of Other Management/Policy.</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://arquitectura.usm.cl/dr-nicolas-valenzuela-asume-como-miembro-del-directorio-de-metro-santiago/; https://www.latercera.com/la-tercera-pm/noticia/quien-es-nicolas-valenzuela-rd-el-director-de-metro-que-tensiona-la-aprobacion-del-presupuesto-2023/W6O2JV4MTRADPB5BKYTXIVMNJA/; https://valenzuelalevi.com</t>
+          <t>https://alumni.fen.uchile.cl/noticia/egresado-jorge-hermann-se-integra-como-nuevo-jefe-de-la-division-estudios-del-ministerio-del-trabajo; https://hermannconsultores.cl/; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2653,49 +2653,49 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Metro de Santiago (Metro S.A.)</t>
+          <t>Metrô de São Paulo (Companhia do Metropolitano de São Paulo)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tadashi Alberto Takaoka Caqueo</t>
+          <t>Milton Frasson</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Presidente do Conselho de Administração (Board Chair)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (April 25, 2022)</t>
+          <t>Elected by the General Assembly; continues as Chair, appearing unchanged on the current governance portal listing after the April 2026 board changes</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Innovation and entrepreneurship specialist. Former Manager of Venture Entrepreneurship at CORFO (Chile's economic development agency). Experience spanning consulting, general management, entrepreneurship, university teaching, and business acceleration. Board member of Fundación Generación Empresarial and Universidad Arturo Prat (UNAP). Strategic focus on bringing innovation to public transportation services at Metro.</t>
+          <t>Business administrator with career in finance and administration at São Paulo state transport companies. Served as Administrative and Financial Director at CPOS (Feb 2008–Jan 2011) and CPTM—São Paulo's commuter rail company (Jan 2011–Jan 2019). Remains at CPTM as Executive Advisor (Assessor Executivo).</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Industrial Civil Engineer (Ingeniero Civil Industrial); Master in Operations Management, Universidad de Chile</t>
+          <t>Business administration degree; postgraduate degree in Financial Administration</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Innovation and entrepreneurship management professional. Career centered on business innovation at CORFO and consulting, not on transit operations. While he brings a strategic innovation lens to Metro's board, his background is in general management and entrepreneurship rather than transit-specific experience.</t>
+          <t>Frasson has spent his career at transit-adjacent organizations (CPTM, CPOS), but his roles were administrative and financial rather than operational. He did not manage transit operations, engineering, or capital projects directly; his expertise is finance and administration applied to transport companies.</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.linkedin.com/in/tadashitakaoka/; https://economiayadministracion.uc.cl/assets/uploads/2024/07/CV-Tadashi.pdf; https://statealumni.cl/en/tadashi-takaoka/</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2720,49 +2720,49 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Metro de Santiago (Metro S.A.)</t>
+          <t>Metrô de São Paulo (Companhia do Metropolitano de São Paulo)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Francisca Javiera Estrada Quezada</t>
+          <t>Antonio Julio Castiglioni Neto</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Director (Directora)</t>
+          <t>Diretor-Presidente e Conselheiro (CEO and Board Member)</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government via shareholders' meeting (confirmed April 29, 2024)</t>
+          <t>Appointed by Governor Tarcísio de Freitas; confirmed by the Conselho de Administração on April 27, 2023; continues as CEO and board member, appearing unchanged on the current governance portal listing after the April 2026 board changes</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Corporate lawyer with extensive experience in state-owned enterprises and mining. Senior corporate lawyer and director of subsidiaries at Codelco (Chile's national copper company). First woman to serve as fiscal (chief legal officer) of an operating division at Codelco (División Gabriela Mistral). Currently serves as Fiscal (chief legal officer) at ENAMI (Empresa Nacional de Minería). Expertise in regulatory law and corporate governance of state enterprises.</t>
+          <t>Career state attorney (Procurador do Estado) since 2005 in Espírito Santo, specializing in concessions and public-private partnerships. Served as CEO of Porto de Vitória (2019–2022), leading Brazil's first port authority privatization. Previously headed the regulatory agency (ARSP) in Espírito Santo (2015–2019). Since taking the Metrô CEO role, has also served as a board member of Sabesp (Aug 2023–Sep 2024) and, since November 2024, of Companhia Docas de São Sebastião (CDSS).</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Lawyer (Abogada), Universidad de Chile; Master in Regulatory Law, Pontificia Universidad Católica de Chile</t>
+          <t>Law degree; expertise in concessions and PPP law</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Corporate lawyer specializing in regulatory law and state-owned enterprise governance. Career primarily in mining sector legal roles (Codelco, ENAMI). Brings legal and corporate governance expertise but no transit-specific background.</t>
+          <t>Legal background with executive experience in port management, water utility governance, and regulatory agencies, not transit operations. His expertise is public law, concessions, and privatization—management/policy skills applied to infrastructure generally, not transit-specific operations.</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.linkedin.com/in/javieraestradaquezada/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2787,74 +2787,74 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Metro de Santiago (Metro S.A.)</t>
+          <t>Metrô de São Paulo (Companhia do Metropolitano de São Paulo)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Matías Ambrosio Salazar Zegers</t>
+          <t>Daniel Rodrigues Aldigueri</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Conselheiro de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Appointed by national government (October 10, 2023, replacing Gabriela Elgueta Poblete; confirmed at shareholders' meeting April 29, 2024)</t>
+          <t>Elected by the General Assembly; already a board member in the March 2026 RI-2025 report and continues unchanged on the current governance portal listing</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Lawyer and public policy professional. Served as Regional Secretary of Transport (Seremi de Transportes) of the Metropolitan Region during President Michelle Bachelet's second government (2014-2018). Head of the Division of Planning and Regional Development at the Santiago Metropolitan Regional Government (from June 2023). Member of the Socialist Party. Expertise in regulatory law, economic law, and administrative law.</t>
+          <t>Civil engineer with more than 25 years of professional experience in infrastructure, transport services, and corporate governance. Career civil servant in the ANAC regulation-specialist track; currently Diretor de Navegação e Fomento (Director of Navigation and Development) at the Ministry of Ports and Airports (MPOR) and President of the Port Authority Council of the Port of Fortaleza.</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Lawyer (Abogado); Master in Law with specialization in Regulatory Law</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Civil Engineering (UFC); Doctorate in Transportation (Universidade de Brasília); Master's in Transportation Engineering (Poli/USP); Master's in Logistics and Port Management (UPV, Spain); JICA (Japan) certificate in Urban Transport Planning and Design</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Government policy and legal professional. While he served as Regional Secretary of Transport (an appointed government position, not elected), this was a policy/regulatory oversight role rather than direct transit operations management. His broader career is in law, regulatory policy, and regional government planning. The Seremi role is an appointed administrative position representing the national ministry at regional level, classified here as policy/management rather than transit operations.</t>
+          <t>Aldigueri's actual career track has been in ports and civil-aviation regulation (ANAC, Ministério de Portos e Aeroportos, Porto de Fortaleza port authority), not urban rail or bus transit operations or capital projects. Under the rule that general engineers do not qualify as Transit Ops/Management unless they worked in transit, his professional experience places him in Other Management/Policy.</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.latercera.com/pulso/noticia/metro-designa-a-ex-seremi-de-transporte-como-director-de-la-compania/AX72LBIBVJADVA5R2QMIWSTWXM/; https://corporacionrm.cl/sr-matias-salazar-zegers/; https://www.linkedin.com/in/matias-salazar-46265225/</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://www.gov.br/portos-e-aeroportos/pt-br/composicao/secretaria-nacional-de-hidrovias-e-navegacao/departamento-de-navegacao-e-fomento/daniel-rodrigues-aldigueri; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2876,27 +2876,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Milton Frasson</t>
+          <t>Fabiano Martins de Oliveira</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Presidente do Conselho de Administração (Board Chair)</t>
+          <t>Conselheiro de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly</t>
+          <t>Elected by the General Assembly; already a board member in the March 2026 RI-2025 report and continues unchanged on the current governance portal listing</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Business administrator with career in finance and administration at São Paulo state transport companies. Served as Administrative and Financial Director at CPOS (2008–2011) and CPTM—São Paulo's commuter rail company (2011–2019). Currently serves as Executive Advisor at CPTM.</t>
+          <t>Municipal Tax Auditor (Auditor-Fiscal Tributário Municipal) for the City of São Paulo. Served more than four years as Subsecretário de Planejamento e Orçamento (Subsecretary of Planning and Budget) for the Municipality of São Paulo, where he also served as Director of Financial Administration. Since 2019, has served as a Conselheiro de Administração (board member) of São Paulo Transportes (SPTrans), the city's bus-transit authority. Also served as a Fiscal Council member at CET (Companhia de Engenharia de Tráfego) and São Paulo Urbanismo.</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Business administration degree; postgraduate degree in Financial Administration</t>
+          <t>Specialist in Financial Management; MBA in Modern Tax Management</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>While Frasson has spent his career at transit-adjacent organizations (CPTM, CPOS), his roles were administrative and financial rather than operational. He did not manage transit operations, engineering, or capital projects directly. His expertise is in finance and administration applied to transport companies.</t>
+          <t>Although he holds a board seat at SPTrans, that is an oversight/governance role rather than a transit operations or capital-projects management role, and his own career is in municipal tax auditing and budget/finance administration. His expertise is public finance and administration applied across several city agencies, not direct transit operations management.</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://ri-admin.metrosp.com.br/wp-content/uploads/2025/04/Ata_2025_04_29_AGOE_PCA.pdf</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf; https://www.sptrans.com.br/relatorio-integrado-da-administracao-2024/</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2943,42 +2943,42 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Antonio Julio Castiglioni Neto</t>
+          <t>Mauro Antônio Gumiero Voltarelli</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Diretor-Presidente e Conselheiro (CEO and Board Member)</t>
+          <t>Conselheiro de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Appointed by Governor Tarcísio de Freitas; confirmed by the Conselho de Administração on April 27, 2023</t>
+          <t>Elected by the General Assembly; already a board member in the March 2026 RI-2025 report and continues unchanged on the current governance portal listing</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Career state attorney (Procurador do Estado) since 2005 in Espírito Santo, specializing in concessions and public-private partnerships. Served as CEO of Porto de Vitória (2019–2022), leading Brazil's first port authority privatization. Previously headed the regulatory agency (ARSP) in Espírito Santo (2015–2019).</t>
+          <t>Business administrator. Owned and operated Pura Transporte e Logística, a private transport company (May 2002–Nov 2011). Worked as a management/finance/commercial consultant at Landits Gestão de Shopping Centers (Jan 2012–Dec 2014) and as owner-president of OutCome Consultoria Empresarial (Jan 2015–Mar 2017). Served six years as Gerente Setorial (Sectoral Manager) at DETRAN-SP, the state vehicle-licensing department. Advisor at CPTM (São Paulo's commuter rail company) from April 2023 to February 2025. Currently Diretor Administrativo/Financeiro e Infraestrutura (Director of Administration, Finance and Infrastructure) at São Paulo Transporte S.A. (SPTrans), the city's bus-transit authority; briefly served as SPTrans's Acting President (Diretor-Presidente em Exercício) in mid-2025.</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Law degree; expertise in concessions and PPP law</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Administration degree; MBA in Business Management; postgraduate in Controllership and Finance (PEC-Controladoria e Finanças)</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Legal background with executive experience in port management and regulatory agencies, not transit operations. His expertise is in public law, concessions, and privatization—management/policy skills applied to infrastructure, not transit-specific operations.</t>
+          <t>SPTrans's own organizational chart places Voltarelli's unit — the Diretoria de Administração e de Infraestrutura (DA) — as a directorate distinct from the Diretoria de Operações (which runs bus service) and the Diretoria de Planejamento de Transporte (which handles transit planning/capital projects). DA itself is composed of a Superintendência Financeira, a Superintendência Administrativa, and a Superintendência de Infraestrutura — i.e., it is fundamentally a finance/procurement/corporate-support directorate that also houses infrastructure-asset administration, not the unit that delivers bus service or executes transit capital projects. Combined with his broader career (private transport-company ownership, vehicle-licensing administration, management consulting), his primary expertise reads as general business/financial administration rather than hands-on transit operations or capital-project management.</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://prefeitura.sp.gov.br/web/mobilidade/w/institucional/sptrans/acesso_a_informacao/179594; https://prefeitura.sp.gov.br/web/mobilidade/w/agenda-do-diretor-presidente-em-exerc%C3%ADcio-mauro-ant%C3%B4nio-gumiero-voltarelli-13-de-agosto-de-2025</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3010,42 +3010,42 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Carlos Roberto de Albuquerque Sá</t>
+          <t>Wagner Fajardo Pereira</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro Independente e Coordenador do Comitê de Auditoria Estatutário (Independent Board Member and Statutory Audit Committee Coordinator)</t>
+          <t>Conselheiro Representante dos Empregados (Employee Representative Board Member)</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly as independent member</t>
+          <t>Elected by Metrô employees as their representative on the board (mandated by Brazilian state-enterprise law, Lei 13.303/2016); confirmed unchanged as the sole employee representative on the current governance portal listing</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Accountant and economist specializing in corporate governance, risk management, and compliance. Professor of Corporate Risk Management at IBGC (Brazilian Institute of Corporate Governance). Serves as Audit Committee Coordinator at Camil Alimentos since 2018. IBGC-certified board member.</t>
+          <t>Graduate in Social Communication (Faculdade de Comunicação, Universidade Metodista de São Paulo). Workplace Safety Technician (Técnico de Segurança do Trabalho) at Metrô since 1981. Extensive career in labor representation: former worker representative on the CBTU (Companhia Brasileira de Trens Urbanos) board, councilor at the Cities Ministry (Conselho das Cidades), and Coordinator of the General Secretariat of the São Paulo Metro Workers Union (Sindicato dos Metroviários de São Paulo).</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Accounting and economics degrees; postgraduate training in finance</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Other Management/Policy</t>
+          <t>Degree in Social Communication</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Labor Representative</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Finance, accounting, and corporate governance professional. No transit background. His role is explicitly focused on audit oversight and risk management—core financial management expertise.</t>
+          <t>Explicitly designated employee/union representative seat on the board, as required by Brazilian state-enterprise law. Wagner is a career Metrô employee and a Metro Workers Union leader, confirming the mandated employee-representative classification.</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://diariodotransporte.com.br/2024/12/16/metro-de-sao-paulo-publica-ata-de-conselho-que-elegeu-novo-diretor-de-engenharia-e-planejamento/</t>
+          <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3077,27 +3077,27 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Cleyton Ricardo Batista</t>
+          <t>Walkyria Aparecida Augusto</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro (Board Member)</t>
+          <t>Conselheira Independente e Coordenadora do Comitê de Auditoria Estatutário (Independent Board Member and Statutory Audit Committee Coordinator)</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly</t>
+          <t>Elected by the Extraordinary General Assembly on April 28, 2026 as an independent board member, taking over as Statutory Audit Committee coordinator — the role previously held by outgoing member Carlos Roberto de Albuquerque Sá. Mandate runs until the Ordinary General Assembly approving 2027 accounts, expected April 2028.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Public attorney with over 20 years of experience, specializing in Civil Law. Heads the Judicial and Advisory Contentious Department at EMTU/SP (Empresa Metropolitana de Transportes Urbanos de São Paulo), the state's metropolitan transportation authority that coordinates bus and other transit services in the São Paulo metropolitan region.</t>
+          <t>Business administration graduate with an MBA in Risk Management and Finance. Certified Internal Auditor (CIA), certified in Control Self-Assessment (CCSA) and Risk Management Assurance (CRMA), and certified in anti-money-laundering/counter-terrorist-financing (PLDFT) and Compliance &amp; Ethics. IBGC-certified Board Member (CCA) and Audit Committee member (CCoAud). Currently chairs the Statutory Audit Committee at Banco Pine and sits on the advisory boards of Giant Cargo and the Associação Fernanda Bianchini (a ballet company for the blind). Former financial-market executive in Audit, Compliance, and Risk.</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Law degree; specialist in Civil Law</t>
+          <t>Business administration degree; MBA in Risk Management and Finance; CIA, CCSA, CRMA, PLDFT and Compliance &amp; Ethics certifications; IBGC Certified Board Member (CCA) and Audit Committee Member (CCoAud) certifications</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Legal professional working at a transportation authority (EMTU/SP), but his role is judicial/legal advisory, not transit operations or management. His expertise is in law applied to the transport sector.</t>
+          <t>Finance, audit, risk, and compliance executive with no transit background; her role is explicitly audit/risk oversight, the same finance-governance profile as her predecessor Carlos Roberto de Albuquerque Sá in the prior board version.</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/</t>
+          <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3144,27 +3144,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Luís Felipe Vidal Arellano</t>
+          <t>Alessandra de Almeida Figueiredo</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro (Board Member)</t>
+          <t>Conselheira de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly; represents São Paulo municipal government interests as Secretary of Finance</t>
+          <t>Elected by the Extraordinary General Assembly on April 28, 2026; mandate runs until the Ordinary General Assembly approving 2027 accounts, expected April 2028</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Career municipal attorney (Procurador do Município) and currently Secretary of Finance (Secretário da Fazenda) of the Municipality of São Paulo since June 2023. Previously served as Sub-secretary of the Municipal Treasury (2014–2018) overseeing financial management, public debt, accounting, and fiscal policy. President of the Governance Committee for Parastatal Entities. Also worked in tax audit at both municipal and federal levels.</t>
+          <t>Corporate attorney and Master's candidate in Public Policy; specialist in Legal Administration and Business Law. Partner at Figueiredo Advogados, with 24 years of experience advising large national and international companies. Director of the UK-based Caring Family Foundation, Global Advisor for G100 Women, and advisor to law firms. Recognized as an executive-leadership standout by Santander's SW50 program and listed among the country's most admired lawyers by trade publications.</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Law degree; Doctorate in Economic and Financial Law from USP; MBA in Advanced Public Finance Management from Fundação Dom Cabral; Specialist in Economic Analysis from FIPE/USP</t>
+          <t>Law degree; Master's in Public Policy (in progress); specialist certifications in Legal Administration and Business Law</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Public finance and law expert serving as the city's finance secretary. While a senior government official, he is an appointed (not elected) official. His expertise is in finance, law, and fiscal policy—not transit operations.</t>
+          <t>Corporate/business lawyer with no transit background; her expertise is corporate law, governance advisory, and business law — non-transit professional skills.</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://www.linkedin.com/in/luis-felipe-vidal-arellano-phd-mba-cca-b91b5748/; https://www.agendaspmaisverde.org.br/palestrantes/luis-felipe-vidal-arellano/</t>
+          <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3211,27 +3211,27 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Villaça Vargas Sampaio Braga</t>
+          <t>André da Silva Curcio</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro (Board Member)</t>
+          <t>Conselheiro de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly; represents the São Paulo state government (Governor's office)</t>
+          <t>Elected by the Extraordinary General Assembly on April 28, 2026; mandate runs until the Ordinary General Assembly approving 2027 accounts, expected April 2028</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Attorney specializing in Constitutional Law and Public Administration. Served as advisor to Superior Court justices until January 2023. Currently Special Advisor (Assessor Especial) to São Paulo Governor Tarcísio de Freitas. His LinkedIn profile confirms his role in the São Paulo state government.</t>
+          <t>Holds law and letters (bachelor's and teaching license) degrees and is pursuing graduate studies in Neuroscience and Behavior. More than 15 years at the São Paulo state Secretaria da Fazenda (State Treasury/Finance Department); Corregedor Geral (Inspector General) of the Tax Audit Inspectorate since March 2024 and a Judge on the state Tax and Fees Tribunal (Tribunal de Impostos e Taxas) since January 2022. Previously a State Revenue Tax Auditor (Auditor Fiscal da Receita Estadual); guest accounting instructor at FUNDACE/USP.</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Law degree; postgraduate credentials in Constitutional Law and Public Administration</t>
+          <t>Law degree; Letters degree (bachelor's and teaching license); graduate studies in Neuroscience and Behavior</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Government legal advisor and attorney with constitutional law expertise. He is an appointed advisor to the governor, not an elected official. His background is in law and public administration, not transit.</t>
+          <t>Career state tax-administration and judicial official (state Treasury inspectorate, tax tribunal judge); legal and fiscal-policy expertise, with no transit background.</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://www.linkedin.com/in/gustavo-villa%C3%A7a-b60542146/</t>
+          <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3278,27 +3278,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Mauro Antônio Gumiero Voltarelli</t>
+          <t>Eugênia Cristina Cleto Marolla</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro (Board Member)</t>
+          <t>Conselheira de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly</t>
+          <t>Elected by the Extraordinary General Assembly on April 28, 2026; mandate runs until the Ordinary General Assembly approving 2027 accounts, expected April 2028</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Administrator and management consultant. Former owner of Pura Transporte, a private transport company (2011–2022). Sectoral Manager at DETRAN-SP (state vehicle licensing department) since 2017. Subsequently served as Acting President (Diretor Presidente em Exercício) at SPTrans, São Paulo's municipal bus transit authority, in mid-2025.</t>
+          <t>Career state attorney (Procuradora do Estado de São Paulo, PGE/SP) since 2004, with the last five years focused on strategic legal consulting for public administration — public-service regulation, concessions and PPPs, administrative contracts, and project governance. Recently held leadership roles in the São Paulo state Casa Civil (Governor's Office): Subsecretária de Análise Governamental, coordinating teams that review the merit, convenience, and compliance of proposals submitted to the Secretary-Chief of Casa Civil and the Governor; and Assessora-Chefe of the government's technical advisory unit, reviewing compliance and preparing gubernatorial acts. Also served on the Fiscal Council of DesenvolveSP, the state's development-finance agency.</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Administration degree; MBA in Business Management</t>
+          <t>Law degree; career state attorney (Procuradoria Geral do Estado de São Paulo)</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -3308,22 +3308,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>While Voltarelli later served as Acting President at SPTrans (the municipal bus authority), his primary background is in private transport business ownership, management consulting, and vehicle licensing (DETRAN). His career is in management and administration applied to the transport sector rather than hands-on transit operations management.</t>
+          <t>Career state attorney and gubernatorial-office legal/policy advisor specializing in public-service concessions, PPPs, and public-administration governance; law and policy expertise, not transit operations.</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://prefeitura.sp.gov.br/web/mobilidade/w/agenda-do-diretor-presidente-em-exerc%C3%ADcio-mauro-ant%C3%B4nio-gumiero-voltarelli-13-de-agosto-de-2025</t>
+          <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3345,27 +3345,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>João Jorge Fadel Filho</t>
+          <t>Fabiano Maia Pereira</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Conselheiro Independente (Independent Board Member)</t>
+          <t>Conselheiro de Administração (Board Member)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Elected by the General Assembly as independent member</t>
+          <t>Elected by the Extraordinary General Assembly on April 28, 2026; mandate runs until the Ordinary General Assembly approving 2027 accounts, expected April 2028</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Limited publicly available biographical information. Appears in São Paulo legal databases with extensive litigation history, suggesting a legal or business background. Designated as an independent member of the board, meaning he has no direct ties to the controlling shareholder (state government) or management.</t>
+          <t>Executive with experience in public and corporate finance, governance, and strategic management. In the five years before joining the board, served as an advisor at the São Paulo state Secretaria da Fazenda, focused on implementing a new treasury system under the state's Public Finance Management Modernization Program. Between May 2024 and April 2025, worked in the federal Secretaria de Relações Institucionais of the Presidency of the Republic, engaging with Congress and civil society on strategic economic policy. Served as CFO of ABGF (Agência Brasileira Gestora de Fundos Garantidores e Garantias) from 2022 to 2024, concurrently serving as its CEO (Diretor-Presidente) from 2023 to 2024, leading the company's strategic repositioning around financial sustainability and process modernization.</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Not publicly available</t>
+          <t>Could not verify — specific degrees/institutions were not stated in any source consulted</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -3375,94 +3375,27 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Independent board member with apparent legal/business background. No evidence of transit operations experience. Classified as Other Management/Policy by default given independent member designation typically requires business, finance, or legal expertise. Low confidence due to limited biographical data.</t>
+          <t>Public and corporate finance executive (state Treasury, federal government-relations, CFO/CEO of a federal guarantee-fund agency); finance and governance expertise, with no transit background.</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://www.jusbrasil.com.br/processos/nome/27787895/joao-jorge-fadel-filho</t>
+          <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Metrô de São Paulo (Companhia do Metropolitano de São Paulo)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Wagner Fajardo Pereira</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Conselheiro Representante dos Empregados (Employee Representative Board Member)</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Elected by Metro employees as their representative on the board (mandated by Brazilian state-enterprise law)</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Social Communications graduate and longtime Metrô de São Paulo employee since 1981, specializing in workplace safety. Extensive career in labor representation: former worker representative on the CBTU (Companhia Brasileira de Trens Urbanos) board, councilor at the Cities Ministry, and General Secretary Coordinator of the São Paulo Metro Workers Union (Sindicato dos Metroviários de São Paulo). Voted against the appointment of the current CEO in 2023, raising concerns about qualifications.</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Degree in Social Communication</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Labor Representative</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Explicitly designated employee/union representative seat on the board. Wagner is the General Secretary Coordinator of the Metro Workers Union and has served as a labor representative on multiple transit-related boards. His role on the Conselho de Administração is as the mandated employee representative.</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>https://af0020d.azurewebsites.net/conselho-de-administracao/; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M44"/>
+  <autoFilter ref="A1:M43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3549,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SBASE (Subterráneos de Buenos Aires S.E.) — now SBASAU (Subterráneos de Buenos Aires S.A.U.)</t>
+          <t>SBASAU (Subterráneos de Buenos Aires S.A.U.) — formerly SBASE (Subterráneos de Buenos Aires S.E.)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3563,31 +3496,31 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="G2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>City-owned state enterprise (sociedad del estado, transformed to sociedad anónima unipersonal in January 2026 via Decree 20/2026). Directorio appointed by the GCBA (Gobierno de la Ciudad Autónoma de Buenos Aires). The board consists of a president, vice president, and directors. The city government's head of government (Jefe de Gobierno) appoints all board members. SBASE/SBASAU is responsible for the development, administration, expansion, and oversight of the Buenos Aires subway (Subte) and Premetro infrastructure.</t>
+          <t>City-owned corporation. SBASE was transformed from a Sociedad del Estado into a Sociedad Anónima Unipersonal (SBASAU) via Decreto 20/2026 (published Boletín Oficial CABA, January 2026), implementing the conversion mandate of national DNU 70/2023 (Art. 48) for all state-participation companies. Ownership remains 100% GCBA; the change is a legal-form conversion, not a privatization, and Subte operations remain concessioned to Emova. Per the SBASE/SBASAU Estatuto, Título IV 'Dirección y Administración,' Artículo Noveno, the Directorio is composed of a Presidente, a Vicepresidente, and cuatro (4) Directores Titulares — six seats total — all designated by the Asamblea (GCBA, as sole shareholder) for three-year terms. A separate Comisión Fiscalizadora (statutory auditors — currently Mariano Edmundo Barroso, Jorge Iwanczuk, and Francisco José Olivero Majdalani per the official GCBA governance page) performs audit functions and is NOT part of the Directorio; it is excluded from this member list per the agency's own organizational chart.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>The most recent confirmed full board composition is from January 2024 (appointed under Jefe de Gobierno Jorge Macri). A 2025 board resolution (Resolution 134/2025) was signed by Ibáñez, Seefeld, Kogan, and De Stéfano — suggesting Jorge Kogan (former city Secretary of Transport, resigned Sept 2024) may have joined the board, possibly replacing a member. The company was formally transformed from Sociedad del Estado to Sociedad Anónima Unipersonal (SAU) in January 2026, though its functions and state ownership remain unchanged. There is no public-facing governance page listing current board members. No labor, community, or elected official seats exist on the board — all members are government appointees with professional/political backgrounds.</t>
+          <t>CHANGES SINCE MARCH 2026 SNAPSHOT: (1) SBASE completed its formal conversion to SBASAU under Decreto 20/2026 (Jan 2026); governance/ownership substance is unchanged. (2) Víctor José Colombano was confirmed as a new Director Titular, designated via Acta de Asamblea General Ordinaria dated 15 January 2026, effective 17 January 2026 — verified directly from the primary-source PDF text (GCABA Oficina de Integridad Pública dictamen IF-2026-33966889-GCABA-OFIP, extracted via pdftotext) which names him with D.N.I. 18.069.067. That DNI independently matches a 2004 Boletín Oficial CABA record ('Colombano, Víctor,' resignation as Director General de Emergencia Habitacional) and a CUIT registry entry, confirming this is the same longtime Peronist political figure — not a coincidental namesake. Public bios and party-affiliated outlets (Parlamentario, Ámbito, La Política Online) describe him as 'congresal Metropolitano del PJ CABA y congresal nacional PJ' (an internal Justicialist Party congress DELEGATE) plus a career in city/national public administration (Director General de Emergencia Habitacional 2004-era, manager roles tied to Mercado Central, Instituto de Vivienda de la Ciudad, and head of the national 'El Estado en tu Barrio' program from Oct 2022). CAUTION: some AI-generated web-search summaries mischaracterized him as a sitting 'national deputy with a mandate until 2027' — this could not be corroborated against the Honorable Cámara de Diputados de la Nación's own roster (hcdn.gob.ar), and the primary-source OFIP dictamen (which exhaustively reviews his declared activities for conflicts of interest) never mentions a seat in Congress, only simultaneous work as an employee of ADIF S.A. (national rail infrastructure agency) and an ad-honorem Secretario Administrativo y de Relaciones Institucionales at ALAF (Asociación Latinoamericana de Ferrocarriles, a rail-industry trade association). 'Congresal' (party congress delegate) is being conflated with 'diputado' (elected national deputy) in that search output; the two are not the same office, and this file treats him as NOT a current elected official absent stronger evidence. (3) Mario Sebastián Sabugo appears as a new Director Titular on the official GCBA governance page; he did not appear in the March 2026 snapshot, the January 2024 appointment-cycle press coverage, or any subsequent news article located during this research — his exact appointment date/method could not be independently verified beyond the live governance page. (4) Eduardo José Moreno and Bernarda Balestra, both present in the March 2026 file, no longer appear on the current official board listing; no departure date or reason was found in public sources. (5) Jorge Kogan — flagged in the March 2026 file only as 'probable' based on his signature on Resolution 134/2025 — is CONFIRMED ABSENT from the current Directorio; he does not appear on the official governance page, resolving the prior ambiguity (he was never durably a board member, or he departed without independent public documentation). SEEFELD CORRECTION (confirmed serious error in the March 2026 file): Guillermo 'Willy' Seefeld remains a sitting Director (the longest-serving member, on the board continuously since 2012, per the very enelSubte article the prior file cited). His actual documented background is: PRO party dirigente ('dirigente del PRO'), brother of actor Martín Seefeld, owner of a parador (beach resort) in Pinamar, and a longtime associate of Mauricio Macri's social/political circle; he was also named in reporting about corruption allegations tied to Subte graffiti-cleaning contracts. The background wrongly attributed to him in the March 2026 file — 'Secretario de Tránsito y Transporte del GCBA durante la gestión de Jorge Telerman' and 'Subsecretario de Transporte Terrestre de la Nación' (Menem era) — belongs to Gustavo Álvarez, a DIFFERENT SBASE director who served on an earlier (c. 2016) iteration of the board alongside Seefeld, Alabuenas, and Verónica López Quesada; Álvarez does not appear on the current board and this file does not include him. No professional/technical credentials or transit-management experience for Seefeld were found in any vetted source. UNVERIFIABLE / LOW-CONFIDENCE ITEMS: Sabugo's exact appointment date and appointment mechanism; the reasons/dates for Moreno's, Balestra's, and Kogan's departures from the board; Seefeld's formal education; Colombano's formal education and the complete content of his declared CV (only excerpts were quoted in the public OFIP dictamen). BLOCKED FETCHES: none — all cited domains were reachable. One caution: an early WebFetch pass at the OFIP PDF (via automatic HTML/text summarization) incorrectly reported the document contained no match for 'Colombano'; downloading the same file and running pdftotext directly resolved this and produced the accurate quotations used above, underscoring the need to verify AI-summarized fetches against raw source text for high-stakes facts.</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3543,7 @@
       <c r="D3" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>0.09090909090909091</v>
       </c>
       <c r="F3" s="9" t="n">
@@ -3619,7 +3552,7 @@
       <c r="G3" s="11" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="12" t="n">
@@ -3627,12 +3560,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Decentralized public body (organismo público descentralizado) governed by a Consejo de Administración (Board of Directors) composed entirely of government officials and institutional representatives. The Secretary of Mobility serves as Board President. The Board includes representatives from CDMX centralized administration (Secretarías de Gobierno, Finanzas, Obras), parastate entities (STE, Metrobús), federal government (SCT, Banobras), and the State of Mexico. The union (SNTSTC) was granted participation in Board sessions. A separate Consejo Consultivo (advisory council) of former directors and transit engineers was created in 2019. Day-to-day management is handled by a Director General appointed by the Jefe/Jefa de Gobierno. The Board has between 5 and 15 members per the Estatuto Orgánico. There are no independent or community-appointed members.</t>
+          <t>Decentralized public body (organismo público descentralizado) governed by a Consejo de Administración (Board of Directors) composed of government officials and institutional representatives, chaired by the Secretary of Mobility. Per Article 7 of the Estatuto Orgánico (reconstructed from the July 2018 text, which is the most recent version whose full Article 7 text could be retrieved — see notes on statute currency), the statutory voting seats are: from CDMX centralized administration — Secretary of Mobility (President), Secretary of Government, Secretary of Finance (now Secretaría de Administración y Finanzas, which absorbed the Oficial Mayor seat when that post was eliminated in 2019), Secretary of Works and Services; from CDMX parastatal entities — the Director General of Servicio de Transportes Eléctricos (STE) and the head of 'Sistema de Movilidad 1' (the 2016-2019 legal name of RTP/Red de Transporte de Pasajeros, now reverted to RTP but apparently not relabeled in Article 7's text — the seat is held by RTP's current Director General); from the federal government — a representative of SICT (formerly SCT) and a representative of Banobras; and one representative designated by the State of Mexico. Article 7 (2018 text) also references one public commissioner ('comisario público', voice but no vote) and, per a 2001 agreement, two citizen comptrollers ('contralores ciudadanos') — see notes; these are non-voting oversight roles, not counted among the board members below. The Director General of STC is NOT listed as an Article 7 Council seat; available evidence indicates the Director General is the administrator/executive appointed by the Jefa de Gobierno who implements Council resolutions and reports to the Council (commonly functioning as its non-voting secretary in this type of CDMX decentralized body), rather than a voting member — he is nonetheless included below because he is the agency's chief executive and because prior analysis specifically asked that his classification be documented. The union (SNTSTC) has no Article 7 seat; its participation in Council sessions stems from an administrative agreement announced by the STC Director General in 2013-2015 under instruction from then-Head of Government Miguel Ángel Mancera, granting the union attendance at Council sessions and two seats on the Comité de Incidentes Relevantes — not a statutory board seat. A separate Consejo Consultivo (advisory council) of outside experts, academics, and civil-society representatives exists alongside the Consejo de Administración (referenced in modifications from 2018 and again in 2024) but is a distinct body. There are no independent/community-appointed voting members on the Consejo de Administración itself.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>The STC Metro's Consejo de Administración is entirely composed of government officials — no independent members, community representatives, or rider advocates. The Secretary of Mobility chairs it, making it effectively a government coordination body rather than an independent oversight board. The Director General is a political appointee of the Jefa de Gobierno (Clara Brugada). The current Director General, Adrián Rubalcava, is a career politician (former mayor of Cuajimalpa, lawyer by training) with no transit operations background. The union leader Fernando Espino Arévalo has controlled the SNTSTC since 1978 (over 47 years). The Estatuto Orgánico was last modified in 2022. The Oficial Mayor position was eliminated in CDMX in 2019 and absorbed by the Secretaría de Administración y Finanzas. Board size of 11 is estimated based on statutory composition — exact current membership is difficult to verify as CDMX does not publish a public roster of sitting board members. Federal representatives (SCT, Banobras) and State of Mexico representative could not be individually identified.</t>
+          <t>STATUTE CURRENCY (Q1): The March 2026 file's claim that the Estatuto Orgánico was 'last modified in 2022' is incomplete. Actual chronology established: a prior version was published 1967 with amendments through 2007 and July 6, 2018 (full text of this 2018 version, including Article 7, was retrieved via vlex.com.mx); a wholly new Estatuto Orgánico entered into force August 29, 2022 (published in Gaceta Oficial August 24, 2022), explicitly revoking the 2007 and 2018 versions; it was further modified July 6, 2024 (creating an external Consejo Consultivo, adding 'sesiones emergentes,' and expanding security/anti-vendor powers) and again around September 18, 2024 (clarifying that the Director General is appointed by the Head of Government). News coverage of the 2022 and 2024 modifications describes governance/procedural and security changes but none reports any change to the Consejo de Administración's seat composition. However, the full current text of Article 7 (2022/2024 version) could not be retrieved — metro.cdmx.gob.mx (including its /storage PDF of the 2022 Gaceta) was unreachable via both WebFetch and a direct curl attempt (connection timed out / ECONNREFUSED from IP 187.218.8.10), and capital-cdmx.org (403) and reforma.com (403) also could not be fetched. The composition described here is therefore RECONSTRUCTED from the revoked-but-fully-retrieved 2018 text plus secondary reporting confirming no compositional changes since — rated Medium confidence, not High, pending direct access to the current Gaceta Oficial text. DIRECTOR GENERAL STATUS (Q1): Not an Article 7 Council seat in the retrieved text; he is the administrator appointed by the Jefa de Gobierno who executes Council decisions. Kept in this roster (flagged) per the classification-documentation instruction, not because his formal board membership is confirmed. 'SISTEMA DE MOVILIDAD 1' SEAT (Q2): Resolved. RTP (Red de Transporte de Pasajeros, created 2000) was legally renamed 'Sistema de Movilidad 1' / 'M1' on June 15, 2016, and reverted to the RTP name on January 2, 2019 — Article 7's reference to 'Sistema de Movilidad 1' is the pre-2019 legal name of RTP, not Metrobús (a separate decentralized organism created by decree in 2005 with no identified Article 7 seat). The seat is therefore held by RTP's current Director General, Daniel Arcos Rodríguez — NOT by Rosario Castro Escorcia, who heads Metrobús and has been removed from this roster accordingly (she may still be a capable, transit-experienced official — UNAM economics, Colmex master's, career across STC/SEMOVI/Metrobús — but the evidence does not place her on this board). Residual uncertainty: without the current Article 7 text, it cannot be fully excluded that a 2022/2024 amendment added Metrobús or relabeled the seat; confidence on Arcos holding this specific seat is Medium. UNION SEAT (Q3): Resolved — not a formal Article 7 seat. SNTSTC's presence at Consejo de Administración sessions originates in a 2013-2015 negotiated administrative agreement (announced by the STC Director General under instruction from Jefe de Gobierno Miguel Ángel Mancera) granting the union participation in Council sessions and two seats on the Comité de Incidentes Relevantes, not a designated board seat under the Estatuto. Fernando Espino Arévalo remains listed here because this negotiated participation has persisted for over a decade and is treated as de facto board presence in practice (confirmed active as recently as April 2026, alongside DG Rubalcava, in union-STC negotiations). NON-VOTING SEATS (Q4): Resolved — the 2018 Article 7 text references one public commissioner ('comisario público,' voice but no vote) and, per a 2001 agreement, two citizen comptrollers ('contralores ciudadanos'). These are oversight/non-voting roles rather than board members and are NOT included in members[] or board_size; if counted, they would add three unnamed 'Other Management/Policy'-type entries. No individuals holding these roles in 2026 could be identified — could not verify. UNNAMED SEATS (Q5): The federal SICT representative, federal Banobras representative, and State of Mexico representative could not be identified by name despite targeted searching (news archives, transparency portals, Banobras' own transparency filings) — kept as institutional placeholders, Low confidence. ESPINO CORRECTIONS (Q6): Corrected. He served as federal/local deputy on six occasions between 1991 and 2015 (federal deputy 1991-1994 in the 55th Legislature; local ALDF deputy 2000-2003; federal deputy 2009-2012 in the LXI Legislature; plus additional terms per SIL/Segob legislator records) — not 1991-2012 as previously filed. His electrical engineering degree from IPN (Instituto Politécnico Nacional) is confirmed, including his involvement in IPN's 'porrista' movement at the Escuela Superior de Ingeniería Mecánica y Eléctrica. WHAT CHANGED SINCE MARCH 2026: (1) Rosario Castro Escorcia (Metrobús) removed; Daniel Arcos Rodríguez (RTP) added as the actual 'Sistema de Movilidad 1' seat-holder — a reclassification of who was already misidentified in March, not a change in officeholder (Arcos has led RTP through 2026; no evidence he is new to the post). (2) Espino's political-career dates and education corrected per Q6. (3) Martín López Delgado (STE) confidence downgraded from High to Medium — his continued tenure as of August 2026 could not be freshly confirmed beyond an undated RTP social-media post pairing him with Daniel Arcos; no reporting of his removal was found either. (4) All four CDMX secretaries (SEMOVI, Gobierno, Administración y Finanzas, Obras y Servicios) and DG Rubalcava confirmed still in post as of August 2026 (Rubalcava confirmed active via an August 26, 2026 CIDESI collaboration agreement, despite an April 2026 opinion piece speculating his 'days were numbered' amid a metro workers' strike — that speculation did not materialize). BLOCKED/UNREACHABLE FETCHES: metro.cdmx.gob.mx and all its subpaths (ECONNREFUSED via WebFetch; connection timed out via direct curl from the user's machine, indicating the host itself is not reachable from this network, not merely a proxy restriction), rtp.cdmx.gob.mx (ECONNREFUSED), ste.cdmx.gob.mx (curl timeout), transparencia.cdmx.gob.mx storage PDF (ECONNREFUSED), capital-cdmx.org (403), reforma.com (403), web.archive.org (harness-blocked, cannot be used as a mirror). vlex.com.mx, es.wikipedia.org, and general WebSearch were usable and form the evidentiary backbone of this file. UNVERIFIABLE: exact current Article 7 text (2022/2024 version); identities of the SICT rep, Banobras rep, State of Mexico rep, public commissioner, and two citizen comptrollers; Daniel Arcos Rodríguez's professional background/education beyond holding a maestría ('Mtro.') and running RTP.</t>
         </is>
       </c>
     </row>
@@ -3653,31 +3586,31 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="G4" s="10" t="n">
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" s="12" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Mixed-ownership company (sociedad de economía mixta) with 9-member board: 4 ex-officio seats from subnational government (Mayor of Medellín, Director of Planning of Medellín, Governor of Antioquia, Director of Planning of Antioquia) and 5 members appointed by the President of the Republic (2 ministry representatives from Transport and Finance, plus 3 independents). National government holds majority control through its 5 presidential appointees.</t>
+          <t>Mixed-ownership company (sociedad de economía mixta) structurally organized as a 9-member board: 4 ex-officio seats from subnational government (Mayor of Medellín, Director of Planning of Medellín, Governor of Antioquia, Director of Planning of Antioquia) and 5 seats whose appointment power rests with the national government (2 ministry representatives — Transport and Finance — plus 3 independents named by the President). As of the verification date, only 7 of the 9 principal seats are filled; the 2 independent presidential-appointee seats are vacant (see notes). Whichever national administration holds the presidency controls appointment of the 5 national seats, giving the national government a structural majority when all seats are filled.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Board composition reflects September 2023 presidential appointments (Decree 1561) plus local officials elected in October 2023 who took office January 2024. The 5 national-government seats give the Petro administration majority control. Some controversy arose because two of the independent appointees (Hinestroza, Tafur) had business ties to former Medellín mayor Daniel Quintero. Manuel Naranjo may have shifted roles within the Antioquia government (to Secretary of Economic Development), but was listed on the official Metro board page as of verification date.</t>
+          <t>CHANGES SINCE MARCH 2026 SNAPSHOT: (1) Antioquia Director of Planning seat turned over twice: Manuel Alejandro Naranjo Giraldo → an intermediate holder, Eugenio Prieto Soto → Luis Fernando Agudelo Henao, formalized by an Antioquia governor's decree dated 2026-07-16 (corroborated independently via his antioquia.gov.co gabinete profile, which lists him as current Director of the Departamento Administrativo de Planeación). (2) Medellín Director of Planning seat also turned over: Ana Cathalina Ochoa Yepes (confirmed correct as of March 2026) has been replaced by Luz Ángela González Gómez, independently corroborated by an August 19, 2026 news item (ifmnoticias.com) showing González presenting the POT review to Medellín's city council in that capacity. Exact transition date not found. (3) Ministry of Transport board representative appears to have changed from Ferney Camacho to Liliana Yanneth Bohórquez Avendaño, who now holds (per her own Metro bio) the role of (acting/'encargada') Director of Infrastructure at the Ministry of Transport — the same ministry post that carries this board seat. This is corroborated only by the Metro's own current bio page for her (metrodemedellin.gov.co/quienes-somos/.../liliana-yanneth-bohorquez-avendano) and her LinkedIn profile; no independent news article or decree confirming the Camacho→Bohórquez handover or its date was found. Colombia's presidential transition (new President Abelardo de la Espriella inaugurated 2026-08-07, appointing an entirely new cabinet including a new Transport Minister, Elsa Margarita Noguera, per Decree 1136) makes ministry-level staff turnover plausible around this time, but the causal link to this specific board seat change is inferred, not confirmed — flagged as unverifiable. (4) BOARD SIZE FINDING: the board is still structurally 9 principal seats — that has not changed — but 2 of the 3 independent presidential-appointee seats (previously held by Juan Carlos Tafur Hernández and Mary Luz Escobar Rivera) are listed as 'Vacante' on Metro de Medellín's current official board roster page (metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva), leaving Sebastián Hinestroza Arango as the only filled independent seat. This vacancy is reported as fact based on that single official source; the CAUSE and TIMING of the vacancies were not verified (could reflect resignations/removals under the outgoing Petro administration before 2026-08-07, or a transition-related gap awaiting new decrees from the De la Espriella administration — no news coverage of either was found). Corroboration is mixed: Juan Carlos Tafur Hernández's individual Metro bio page now 404s (consistent with departure — his prior bio content is instead sourced here via a still-working El Colombiano article), but Mary Luz Escobar Rivera's individual Metro bio page still resolves and displays her old bio content, which is inconsistent with the roster page marking her seat vacant. This inconsistency (a stale orphaned bio page vs. an updated roster listing) was not resolved and should be re-checked in the next verification cycle. Because members[] lists only actual named seat-holders, board_size here is set to 7 (matching len(members)); this must NOT be read as the board having permanently shrunk to 7 seats — see governance_model. (5) Fixed per audit: Sebastián Hinestroza Arango's education field previously incorrectly stated an unconfirmed 'engineering/construction' background; his official Metro bio states he holds a degree as 'Administrador de Negocios' (Business Administrator) with a specialization in Gerencia de Proyectos (Project Management) — no specific university is named on the source page. (6) The dead Tafur source URL (metrodemedellin.gov.co/en/.../juan-carlos-tafur-hernandez, confirmed 404) has been replaced for historical reference with a working article: https://www.elcolombiano.com/medellin/carta-juan-carlos-tafur-metro-problemas-tecnicos-EG25672688 UNCHANGED AND RE-CONFIRMED: Andrés Julián Rendón Cardona (Governor), Federico Gutiérrez Zuluaga (Mayor), and Luis Alexander López Ruíz (Ministry of Finance representative) all remain in their board seats; López Ruíz's continuation post-transition was not independently corroborated beyond the current Metro roster page (Medium confidence). TRANSIT OPS TEST: under primary classifications, 0 of 7 current filled seats classify as Transit Ops/Management (same finding as March). One seat (Bohórquez, Ministry of Transport representative) is a genuinely contested case — her specialization in transit/transport design and her seat on the board of Metrolínea S.A. (Bucaramanga's BRT mass-transit operator) support an alternate Transit Ops/Management read, but her career is centered on traffic engineering and road safety administration (signal coordination, road-safety policy) rather than managing transit operations or capital projects, so the primary call remains Other Management/Policy. Under the alternate read, the count would be 1 of 7. Also unresolved: who currently presides over the board — the March snapshot listed Gutiérrez as 'President of the Board,' but a search result surfaced during this audit describes the board as presided over by the Governor; this was not independently re-verified, so the title has been narrowed to his ex-officio role without asserting the presidency.</t>
         </is>
       </c>
     </row>
@@ -3700,29 +3633,29 @@
       <c r="D5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>State-owned corporation (Empresa de Transporte de Pasajeros Metro S.A.) with a 7-member board (Directorio) appointed by the national government through the shareholders' meeting (Junta de Accionistas). The Chilean state, represented by the Treasury (Fisco de Chile) and CORFO, holds 100% of shares. Board members serve two-year terms and may be reelected indefinitely.</t>
+          <t>State-owned corporation (Empresa de Transporte de Pasajeros Metro S.A.) with a 7-member board (Directorio) appointed by the national government through the shareholders' meeting (Junta de Accionistas). The Chilean state, represented by the Treasury (Fisco de Chile) and CORFO, holds 100% of shares. Metro's bylaws historically provide for two-year board terms with indefinite reelection, but multiple April/May 2026 news reports describe the board seated on April 27, 2026 as serving for 'the next four years' (coinciding with President Kast's four-year presidential term); this discrepancy could not be resolved with the sources available (see notes).</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Board composition confirmed via official Metro governance page (updated March 11, 2026) and CMF filings. The current board was largely appointed in April 2022 under President Boric's administration, with one replacement (Salazar Zegers for Elgueta Poblete) in October 2023 and two new members (Estrada Quezada confirmed, González Leiva reconfirmed) at the April 2024 shareholders' meeting. Board renewal expected around late April 2026.</t>
+          <t>MAJOR CHANGE SINCE MARCH 2026: The entire board was replaced at an Ordinary Shareholders' Meeting on April 27, 2026, following the March 11, 2026 inauguration of President José Antonio Kast. All seven members from the March 2026 snapshot (Guillermo Muñoz Senda, Marcela Munizaga Muñoz, Susana González Leiva, Nicolás Valenzuela Levi, Tadashi Takaoka Caqueo, Francisca Estrada Quezada, Matías Salazar Zegers) were replaced. The new roster — Patricio Rey Sommer (President), Nicole Keller Flaten (VP), María Cecilia Guzmán Ossa, Rodrigo Troncoso Olchevskaia, Cristina Torres Delgado, Patricio Pérez Gómez, and Jorge Hermann Anguita — was independently verified against Metro's official governance page (last updated June 9, 2026, per the site) and the CMF corporate filing for entity RUT 61.219.000, both of which list the same seven names with an April 27, 2026 appointment date. This confirms the prior research was correct and complete. No further changes were found between April 27, 2026 and the August 27, 2026 verification date; the metro.cl governance page (updated as recently as June 9, 2026) still shows this same roster. NOTABLE FINDING: prior research undersold Patricio Pérez Gómez's transit credentials — a full profile (Instituto de Directores de Chile alumni page) shows he was General Manager of EFE (the state railway) and Director of the Metropolitan Public Transport Directorate (DTPM), plus a stint at transport consultancy Steer Davies Gleave, making him a clear Transit Ops/Management case rather than 'generic engineer.' UNCERTAIN/UNRESOLVED: (1) The 'four-year term' reported by multiple outlets (Ex-Ante, Radio Agricultura, T13) conflicts with the two-year term with indefinite reelection described in general summaries of Metro's bylaws found via search; could not access the underlying Metro S.A. estatutos document directly to resolve this, so it is flagged rather than asserted either way. (2) Two outlets (The Clinic, Emol) described Rodrigo Troncoso Olchevskaia as an 'architect,' but Metro's own governance page, a UDD faculty bio, and a ZoomInfo/UDD profile all independently identify him as an Ingeniero Comercial (Commercial Engineer) with a PhD in Economics from PUC — the 'architect' label appears to be a media mix-up with fellow UDD academic Pablo Allard (dean of Architecture), who was appointed to EFE's board the same week in a similar dual announcement; this JSON uses the corroborated Commercial Engineer/PhD Economics profile. (3) Detailed independent biographical sourcing for María Cecilia Guzmán Ossa relied on LinkedIn search snippets, an ESE Business School alumni page, and a cultural-consultancy team bio (g-v.cl) rather than a single authoritative profile — background is reasonably well corroborated across sources but confidence is Medium. (4) A DiarioMayor.cl article on Cristina Torres Delgado returned a 404 and could not be directly read; her current role (director, Centro de Políticas Públicas, Facultad de Economía y Negocios, Universidad San Sebastián) was instead corroborated via LinkedIn search snippet and a March 2026 El Dínamo interview. No WebFetch domains were blocked outright; all attempted fetches either succeeded or returned ordinary HTTP errors (404) unrelated to any allowlist restriction.</t>
         </is>
       </c>
     </row>
@@ -3743,31 +3676,31 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="10" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="H6" s="10" t="n">
+      <c r="I6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>State-owned mixed-capital company (sociedade de economia mista) controlled by the São Paulo state government. The Conselho de Administração (Board of Directors) has 7–11 members elected by the General Assembly for unified two-year terms with reelection permitted. The board must include the CEO (Diretor-Presidente), employee representatives, minority shareholder representatives, and independent members. The Diretoria Executiva (Executive Board) has up to 6 directors appointed by the Conselho de Administração.</t>
+          <t>State-owned mixed-capital company (sociedade de economia mista) controlled by the São Paulo state government. Per the company's 2025 Integrated Report, the Conselho de Administração (Board of Directors) has 7–11 members elected by the General Assembly for unified two-year terms with reelection permitted (a Moody's credit report instead cites a 3–11 range, which this file treats as a likely paraphrase of the bylaws rather than the authoritative figure). The board must include the CEO (Diretor-Presidente), an employee representative, minority-shareholder representatives, and independent members. As of this update the board is at its statutory maximum of 11 seats. The Diretoria Executiva (Executive Board) has up to 6 directors appointed by the Conselho de Administração.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Board composition sourced from the official Metrô corporate governance portal and cross-referenced with investor relations documents, Diário do Transporte coverage, and ANPTrilhos reporting. The company is supervised by the Secretaria dos Transportes Metropolitanos (STM) of São Paulo state. The governance page at governancacorporativa.metrosp.com.br returned a 503 error; data was obtained from a mirror/staging site (af0020d.azurewebsites.net) that appeared to have current board data consistent with other sources. Metrô is not listed on SEC EDGAR—it does not trade as an ADR on NYSE (unlike some other São Paulo state companies like SABESP). Wagner Fajardo Pereira is the sole employee/union representative on the board.</t>
+          <t>UPDATE FROM MARCH 2026 SNAPSHOT: The prior version of this file (date_verified 2026-03-17) was sourced from a stale mirror site (af0020d.azurewebsites.net) and incorrectly listed Cleyton Ricardo Batista, Luís Felipe Vidal Arellano, and João Jorge Fadel Filho as current members — all three left the board around 2023 and do not appear in any 2026 source consulted here. This refresh instead uses the company's official Relatório Integrado 2025 (published 2026-03-13; ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf), which shows a 9-member board as of March 2026 (Milton Frasson, Antonio Julio Castiglioni Neto, Carlos Roberto de Albuquerque Sá, Daniel Rodrigues Aldigueri, Fabiano Martins de Oliveira, Gustavo Villaça Vargas Sampaio Braga, Mauro Antônio Gumiero Voltarelli, Rodrigo Bezerra da Silva, Wagner Fajardo Pereira), plus the official Comunicado ao Mercado of 2026-05-11 (ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf) describing an Extraordinary General Assembly on 2026-04-28 that elected 5 new/replacement board members, and the live governance portal (governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administração.aspx), which returned a clean current roster of exactly 11 names during this research session (it had returned a 503 error in the prior March research round). CHANGES SINCE MARCH 2026: Compared to the RI-2025 9-member roster, three members are no longer listed on the governance portal — Carlos Roberto de Albuquerque Sá (independent member and Audit Committee coordinator), Gustavo Villaça Vargas Sampaio Braga (governor's office legal advisor), and Rodrigo Bezerra da Silva. Five new members joined via the 2026-04-28 Extraordinary General Assembly per the Comunicado: Walkyria Aparecida Augusto (independent member, now Audit Committee coordinator — the Comunicado's framing and her assumption of the coordinator role make clear she succeeds Carlos Roberto de Albuquerque Sá in that function), Alessandra de Almeida Figueiredo, André da Silva Curcio, Eugênia Cristina Cleto Marolla, and Fabiano Maia Pereira. Net effect: 9 - 3 + 5 = 11, which matches both the Moody's credit report of 2026-04-06 (moodyslocal.com.br, stating the board 'atualmente' has 11 members, 10 elected by the controlling shareholder plus the employee representative) and the statutory cap. Six members carry over unchanged from the March snapshot: Milton Frasson (Chair), Antonio Julio Castiglioni Neto (CEO), Daniel Rodrigues Aldigueri, Fabiano Martins de Oliveira, Mauro Antônio Gumiero Voltarelli, and Wagner Fajardo Pereira (employee representative, confirmed unchanged). COULD NOT VERIFY: (1) The exact dates and stated reasons for the departures of Carlos Roberto de Albuquerque Sá, Gustavo Villaça Vargas Sampaio Braga, and Rodrigo Bezerra da Silva — no resignation notice, Ata de Assembleia, or news coverage of their exits was found among the sources searched; their absence is inferred from the current governance portal listing versus their presence in the RI-2025 report. (2) Whether the Moody's report's 11-member count as of 2026-04-06 already reflects the 2026-04-28 board changes (which would mean the Moody's report's stated date lags its actual data-cutoff) or reflects a separate, earlier expansion of the RI-2025 board from 9 to 11 seats that was then partially reshuffled again on 2026-04-28 — the underlying Ata (minutes) of the 2026-04-28 Assembleia Geral Extraordinária was not located, so the exact sequencing of departures/additions between mid-March and late April 2026 could not be fully reconstructed; only the net start (9, March) and end (11, current) states are solidly confirmed. (3) Fabiano Maia Pereira's specific educational credentials were not stated in any source consulted. BLOCKED / FAILED FETCHES: conselhodeadministracao.metrosp.com.br returned an empty page; www.metrocptm.com.br and www.econodata.com.br both returned HTTP 403 Forbidden (neither is on the approved fetch allowlist, so this is expected); a direct WebFetch of the Estatuto Social PDF (governancacorporativa.metrosp.com.br) and of transparencia.metrosp.com.br/node/2782/download returned undecoded binary PDF content rather than extracted text. None of these blocked the final composition determination, which rests on the governance portal's live HTML listing, the official Comunicado ao Mercado, the RI-2025 report, and the Moody's report — all mutually consistent. Per the user's explicit direction, af0020d.azurewebsites.net and af0020.azurewebsites.net were not used as sources in this update.</t>
         </is>
       </c>
     </row>

--- a/latam_transit_boards.xlsx
+++ b/latam_transit_boards.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Agency Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -561,20 +561,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Judgment Call?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Why This Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Classification Rationale</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Source URL(s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Confidence Level</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Date Verified</t>
         </is>
@@ -626,22 +636,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>While Ibáñez has held numerous senior public administration roles, none involved direct transit operations or management. His career spans technology (INTI), culture (Teatro Colón), regulatory oversight, and general government management — all outside the transit sector.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>https://enelsubte.com/noticias/javier-ignacio-ibanez-es-el-nuevo-presidente-de-sbase/; https://buenosaires.gob.ar/subte/noticias/subterraneos-de-buenos-aires-tiene-nuevo-presidente; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -693,22 +705,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Alabuenas is a lawyer and public administrator. Although he has spent many years at SBASE, his roles have been in corporate governance and legal oversight rather than transit operations or engineering. His pre-SBASE career was in public space regulation, not transit.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>https://enelsubte.com/noticias/mauro-alabuenas-es-el-nuevo-presidente-de-sbase/; https://www.enelsubte.com/noticias/el-presidente-de-sbase-mauro-alabuenas-en-un-dialogo-exclusivo-con-enelsubte/; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -760,22 +774,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Sabugo's public-sector role (Subsecretario de Planeamiento) was general city/urban-environmental planning, not a transit-specific planning post — the city government's transit/mobility planning function sits in a separate Subsecretaría de Planificación de la Movilidad y la Seguridad Vial. His primary career is as an architecture-history academic. No evidence of direct experience managing transit systems, rail/bus operations, or transit capital projects was found, so this does not meet the bar for Transit Ops/Management under the 'general planners don't count unless transit-focused' rule.</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>https://buenosaires.gob.ar/gcaba_historico/nosotros; https://www.iaa.fadu.uba.ar/?tag=dr-arq-mario-sabugo; https://boletinoficial.buenosaires.gob.ar/normativaba/norma/111578</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -827,22 +843,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>De Stéfano's background is in intelligence and legal affairs, with no known transit experience. His appointment appears politically motivated rather than based on transit or management expertise.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>https://www.enelsubte.com/noticias/polemica-por-la-aparicion-de-un-director-de-sbase-en-el-video-de-la-gestapo/; https://www.enelsubte.com/noticias/escandalo-de-espionaje-oposicion-y-sindicatos-piden-que-se-remueva-a-de-stefano-del-directorio-de-sbase/; https://buenosaires.gob.ar/gcaba_historico/nosotros</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -881,7 +899,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>CORRECTED FROM PRIOR SNAPSHOT — PLEASE READ NOTES. Described in the agency's own cited source (enelSubte, 'Quién es quién en el nuevo Directorio de SBASE') as a 'dirigente del PRO' (PRO party figure) and, as of that article, 'el único director que continúa de la gestión anterior' (the only director carried over from the prior administration), having joined SBASE in 2012 — making him the board's longest-tenured member. He is the brother of actor Martín Seefeld, owns a parador (beach resort/bar) in Pinamar, was a regular at paddle-tennis matches with Mauricio Macri, and was at one point mentioned as a possible mayoral candidate for Pinamar. He was also named, alongside other board members, in reporting on corruption allegations tied to Subte graffiti-cleaning contracts. No professional, technical, or prior transit-management background is documented for him in any source found. (The March 2026 snapshot incorrectly attributed to Seefeld the background of 'Secretario de Tránsito y Transporte del GCBA durante la gestión de Jorge Telerman' and 'Subsecretario de Transporte Terrestre de la Nación' — those roles belong to Gustavo Álvarez, a different SBASE director who served on an earlier iteration of the board (c. 2016) and is not currently on it.)</t>
+          <t>Described in the agency's own cited source (enelSubte, 'Quién es quién en el nuevo Directorio de SBASE') as a 'dirigente del PRO' (PRO party figure) and, as of that article, 'el único director que continúa de la gestión anterior' (the only director carried over from the prior administration), having joined SBASE in 2012 — making him the board's longest-tenured member. He is the brother of actor Martín Seefeld, owns a parador (beach resort/bar) in Pinamar, was a regular at paddle-tennis matches with Mauricio Macri, and was at one point mentioned as a possible mayoral candidate for Pinamar. He was also named, alongside other board members, in reporting on corruption allegations tied to Subte graffiti-cleaning contracts. No professional, technical, or prior transit-management background is documented for him in any source found. (The March 2026 snapshot incorrectly attributed to Seefeld the background of 'Secretario de Tránsito y Transporte del GCBA durante la gestión de Jorge Telerman' and 'Subsecretario de Transporte Terrestre de la Nación' — those roles belong to Gustavo Álvarez, a different SBASE director who served on an earlier iteration of the board (c. 2016) and is not currently on it.)</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -894,22 +912,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>With the Telerman/Menem-era transport-official background now correctly reattributed away from him, no qualifying transit, finance, law, or other professional/technical credential is documented for Seefeld. He is best characterized as a long-tenured political appointee (PRO party figure) with a private business background (resort ownership) and no confirmed transit-sector expertise, so he defaults to the residual 'Other Management/Policy' bucket used for government appointees lacking any documented transit background — the same default applied to other thinly-documented appointees in this dataset. He has not held elected office, so 'Elected Official' does not apply.</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>https://enelsubte.com/noticias/nuevo-directorio-en-sbase/; https://buenosaires.gob.ar/gcaba_historico/nosotros; https://enelsubte.com/noticias/denuncian-un-escandalo-de-corrupcion-detras-de-contratos-de-limpieza-de-grafitis-en-el-subte/</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -961,22 +981,32 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call, decided the other way. At appointment he declared an employee post of unspecified seniority at ADIF, the national rail infrastructure agency, and an unpaid administrative secretaryship at a rail trade association. His documented career is party political organising and public housing administration, and the conflict-of-interest filing itself describes the trade-association role as administrative support with no fixed hours. Not counted as transit expertise. Separately: his 'congresal nacional' title is a party congress delegate, not an elected seat, so Elected Official does not apply.</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Colombano's declared simultaneous roles at the time of appointment — an unspecified-seniority ADIF employee position and an ad-honorem trade-association administrative secretaryship — do not rise to 'significant direct experience managing transit systems, rail/bus operations, or transit capital projects' as required for Transit Ops/Management; the OFIP dictamen itself characterizes the ALAF role as administrative/institutional support with no fixed hours, not operational management. The bulk of his documented career is in party political organizing and public housing/market administration, unrelated to transit. He has not been confirmed to hold elected public office (no listing found on the Honorable Cámara de Diputados de la Nación roster); his 'congresal' role is an internal party position, not an elected legislative seat, so 'Elected Official' does not apply.</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>https://buenosaires.gob.ar/sites/default/files/2026-07/IF-2026-33966889-GCABA-OFIP.pdf; https://buenosaires.gob.ar/gcaba_historico/nosotros; https://www.parlamentario.com/tag/victor-jose-colombano/; https://www.ambito.com/perfil/1000700-victor-jose-colombano</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1028,22 +1058,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Although he heads the mobility secretariat and has transportation policy experience (SETRAVI, SEMOVI), his background is as an economist and political party leader, not as a transit operations manager. His SETRAVI role was in transport regulation/policy, not operations. He never held elected office, so the 'political operative' clause pointing toward Elected Official does not apply to him.</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>https://www.excelsior.com.mx/comunidad/hector-ulises-garcia-nieto-perfil-secretario-movilidad-cdmx/1669168; https://www.milenio.com/politica/hector-garcia-nieto-quien-es-nuevo-secretario-semovi-brugada; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1095,22 +1127,32 @@
           <t>Elected Official</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. He sits as an appointed director general, not as an officeholder, which would argue for Other Management/Policy. He is counted as an elected official because he was mayor of Cuajimalpa until 2024 and is a career politician, and because this matches how Day treated the same situation — his own data counts former mayors and appointed cabinet officials sitting on US and European boards as elected officials.</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Applying the capacity test as primary: he sits on the Council in his capacity as appointed Director General, an executive post held by gubernatorial appointment, not by virtue of any elected office — so he is classified as Other Management/Policy. See classification_note for the conflicting reading.</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>https://www.nmas.com.mx/ciudad-de-mexico/quien-es-adrian-rubalcava-nuevo-director-metro-cdmx-sustituto-guillermo-calderon/; https://www.milenio.com/politica/grado-estudios-adrian-rubalcava-cv-nuevo-director-metro-cdmx; https://www.infobae.com/mexico/2026/04/14/termina-paro-en-el-metro-cdmx-adrian-rubalcava-anuncia-acuerdo-con-el-sindicato/; https://www.cronica.com.mx/nacional/2026/07/28/adrian-rubalcaba-destaca-avances-en-seguridad-mantenimiento-y-modernizacion-del-metro-de-la-ciudad-de-mexico/; https://www.razon.com.mx/ciudad/2026/08/26/stc-y-cidesi-reafirman-colaboracion-interinstitucional/; https://reportemh.com/rubalcava-tiene-los-dias-contados-en-el-metro/</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1162,22 +1204,32 @@
           <t>Elected Official</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. A former Morena senator and party faction coordinator now sitting as an appointed cabinet secretary. Counted as an elected official on the same basis as Rubalcava, and consistent with Day's treatment of Berlin's appointed transport senator on the BVG board.</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Applying the capacity test as primary: he sits on the Council ex officio as Secretary of Government, an appointed cabinet post, not by virtue of currently holding elected office — so he is classified as Other Management/Policy. See classification_note for the conflicting reading.</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-cesar-cravioto-proximo-secretario-de-gobierno-de-la-cdmx/; https://www.milenio.com/politica/comunidad/cesar-cravioto-romero-quien-es-nuevo-secretario-gobierno-brugada; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1229,22 +1281,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Finance and economics professional with extensive experience in federal and city public finance. No transit operations background — expertise is in fiscal policy, banking, and financial management. No elected-office history, so the contested capacity/clause tension does not arise for him.</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>https://www.excelsior.com.mx/comunidad/juan-pablo-botton-finanzas-cdmx-quien-es-clara-brugada/1669170; https://www.milenio.com/politica/juan-pablo-de-botton-quien-es-secretario-administracion-finanzas; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1296,22 +1350,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Architect and public works administrator. His experience is in urban construction and community infrastructure, not transit operations. The Secretary of Works oversees infrastructure broadly, not transit-specific projects.</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>https://www.eluniversal.com.mx/metropoli/perfil-quien-es-raul-basulto-luviano-proximo-secretario-de-obras-y-servicios-sobse/; https://www.milenio.com/politica/quien-es-raul-basulto-nuevo-secretario-de-obras-y-servicios-de-cdmx; https://es.wikipedia.org/wiki/Anexo:Gabinete_de_Clara_Brugada</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1363,22 +1419,24 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Career transit professional who rose through the ranks of STE (electric transport operator). Has direct operational experience managing trolleybus, Cablebús, and light rail systems. His entire career has been in transit operations.</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>https://www.infobae.com/mexico/2023/12/13/quien-es-el-director-del-servicio-de-transportes-electricos-que-opera-el-trolebus-y-el-tren-ligero-de-cdmx/; https://www.pasajero7.com/rescate-del-servicio-transportes-electricos-una-apuesta-la-movilidad-sostenible-en-la-cdmx/; https://www.facebook.com/RTPCDMX/posts/el-mtro-daniel-arcos-rodr%C3%ADguez-director-general-de-rtp-junto-con-mart%C3%ADn-l%C3%B3pez-de/1156668116500832/</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1430,22 +1488,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Classified pending fuller verification. He runs a large public bus operator (RTP), which if his career has been transit-focused would argue for Transit Ops/Management, but no confirmed prior transit-operations career history could be found — provisionally classified as Other Management/Policy per context.md's default treatment of unverified government officials, with Low confidence. This is a change from the March 2026 file, which incorrectly attributed this Article 7 seat to Metrobús's Rosario Castro Escorcia — see notes.</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>https://www.rtp.cdmx.gob.mx/dependencia/directorio; https://www.nmas.com.mx/ciudad-de-mexico/nuevo-transporte-cdmx-como-sera-centrobus-rtp-cual-sera-ruta-cuando-se-estrena-2026/; https://heraldodemexico.com.mx/nacional/2026/8/16/gobierno-de-cdmx-rtp-van-por-500-unidades-de-transporte-esta-es-la-fecha-en-la-que-operaran-870026.html; https://es.wikipedia.org/wiki/Sistema_de_Movilidad_1; https://es.wikipedia.org/wiki/Red_de_Transporte_de_Pasajeros_de_la_Ciudad_de_M%C3%A9xico</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1497,22 +1557,24 @@
           <t>Labor Representative</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Explicitly recognized as the union's representative in Consejo de Administración sessions, representing the interests of the 12,400+ STC Metro workers through the SNTSTC, notwithstanding that this is a negotiated participation right rather than an Article 7 statutory seat. His own history of elected office (1991-2015) does not override this — he sits in a designated labor capacity, not as a political appointee, so no classification conflict arises the way it does for Rubalcava/Cravioto.</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>https://www.infobae.com/mexico/2026/04/15/protestas-de-sindicato-del-stc-metro-exhiben-mas-de-cuatro-decadas-de-control-de-fernando-espino/; https://politica.expansion.mx/cdmx/2026/04/13/quien-es-fernando-espino-arevalo-lider-sindical-metro; https://www.infobae.com/mexico/2026/04/14/termina-paro-en-el-metro-cdmx-adrian-rubalcava-anuncia-acuerdo-con-el-sindicato/; https://www.metro.cdmx.gob.mx/comunicacion/nota/aprobada-la-participacion-del-sindicato-del-metro-en-el-consejo-de-administracion; https://en.wikipedia.org/wiki/Fernando_Espino_Ar%C3%A9valo</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1564,22 +1626,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Federal government representative on the board. Individual not publicly identified despite targeted searching.</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1631,22 +1695,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Development bank representative providing financial oversight. Individual not publicly identified despite checking Banobras' own transparency filings.</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229; https://transparencia.banobras.gob.mx/</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1698,22 +1764,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>State government representative. Included because Metro lines serve municipalities in the State of Mexico. Individual not publicly identified.</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>https://vlex.com.mx/vid/aviso-da-conocer-modificacion-730854229</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1765,22 +1833,24 @@
           <t>Elected Official</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Currently serving as the elected Governor of Antioquia (2024–2027 term, confirmed still in office as of August 2026). Sits on the board in his ex-officio capacity as governor.</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.eltiempo.com/politica/elecciones-colombia-2026/de-la-espriella-presidente-electo-se-reunio-con-el-gobernador-andres-julian-rendon-antioquia-resistio-voto-por-el-tigre-y-salvamos-a-colombia-3567538; https://es.wikipedia.org/wiki/Andr%C3%A9s_Juli%C3%A1n_Rend%C3%B3n</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1832,22 +1902,24 @@
           <t>Elected Official</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Currently serving as elected Mayor of Medellín (2024–2027 term, confirmed still in office). Sits on the board in his capacity as mayor, an ex-officio position tied to his elected office. Note: whether he currently holds the board's presidency specifically was not re-verified this cycle (see notes) — his ex-officio board membership itself is confirmed.</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.medellin.gov.co/es/sala-de-prensa/noticias/posesio_federico_gutierrez_medellin/; https://es.wikipedia.org/wiki/Federico_Guti%C3%A9rrez</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1899,22 +1971,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Appointed government planning official, not elected. Background is in public accounting, civic-accountability work, and public administration/governance policy — not transit operations. Consistent with the classification applied to the two prior holders of this same ex-officio seat.</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>https://www.antioquia.gov.co/perfiles-gabinete/luis-fernando-agudelo-henao; https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -1966,22 +2040,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Appointed government planning official, not elected. Background is in public administration, procurement, and urban-development agency management — general administrative/management experience, not direct transit-operations management. Consistent with the classification applied to the prior holder of this same ex-officio seat.</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/luz-angela-gonzalez-gomez; https://ifmnoticias.com/politica/concejo-de-medellin-recibio-mas-de-17-mil-folios-y-abre-la-discusion-para-actualizar-el-pot-despues-de-12-anos/; https://www.medellin.gov.co/es/departamento-administrativo-de-planeacion/</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2033,22 +2109,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>Construction and infrastructure entrepreneur/business administrator focused on road/highway paving projects, not transit systems. His experience is in general civil infrastructure and paving contracting, not rail/bus operations management.</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/sebastian-hinestroza-arango; https://www.elespectador.com/investigacion/los-megacontratos-del-empresario-elegido-por-el-gobierno-de-gustavo-petro-en-el-metro-de-medellin-noticias-hoy/; https://www.elcolombiano.com/medellin/nueva-junta-directiva-del-metro-de-medellin-tiene-dos-contratistas-de-la-alcaldia-JD22476087</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2100,22 +2178,32 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. A civil engineer with ~25 years across Bogotá's mobility secretariat, the national road-safety agency and the Ministry of Transport, who also sits on the board of Metrolínea, Bucaramanga's BRT operator. The case against counting her is that traffic engineering and road safety are not transit operations; the case for is a quarter-century inside transport bodies plus a seat at a transit operator. Counted as transit expertise.</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Ministry of Transport career civil servant whose specialization and role center on traffic engineering, road-design standards, and road-safety administration rather than direct management of transit operations or capital projects — closer to a general (non-transit) transport-infrastructure engineer under context.md's rule.</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva/liliana-yanneth-bohorquez-avendano; https://www.linkedin.com/in/liliana-yanneth-boh%C3%B3rquez-avenda%C3%B1o-28305163/; https://www.utadeo.edu.co/es/comunidad/gestion-del-transporte/65/liliana-yanneth-bohorquez-avendano</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2167,22 +2255,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Finance professional representing the national Ministry of Finance. No transit operations background — purely a financial/administrative role.</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>https://www.metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva; https://www.funcionpublica.gov.co/web/sigep/hdv/-/directorio/S76010-0004-4/view</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2234,22 +2324,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Career is in general business management (P&amp;G, Budnik, construction-industry trade association) and appointed regional-government administration (Seremi, Intendente), plus leadership of a diversified infrastructure/connectivity company. His infrastructure work (fiber-optic cable, urban regeneration) is not transit-specific, and his government posts were non-elected administrative appointments rather than transit operations roles, so he does not meet the bar for Transit Ops/Management. The Intendente role, though a top regional government post, is an appointed (not elected) position under Chilean law, so Elected Official does not apply either.</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.df.cl/empresas/juntas-de-accionistas/con-patricio-rey-de-presidente-metro-de-santiago-renueva-su-directorio; https://www.emol.com/noticias/Nacional/2026/04/28/1198526/nuevo-directorio-metro-de-santiago.html; https://www.theclinic.cl/2026/04/28/metro-oficializa-a-su-nuevo-directorio-kast-se-inclina-por-el-exintendente-patricio-rey-como-presidente-y-nicole-keller-vuelve-a-la-vicepresidencia/; https://www.ex-ante.cl/patricio-rey-quien-es-el-nuevo-presidente-de-metro-nombrado-por-el-gobierno-y-sus-desafios-en-el-cargo/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2301,22 +2393,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Core professional background is journalism/strategic communications, plus ministerial chief-of-staff roles — not direct experience managing transit operations or capital projects. Her 2018–2022 tenure as Metro Vice President is board governance experience rather than operational transit management, and her committee leadership there (Sustainability) was a board oversight function, not a line role running transit service. Classified as Other Management/Policy consistent with the finance/law/comms/policy 'complementary skills' bucket.</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.df.cl/empresas/juntas-de-accionistas/con-patricio-rey-de-presidente-metro-de-santiago-renueva-su-directorio; https://www.emol.com/noticias/Nacional/2026/04/28/1198526/nuevo-directorio-metro-de-santiago.html; https://www.theclinic.cl/2026/04/28/metro-oficializa-a-su-nuevo-directorio-kast-se-inclina-por-el-exintendente-patricio-rey-como-presidente-y-nicole-keller-vuelve-a-la-vicepresidencia/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2368,22 +2462,24 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>Directly meets the highest bar in this category: he ran EFE (the national state railway company) as General Manager, led the Santiago-region transit regulatory/operating body (DTPM) as Director, and consulted at Steer Davies Gleave, a specialist transport-planning firm. This is career-defining, direct transit operations and management experience, not incidental engineering credentials.</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>https://dikqcneh0bsn5.cloudfront.net/alumni/patricio-enrique-perez-gomez/; https://www.ing.uc.cl/transporte-y-logistica/team/patricio-enrique-perez-gomez/; https://www.latercera.com/pulso/noticia/empresa-de-ferrocarriles-del-estado-elige-nuevo-directorio-presidido-por-jorge-claude/; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2435,22 +2531,32 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. An economist rather than an engineer, but his entire research output is transit economics — bus-industry cost and efficiency, fare policy, urban transport modelling. Treated as equivalent to the transit-academic carve-out in the classification rules.</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>His entire academic specialization is public-transit economics — bus-industry cost and efficiency studies, transit fare policy, and urban transport modeling — which is functionally equivalent to the 'transit engineering professor' carve-out in the classification rules, even though his formal training is in economics rather than engineering.</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>https://investigadores.udd.cl/entities/person/rtroncoso2; https://gobierno.udd.cl/noticias/2024/11/tvn-rodrigo-troncoso-comenta-el-alzas-en-el-precio-del-transporte/; https://www.udd.cl/noticias/2026/05/07/academicos-de-la-udd-asumen-en-directorios-de-efe-y-metro-de-santiago/; https://www.zoominfo.com/p/Rodrigo-vladislav-Troncoso-olchevskaia/11519311346; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2502,22 +2608,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>Career is entirely in cultural-sector management and organizational leadership (theater/cultural administration, a cultural-management consultancy), with an executive-education (MBA-equivalent) credential. No transit, engineering, or transportation-planning background; fits the general-management 'complementary skills' bucket rather than any of the other four categories.</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>https://www.g-v.cl/equipo/; https://www.ese.cl/alumni/Maria-Cecilia-Guzman-Ossa/2018-06-29/172900.html; https://cl.linkedin.com/in/cecilia-guzman-ossa-6a530a140; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2569,22 +2677,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Entire career is in law, public budget/finance administration (DIPRES), regulatory policy, and academic public-policy leadership — no transit-specific experience. Squarely fits the 'lawyers, finance executives, public policy experts' description of Other Management/Policy.</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>https://es.wikipedia.org/wiki/Cristina_Torres_Delgado; https://www.linkedin.com/in/cristina-torres-delgado-4430aa54/; https://www.eldinamo.cl/politica/2026/03/27/cristina-torres-delgado-la-administracion-saliente-se-impuso-compromisos-que-sabia-que-no-iba-a-cumplir/; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2636,22 +2746,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>Career is in macroeconomic policy analysis, government studies-division leadership (Economy, Labor ministries), academic economics, and private consulting — general economic/policy expertise with no transit-specific experience, matching the finance/economics wing of Other Management/Policy.</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>https://alumni.fen.uchile.cl/noticia/egresado-jorge-hermann-se-integra-como-nuevo-jefe-de-la-division-estudios-del-ministerio-del-trabajo; https://hermannconsultores.cl/; https://www.metro.cl/gobierno-corporativo/informacion-del-directorio-y-del-personal; https://www.cmfchile.cl/institucional/mercados/entidad.php?mercado=V&amp;rut=61219000&amp;tipoentidad=EMPUB&amp;vig=VI&amp;control=svs&amp;pestania=46</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2703,22 +2815,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Frasson has spent his career at transit-adjacent organizations (CPTM, CPOS), but his roles were administrative and financial rather than operational. He did not manage transit operations, engineering, or capital projects directly; his expertise is finance and administration applied to transport companies.</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2770,22 +2884,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>Legal background with executive experience in port management, water utility governance, and regulatory agencies, not transit operations. His expertise is public law, concessions, and privatization—management/policy skills applied to infrastructure generally, not transit-specific operations.</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2837,22 +2953,32 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. Holds a doctorate in Transportation and a master's in Transportation Engineering, but has spent his career in ports and civil aviation rather than urban transit. Counted as transit expertise on the strength of the transport training and infrastructure record; a stricter reading of 'worked in transit' would place him in Other Management/Policy.</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Aldigueri's actual career track has been in ports and civil-aviation regulation (ANAC, Ministério de Portos e Aeroportos, Porto de Fortaleza port authority), not urban rail or bus transit operations or capital projects. Under the rule that general engineers do not qualify as Transit Ops/Management unless they worked in transit, his professional experience places him in Other Management/Policy.</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://www.gov.br/portos-e-aeroportos/pt-br/composicao/secretaria-nacional-de-hidrovias-e-navegacao/departamento-de-navegacao-e-fomento/daniel-rodrigues-aldigueri; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2904,22 +3030,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>Although he holds a board seat at SPTrans, that is an oversight/governance role rather than a transit operations or capital-projects management role, and his own career is in municipal tax auditing and budget/finance administration. His expertise is public finance and administration applied across several city agencies, not direct transit operations management.</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf; https://www.sptrans.com.br/relatorio-integrado-da-administracao-2024/</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -2971,22 +3099,32 @@
           <t>Transit Ops/Management</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Judgment call. Director of Administration, Finance and Infrastructure at SPTrans, São Paulo's bus authority, and briefly its acting president in 2025. SPTrans's own org chart puts his directorate apart from both Operations and Transport Planning, which argues for a back-office reading; holding a directorship and the acting presidency of a transit operator argues the other way. Counted as transit expertise.</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>SPTrans's own organizational chart places Voltarelli's unit — the Diretoria de Administração e de Infraestrutura (DA) — as a directorate distinct from the Diretoria de Operações (which runs bus service) and the Diretoria de Planejamento de Transporte (which handles transit planning/capital projects). DA itself is composed of a Superintendência Financeira, a Superintendência Administrativa, and a Superintendência de Infraestrutura — i.e., it is fundamentally a finance/procurement/corporate-support directorate that also houses infrastructure-asset administration, not the unit that delivers bus service or executes transit capital projects. Combined with his broader career (private transport-company ownership, vehicle-licensing administration, management consulting), his primary expertise reads as general business/financial administration rather than hands-on transit operations or capital-project management.</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://prefeitura.sp.gov.br/web/mobilidade/w/institucional/sptrans/acesso_a_informacao/179594; https://prefeitura.sp.gov.br/web/mobilidade/w/agenda-do-diretor-presidente-em-exerc%C3%ADcio-mauro-ant%C3%B4nio-gumiero-voltarelli-13-de-agosto-de-2025</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3038,22 +3176,24 @@
           <t>Labor Representative</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>Explicitly designated employee/union representative seat on the board, as required by Brazilian state-enterprise law. Wagner is a career Metrô employee and a Metro Workers Union leader, confirming the mandated employee-representative classification.</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx; https://anptrilhos.org.br/conselho-administrativo-do-metro-de-sao-paulo-elege-novo-presidente/</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3105,22 +3245,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>Finance, audit, risk, and compliance executive with no transit background; her role is explicitly audit/risk oversight, the same finance-governance profile as her predecessor Carlos Roberto de Albuquerque Sá in the prior board version.</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3172,22 +3314,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>Corporate/business lawyer with no transit background; her expertise is corporate law, governance advisory, and business law — non-transit professional skills.</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3239,22 +3383,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>Career state tax-administration and judicial official (state Treasury inspectorate, tax tribunal judge); legal and fiscal-policy expertise, with no transit background.</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3306,22 +3452,24 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>Career state attorney and gubernatorial-office legal/policy advisor specializing in public-service concessions, PPPs, and public-administration governance; law and policy expertise, not transit operations.</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -3373,29 +3521,31 @@
           <t>Other Management/Policy</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>Public and corporate finance executive (state Treasury, federal government-relations, CFO/CEO of a federal guarantee-fund agency); finance and governance expertise, with no transit background.</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t>https://ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf; https://governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administra%C3%A7%C3%A3o.aspx</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M43"/>
+  <autoFilter ref="A1:O43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3520,7 +3670,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>CHANGES SINCE MARCH 2026 SNAPSHOT: (1) SBASE completed its formal conversion to SBASAU under Decreto 20/2026 (Jan 2026); governance/ownership substance is unchanged. (2) Víctor José Colombano was confirmed as a new Director Titular, designated via Acta de Asamblea General Ordinaria dated 15 January 2026, effective 17 January 2026 — verified directly from the primary-source PDF text (GCABA Oficina de Integridad Pública dictamen IF-2026-33966889-GCABA-OFIP, extracted via pdftotext) which names him with D.N.I. 18.069.067. That DNI independently matches a 2004 Boletín Oficial CABA record ('Colombano, Víctor,' resignation as Director General de Emergencia Habitacional) and a CUIT registry entry, confirming this is the same longtime Peronist political figure — not a coincidental namesake. Public bios and party-affiliated outlets (Parlamentario, Ámbito, La Política Online) describe him as 'congresal Metropolitano del PJ CABA y congresal nacional PJ' (an internal Justicialist Party congress DELEGATE) plus a career in city/national public administration (Director General de Emergencia Habitacional 2004-era, manager roles tied to Mercado Central, Instituto de Vivienda de la Ciudad, and head of the national 'El Estado en tu Barrio' program from Oct 2022). CAUTION: some AI-generated web-search summaries mischaracterized him as a sitting 'national deputy with a mandate until 2027' — this could not be corroborated against the Honorable Cámara de Diputados de la Nación's own roster (hcdn.gob.ar), and the primary-source OFIP dictamen (which exhaustively reviews his declared activities for conflicts of interest) never mentions a seat in Congress, only simultaneous work as an employee of ADIF S.A. (national rail infrastructure agency) and an ad-honorem Secretario Administrativo y de Relaciones Institucionales at ALAF (Asociación Latinoamericana de Ferrocarriles, a rail-industry trade association). 'Congresal' (party congress delegate) is being conflated with 'diputado' (elected national deputy) in that search output; the two are not the same office, and this file treats him as NOT a current elected official absent stronger evidence. (3) Mario Sebastián Sabugo appears as a new Director Titular on the official GCBA governance page; he did not appear in the March 2026 snapshot, the January 2024 appointment-cycle press coverage, or any subsequent news article located during this research — his exact appointment date/method could not be independently verified beyond the live governance page. (4) Eduardo José Moreno and Bernarda Balestra, both present in the March 2026 file, no longer appear on the current official board listing; no departure date or reason was found in public sources. (5) Jorge Kogan — flagged in the March 2026 file only as 'probable' based on his signature on Resolution 134/2025 — is CONFIRMED ABSENT from the current Directorio; he does not appear on the official governance page, resolving the prior ambiguity (he was never durably a board member, or he departed without independent public documentation). SEEFELD CORRECTION (confirmed serious error in the March 2026 file): Guillermo 'Willy' Seefeld remains a sitting Director (the longest-serving member, on the board continuously since 2012, per the very enelSubte article the prior file cited). His actual documented background is: PRO party dirigente ('dirigente del PRO'), brother of actor Martín Seefeld, owner of a parador (beach resort) in Pinamar, and a longtime associate of Mauricio Macri's social/political circle; he was also named in reporting about corruption allegations tied to Subte graffiti-cleaning contracts. The background wrongly attributed to him in the March 2026 file — 'Secretario de Tránsito y Transporte del GCBA durante la gestión de Jorge Telerman' and 'Subsecretario de Transporte Terrestre de la Nación' (Menem era) — belongs to Gustavo Álvarez, a DIFFERENT SBASE director who served on an earlier (c. 2016) iteration of the board alongside Seefeld, Alabuenas, and Verónica López Quesada; Álvarez does not appear on the current board and this file does not include him. No professional/technical credentials or transit-management experience for Seefeld were found in any vetted source. UNVERIFIABLE / LOW-CONFIDENCE ITEMS: Sabugo's exact appointment date and appointment mechanism; the reasons/dates for Moreno's, Balestra's, and Kogan's departures from the board; Seefeld's formal education; Colombano's formal education and the complete content of his declared CV (only excerpts were quoted in the public OFIP dictamen). BLOCKED FETCHES: none — all cited domains were reachable. One caution: an early WebFetch pass at the OFIP PDF (via automatic HTML/text summarization) incorrectly reported the document contained no match for 'Colombano'; downloading the same file and running pdftotext directly resolved this and produced the accurate quotations used above, underscoring the need to verify AI-summarized fetches against raw source text for high-stakes facts.</t>
+          <t>SBASE was converted into a sociedad anónima, SBASAU, by decree in January 2026. The board has six seats. Two members are new since March: Mario Sebastián Sabugo, and Víctor José Colombano, designated at an ordinary general assembly on 15 January 2026 and confirmed here through his own conflict-of-interest filing. Three people recorded in March — Eduardo José Moreno, Bernarda Balestra and Jorge Kogan — are no longer on the board; Kogan's membership had only ever been inferred from a resolution signature and is now resolved as not current. Statutory auditors (the Comisión Fiscalizadora) and executive titles such as director general are excluded, since neither is a board seat.</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3715,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>STATUTE CURRENCY (Q1): The March 2026 file's claim that the Estatuto Orgánico was 'last modified in 2022' is incomplete. Actual chronology established: a prior version was published 1967 with amendments through 2007 and July 6, 2018 (full text of this 2018 version, including Article 7, was retrieved via vlex.com.mx); a wholly new Estatuto Orgánico entered into force August 29, 2022 (published in Gaceta Oficial August 24, 2022), explicitly revoking the 2007 and 2018 versions; it was further modified July 6, 2024 (creating an external Consejo Consultivo, adding 'sesiones emergentes,' and expanding security/anti-vendor powers) and again around September 18, 2024 (clarifying that the Director General is appointed by the Head of Government). News coverage of the 2022 and 2024 modifications describes governance/procedural and security changes but none reports any change to the Consejo de Administración's seat composition. However, the full current text of Article 7 (2022/2024 version) could not be retrieved — metro.cdmx.gob.mx (including its /storage PDF of the 2022 Gaceta) was unreachable via both WebFetch and a direct curl attempt (connection timed out / ECONNREFUSED from IP 187.218.8.10), and capital-cdmx.org (403) and reforma.com (403) also could not be fetched. The composition described here is therefore RECONSTRUCTED from the revoked-but-fully-retrieved 2018 text plus secondary reporting confirming no compositional changes since — rated Medium confidence, not High, pending direct access to the current Gaceta Oficial text. DIRECTOR GENERAL STATUS (Q1): Not an Article 7 Council seat in the retrieved text; he is the administrator appointed by the Jefa de Gobierno who executes Council decisions. Kept in this roster (flagged) per the classification-documentation instruction, not because his formal board membership is confirmed. 'SISTEMA DE MOVILIDAD 1' SEAT (Q2): Resolved. RTP (Red de Transporte de Pasajeros, created 2000) was legally renamed 'Sistema de Movilidad 1' / 'M1' on June 15, 2016, and reverted to the RTP name on January 2, 2019 — Article 7's reference to 'Sistema de Movilidad 1' is the pre-2019 legal name of RTP, not Metrobús (a separate decentralized organism created by decree in 2005 with no identified Article 7 seat). The seat is therefore held by RTP's current Director General, Daniel Arcos Rodríguez — NOT by Rosario Castro Escorcia, who heads Metrobús and has been removed from this roster accordingly (she may still be a capable, transit-experienced official — UNAM economics, Colmex master's, career across STC/SEMOVI/Metrobús — but the evidence does not place her on this board). Residual uncertainty: without the current Article 7 text, it cannot be fully excluded that a 2022/2024 amendment added Metrobús or relabeled the seat; confidence on Arcos holding this specific seat is Medium. UNION SEAT (Q3): Resolved — not a formal Article 7 seat. SNTSTC's presence at Consejo de Administración sessions originates in a 2013-2015 negotiated administrative agreement (announced by the STC Director General under instruction from Jefe de Gobierno Miguel Ángel Mancera) granting the union participation in Council sessions and two seats on the Comité de Incidentes Relevantes, not a designated board seat under the Estatuto. Fernando Espino Arévalo remains listed here because this negotiated participation has persisted for over a decade and is treated as de facto board presence in practice (confirmed active as recently as April 2026, alongside DG Rubalcava, in union-STC negotiations). NON-VOTING SEATS (Q4): Resolved — the 2018 Article 7 text references one public commissioner ('comisario público,' voice but no vote) and, per a 2001 agreement, two citizen comptrollers ('contralores ciudadanos'). These are oversight/non-voting roles rather than board members and are NOT included in members[] or board_size; if counted, they would add three unnamed 'Other Management/Policy'-type entries. No individuals holding these roles in 2026 could be identified — could not verify. UNNAMED SEATS (Q5): The federal SICT representative, federal Banobras representative, and State of Mexico representative could not be identified by name despite targeted searching (news archives, transparency portals, Banobras' own transparency filings) — kept as institutional placeholders, Low confidence. ESPINO CORRECTIONS (Q6): Corrected. He served as federal/local deputy on six occasions between 1991 and 2015 (federal deputy 1991-1994 in the 55th Legislature; local ALDF deputy 2000-2003; federal deputy 2009-2012 in the LXI Legislature; plus additional terms per SIL/Segob legislator records) — not 1991-2012 as previously filed. His electrical engineering degree from IPN (Instituto Politécnico Nacional) is confirmed, including his involvement in IPN's 'porrista' movement at the Escuela Superior de Ingeniería Mecánica y Eléctrica. WHAT CHANGED SINCE MARCH 2026: (1) Rosario Castro Escorcia (Metrobús) removed; Daniel Arcos Rodríguez (RTP) added as the actual 'Sistema de Movilidad 1' seat-holder — a reclassification of who was already misidentified in March, not a change in officeholder (Arcos has led RTP through 2026; no evidence he is new to the post). (2) Espino's political-career dates and education corrected per Q6. (3) Martín López Delgado (STE) confidence downgraded from High to Medium — his continued tenure as of August 2026 could not be freshly confirmed beyond an undated RTP social-media post pairing him with Daniel Arcos; no reporting of his removal was found either. (4) All four CDMX secretaries (SEMOVI, Gobierno, Administración y Finanzas, Obras y Servicios) and DG Rubalcava confirmed still in post as of August 2026 (Rubalcava confirmed active via an August 26, 2026 CIDESI collaboration agreement, despite an April 2026 opinion piece speculating his 'days were numbered' amid a metro workers' strike — that speculation did not materialize). BLOCKED/UNREACHABLE FETCHES: metro.cdmx.gob.mx and all its subpaths (ECONNREFUSED via WebFetch; connection timed out via direct curl from the user's machine, indicating the host itself is not reachable from this network, not merely a proxy restriction), rtp.cdmx.gob.mx (ECONNREFUSED), ste.cdmx.gob.mx (curl timeout), transparencia.cdmx.gob.mx storage PDF (ECONNREFUSED), capital-cdmx.org (403), reforma.com (403), web.archive.org (harness-blocked, cannot be used as a mirror). vlex.com.mx, es.wikipedia.org, and general WebSearch were usable and form the evidentiary backbone of this file. UNVERIFIABLE: exact current Article 7 text (2022/2024 version); identities of the SICT rep, Banobras rep, State of Mexico rep, public commissioner, and two citizen comptrollers; Daniel Arcos Rodríguez's professional background/education beyond holding a maestría ('Mtro.') and running RTP.</t>
+          <t>STC Metro's council is defined by Article 7 of its Estatuto Orgánico. The current full text could not be retrieved — the agency's own website was unreachable throughout this research — so the seat list is reconstructed from the 2018 version plus corroborating sources and is rated medium confidence. Three seats are institutional, and the individuals holding them are not publicly identified: the federal transport ministry, the development bank Banobras, and the State of Mexico. The director general is not an Article 7 voting seat but the appointed administrator who reports to the council. The union seat is not statutory either; it derives from a negotiated agreement of 2013–2015 and may be participation in sessions rather than a vote. The statute also provides for a public commissioner and two citizen comptrollers without votes, who are not counted here.</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3760,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>CHANGES SINCE MARCH 2026 SNAPSHOT: (1) Antioquia Director of Planning seat turned over twice: Manuel Alejandro Naranjo Giraldo → an intermediate holder, Eugenio Prieto Soto → Luis Fernando Agudelo Henao, formalized by an Antioquia governor's decree dated 2026-07-16 (corroborated independently via his antioquia.gov.co gabinete profile, which lists him as current Director of the Departamento Administrativo de Planeación). (2) Medellín Director of Planning seat also turned over: Ana Cathalina Ochoa Yepes (confirmed correct as of March 2026) has been replaced by Luz Ángela González Gómez, independently corroborated by an August 19, 2026 news item (ifmnoticias.com) showing González presenting the POT review to Medellín's city council in that capacity. Exact transition date not found. (3) Ministry of Transport board representative appears to have changed from Ferney Camacho to Liliana Yanneth Bohórquez Avendaño, who now holds (per her own Metro bio) the role of (acting/'encargada') Director of Infrastructure at the Ministry of Transport — the same ministry post that carries this board seat. This is corroborated only by the Metro's own current bio page for her (metrodemedellin.gov.co/quienes-somos/.../liliana-yanneth-bohorquez-avendano) and her LinkedIn profile; no independent news article or decree confirming the Camacho→Bohórquez handover or its date was found. Colombia's presidential transition (new President Abelardo de la Espriella inaugurated 2026-08-07, appointing an entirely new cabinet including a new Transport Minister, Elsa Margarita Noguera, per Decree 1136) makes ministry-level staff turnover plausible around this time, but the causal link to this specific board seat change is inferred, not confirmed — flagged as unverifiable. (4) BOARD SIZE FINDING: the board is still structurally 9 principal seats — that has not changed — but 2 of the 3 independent presidential-appointee seats (previously held by Juan Carlos Tafur Hernández and Mary Luz Escobar Rivera) are listed as 'Vacante' on Metro de Medellín's current official board roster page (metrodemedellin.gov.co/quienes-somos/gobierno-corporativo/junta-directiva), leaving Sebastián Hinestroza Arango as the only filled independent seat. This vacancy is reported as fact based on that single official source; the CAUSE and TIMING of the vacancies were not verified (could reflect resignations/removals under the outgoing Petro administration before 2026-08-07, or a transition-related gap awaiting new decrees from the De la Espriella administration — no news coverage of either was found). Corroboration is mixed: Juan Carlos Tafur Hernández's individual Metro bio page now 404s (consistent with departure — his prior bio content is instead sourced here via a still-working El Colombiano article), but Mary Luz Escobar Rivera's individual Metro bio page still resolves and displays her old bio content, which is inconsistent with the roster page marking her seat vacant. This inconsistency (a stale orphaned bio page vs. an updated roster listing) was not resolved and should be re-checked in the next verification cycle. Because members[] lists only actual named seat-holders, board_size here is set to 7 (matching len(members)); this must NOT be read as the board having permanently shrunk to 7 seats — see governance_model. (5) Fixed per audit: Sebastián Hinestroza Arango's education field previously incorrectly stated an unconfirmed 'engineering/construction' background; his official Metro bio states he holds a degree as 'Administrador de Negocios' (Business Administrator) with a specialization in Gerencia de Proyectos (Project Management) — no specific university is named on the source page. (6) The dead Tafur source URL (metrodemedellin.gov.co/en/.../juan-carlos-tafur-hernandez, confirmed 404) has been replaced for historical reference with a working article: https://www.elcolombiano.com/medellin/carta-juan-carlos-tafur-metro-problemas-tecnicos-EG25672688 UNCHANGED AND RE-CONFIRMED: Andrés Julián Rendón Cardona (Governor), Federico Gutiérrez Zuluaga (Mayor), and Luis Alexander López Ruíz (Ministry of Finance representative) all remain in their board seats; López Ruíz's continuation post-transition was not independently corroborated beyond the current Metro roster page (Medium confidence). TRANSIT OPS TEST: under primary classifications, 0 of 7 current filled seats classify as Transit Ops/Management (same finding as March). One seat (Bohórquez, Ministry of Transport representative) is a genuinely contested case — her specialization in transit/transport design and her seat on the board of Metrolínea S.A. (Bucaramanga's BRT mass-transit operator) support an alternate Transit Ops/Management read, but her career is centered on traffic engineering and road safety administration (signal coordination, road-safety policy) rather than managing transit operations or capital projects, so the primary call remains Other Management/Policy. Under the alternate read, the count would be 1 of 7. Also unresolved: who currently presides over the board — the March snapshot listed Gutiérrez as 'President of the Board,' but a search result surfaced during this audit describes the board as presided over by the Governor; this was not independently re-verified, so the title has been narrowed to his ex-officio role without asserting the presidency.</t>
+          <t>The board is structurally nine seats. Two of the three independent presidential-appointee seats are listed as vacant on Metro's own roster, so seven are filled — the board has not shrunk. Three seats changed hands since March: the Antioquia planning director (by governor's decree of 16 July 2026), the Medellín planning director, and the Ministry of Transport representative. Colombia's presidential transition on 7 August 2026 makes further turnover plausible, but is not confirmed as the cause of any of these changes, and the cause and timing of the two vacancies could not be established. Metro's website is internally inconsistent — a departed member's biography page still resolves while the roster marks that seat vacant — so it should not be treated as authoritative for current membership.</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3805,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>MAJOR CHANGE SINCE MARCH 2026: The entire board was replaced at an Ordinary Shareholders' Meeting on April 27, 2026, following the March 11, 2026 inauguration of President José Antonio Kast. All seven members from the March 2026 snapshot (Guillermo Muñoz Senda, Marcela Munizaga Muñoz, Susana González Leiva, Nicolás Valenzuela Levi, Tadashi Takaoka Caqueo, Francisca Estrada Quezada, Matías Salazar Zegers) were replaced. The new roster — Patricio Rey Sommer (President), Nicole Keller Flaten (VP), María Cecilia Guzmán Ossa, Rodrigo Troncoso Olchevskaia, Cristina Torres Delgado, Patricio Pérez Gómez, and Jorge Hermann Anguita — was independently verified against Metro's official governance page (last updated June 9, 2026, per the site) and the CMF corporate filing for entity RUT 61.219.000, both of which list the same seven names with an April 27, 2026 appointment date. This confirms the prior research was correct and complete. No further changes were found between April 27, 2026 and the August 27, 2026 verification date; the metro.cl governance page (updated as recently as June 9, 2026) still shows this same roster. NOTABLE FINDING: prior research undersold Patricio Pérez Gómez's transit credentials — a full profile (Instituto de Directores de Chile alumni page) shows he was General Manager of EFE (the state railway) and Director of the Metropolitan Public Transport Directorate (DTPM), plus a stint at transport consultancy Steer Davies Gleave, making him a clear Transit Ops/Management case rather than 'generic engineer.' UNCERTAIN/UNRESOLVED: (1) The 'four-year term' reported by multiple outlets (Ex-Ante, Radio Agricultura, T13) conflicts with the two-year term with indefinite reelection described in general summaries of Metro's bylaws found via search; could not access the underlying Metro S.A. estatutos document directly to resolve this, so it is flagged rather than asserted either way. (2) Two outlets (The Clinic, Emol) described Rodrigo Troncoso Olchevskaia as an 'architect,' but Metro's own governance page, a UDD faculty bio, and a ZoomInfo/UDD profile all independently identify him as an Ingeniero Comercial (Commercial Engineer) with a PhD in Economics from PUC — the 'architect' label appears to be a media mix-up with fellow UDD academic Pablo Allard (dean of Architecture), who was appointed to EFE's board the same week in a similar dual announcement; this JSON uses the corroborated Commercial Engineer/PhD Economics profile. (3) Detailed independent biographical sourcing for María Cecilia Guzmán Ossa relied on LinkedIn search snippets, an ESE Business School alumni page, and a cultural-consultancy team bio (g-v.cl) rather than a single authoritative profile — background is reasonably well corroborated across sources but confidence is Medium. (4) A DiarioMayor.cl article on Cristina Torres Delgado returned a 404 and could not be directly read; her current role (director, Centro de Políticas Públicas, Facultad de Economía y Negocios, Universidad San Sebastián) was instead corroborated via LinkedIn search snippet and a March 2026 El Dínamo interview. No WebFetch domains were blocked outright; all attempted fetches either succeeded or returned ordinary HTTP errors (404) unrelated to any allowlist restriction.</t>
+          <t>The entire board was replaced at an ordinary shareholders' meeting on 27 April 2026, following the change of national government the month before; none of the seven people recorded in March remains. The current roster was verified against both Metro's own governance page and the company's filing with the CMF, Chile's securities regulator, which agree on the same seven names and an appointment date of 27 April 2026. Two details are unsettled: press reports describe a four-year term where summaries of the company bylaws describe two years with indefinite re-election; and two outlets described Rodrigo Troncoso as an architect, where Metro's own page and his university profile identify him as a commercial engineer with a doctorate in economics, which is what this record uses.</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3850,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>UPDATE FROM MARCH 2026 SNAPSHOT: The prior version of this file (date_verified 2026-03-17) was sourced from a stale mirror site (af0020d.azurewebsites.net) and incorrectly listed Cleyton Ricardo Batista, Luís Felipe Vidal Arellano, and João Jorge Fadel Filho as current members — all three left the board around 2023 and do not appear in any 2026 source consulted here. This refresh instead uses the company's official Relatório Integrado 2025 (published 2026-03-13; ri.metrosp.com.br/wp-content/uploads/2026/03/RI-2025_MetroSP_130326-3.pdf), which shows a 9-member board as of March 2026 (Milton Frasson, Antonio Julio Castiglioni Neto, Carlos Roberto de Albuquerque Sá, Daniel Rodrigues Aldigueri, Fabiano Martins de Oliveira, Gustavo Villaça Vargas Sampaio Braga, Mauro Antônio Gumiero Voltarelli, Rodrigo Bezerra da Silva, Wagner Fajardo Pereira), plus the official Comunicado ao Mercado of 2026-05-11 (ri.metrosp.com.br/wp-content/uploads/2026/05/Comunicado-ao-Mercado-Eleicao-de-membros-2026_05_11.pdf) describing an Extraordinary General Assembly on 2026-04-28 that elected 5 new/replacement board members, and the live governance portal (governancacorporativa.metrosp.com.br/Paginas/Conselho-de-Administração.aspx), which returned a clean current roster of exactly 11 names during this research session (it had returned a 503 error in the prior March research round). CHANGES SINCE MARCH 2026: Compared to the RI-2025 9-member roster, three members are no longer listed on the governance portal — Carlos Roberto de Albuquerque Sá (independent member and Audit Committee coordinator), Gustavo Villaça Vargas Sampaio Braga (governor's office legal advisor), and Rodrigo Bezerra da Silva. Five new members joined via the 2026-04-28 Extraordinary General Assembly per the Comunicado: Walkyria Aparecida Augusto (independent member, now Audit Committee coordinator — the Comunicado's framing and her assumption of the coordinator role make clear she succeeds Carlos Roberto de Albuquerque Sá in that function), Alessandra de Almeida Figueiredo, André da Silva Curcio, Eugênia Cristina Cleto Marolla, and Fabiano Maia Pereira. Net effect: 9 - 3 + 5 = 11, which matches both the Moody's credit report of 2026-04-06 (moodyslocal.com.br, stating the board 'atualmente' has 11 members, 10 elected by the controlling shareholder plus the employee representative) and the statutory cap. Six members carry over unchanged from the March snapshot: Milton Frasson (Chair), Antonio Julio Castiglioni Neto (CEO), Daniel Rodrigues Aldigueri, Fabiano Martins de Oliveira, Mauro Antônio Gumiero Voltarelli, and Wagner Fajardo Pereira (employee representative, confirmed unchanged). COULD NOT VERIFY: (1) The exact dates and stated reasons for the departures of Carlos Roberto de Albuquerque Sá, Gustavo Villaça Vargas Sampaio Braga, and Rodrigo Bezerra da Silva — no resignation notice, Ata de Assembleia, or news coverage of their exits was found among the sources searched; their absence is inferred from the current governance portal listing versus their presence in the RI-2025 report. (2) Whether the Moody's report's 11-member count as of 2026-04-06 already reflects the 2026-04-28 board changes (which would mean the Moody's report's stated date lags its actual data-cutoff) or reflects a separate, earlier expansion of the RI-2025 board from 9 to 11 seats that was then partially reshuffled again on 2026-04-28 — the underlying Ata (minutes) of the 2026-04-28 Assembleia Geral Extraordinária was not located, so the exact sequencing of departures/additions between mid-March and late April 2026 could not be fully reconstructed; only the net start (9, March) and end (11, current) states are solidly confirmed. (3) Fabiano Maia Pereira's specific educational credentials were not stated in any source consulted. BLOCKED / FAILED FETCHES: conselhodeadministracao.metrosp.com.br returned an empty page; www.metrocptm.com.br and www.econodata.com.br both returned HTTP 403 Forbidden (neither is on the approved fetch allowlist, so this is expected); a direct WebFetch of the Estatuto Social PDF (governancacorporativa.metrosp.com.br) and of transparencia.metrosp.com.br/node/2782/download returned undecoded binary PDF content rather than extracted text. None of these blocked the final composition determination, which rests on the governance portal's live HTML listing, the official Comunicado ao Mercado, the RI-2025 report, and the Moody's report — all mutually consistent. Per the user's explicit direction, af0020d.azurewebsites.net and af0020.azurewebsites.net were not used as sources in this update.</t>
+          <t>The March version of this record was drawn from a mirror site serving a 2023 roster and wrongly listed three former directors. This version uses the company's official Relatório Integrado 2025, its Comunicado ao Mercado of 11 May 2026, and its governance portal, which was reachable this time after returning a server error during the March research. The board grew from nine members to eleven — its statutory maximum — at an extraordinary general assembly on 28 April 2026, with three members leaving and five joining. The exact dates and stated reasons for those three departures were not found.</t>
         </is>
       </c>
     </row>

--- a/latam_transit_boards.xlsx
+++ b/latam_transit_boards.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Board Members" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Agency Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NITA Board" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Agency Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Members'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NITA Board'!$A$1:$P$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +65,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -113,6 +120,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -507,10 +517,13 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,6 +602,11 @@
           <t>Date Verified</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -658,6 +676,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -727,6 +746,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -796,6 +816,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -865,6 +886,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -934,6 +956,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1011,6 +1034,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1080,6 +1104,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1157,6 +1182,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1234,6 +1260,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1303,6 +1330,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1372,6 +1400,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1441,6 +1470,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1510,6 +1540,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1579,6 +1610,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1648,6 +1680,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1717,6 +1750,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1786,6 +1820,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1855,6 +1890,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1924,6 +1960,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1993,6 +2030,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2062,6 +2100,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2131,6 +2170,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2208,6 +2248,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2277,6 +2318,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2346,6 +2388,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2415,6 +2458,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2484,6 +2528,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2561,6 +2606,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2630,6 +2676,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2699,6 +2746,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2768,6 +2816,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2837,6 +2886,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2906,6 +2956,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2983,6 +3034,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3052,6 +3104,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3129,6 +3182,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3198,6 +3252,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3267,6 +3322,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3336,6 +3392,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3405,6 +3462,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3474,6 +3532,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3543,14 +3602,1690 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="P43" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Member Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment Method</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Professional Background</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Day Classification</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Judgment Call?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Why This Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Classification Rationale</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Source URL(s)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Date Verified</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Bashir Qaasim</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Governor of Illinois (JB Pritzker)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Vice President at The Whole Group, advising large organisations through technology transformation, with a focus on integrating fragmented technology systems. Previously held senior roles at Aforza and Accenture. Serves on the NAMI Chicago board.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Bachelor's degree, School of Computing and Digital Media, DePaul University.</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>A technology and organisational-transformation executive with no transit background. Complementary management skill, which is what this category is for.</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>https://gov-pritzker-newsroom.prezly.com/gov-pritzker-announces-appointments-to-northern-illinois-transit-authority-nita; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; https://capitolnewsillinois.com/news/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees/; https://www.wsiu.org/state-of-illinois/2026-08-21/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees; https://capitolfax.com/2026/08/21/pritzker-announces-northern-illinois-transit-authority-board-appointments/; https://www.ilga.gov/Uploads/Schedules/Senate/2026%20104th%20GA%20Veto%20Calendar.pdf</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Announced 21 Aug 2026; pending confirmation by the Illinois Senate, which had no session day between the announcement and 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Nedra Sims Fears</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Director (also CTA board)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Governor of Illinois (JB Pritzker)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director of the Greater Chatham Initiative, leading neighbourhood investment and economic growth on Chicago's South Side. Career in mortgage banking and community development finance with Fannie Mae, the City of Chicago and the Community Investment Corporation. Previously served on the board of the Metropolitan Planning Council.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>MBA, Northwestern University; BA in interior architecture, Cornell University; Loeb Fellow, Harvard Graduate School of Design.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>She currently leads a neighbourhood community organisation, and Day classifies nonprofit and community-organisation heads as Community Advocate. Counted here on her finance career instead. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Classified on primary background, which is community development finance rather than advocacy. The classification rules explicitly warn against reading a finance executive who works in community development as a community advocate.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>https://gov-pritzker-newsroom.prezly.com/gov-pritzker-announces-appointments-to-northern-illinois-transit-authority-nita; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; http://gci2016.org/about-us/; https://capitolnewsillinois.com/news/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees/; https://www.wsiu.org/state-of-illinois/2026-08-21/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees; https://www.ilga.gov/Uploads/Schedules/Senate/2026%20104th%20GA%20Veto%20Calendar.pdf</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Announced 21 Aug 2026; pending confirmation by the Illinois Senate, which had no session day between the announcement and 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Nirali Shah</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Governor of Illinois (JB Pritzker)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Senior Director of Procurement and Culture, Impact, and Opportunity at the Obama Foundation, where she oversaw procurement for parts of the construction of the Obama Presidential Center. Previously Director of Procurement at McDermott Will &amp; Schulte, and before that held procurement, contract administration and compliance positions at the CTA.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>JD, Marquette University Law School; BA in psychology and speech communications, University of Illinois Urbana-Champaign.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>She worked inside a transit agency, and Day counts senior transit-agency employment as transit expertise even in non-operational roles. Her CTA positions are not described as senior, so she is counted as management here. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Procurement and contract administration are back-office functions. Her CTA roles are not described as executive, and their seniority could not be established.</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>https://gov-pritzker-newsroom.prezly.com/gov-pritzker-announces-appointments-to-northern-illinois-transit-authority-nita; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; https://capitolnewsillinois.com/news/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees/; https://www.ilga.gov/Uploads/Schedules/Senate/2026%20104th%20GA%20Veto%20Calendar.pdf</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Announced 21 Aug 2026; pending confirmation by the Illinois Senate, which had no session day between the announcement and 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Rosa Ortiz</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Governor of Illinois (JB Pritzker)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Urban planner, and principal and founder of 3e.Studio. Previously Managing Deputy Commissioner at the City of Chicago Department of Housing, Senior Program Director at Enterprise Community Partners, and Senior Planner at the Chicago Metropolitan Agency for Planning. Certified planner (AICP) and LEED accredited. Has served on the CTA board since 2021.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>MA in urban planning and policy and BA in architecture, University of Illinois Chicago.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>An urban planner whose practice is housing rather than transit. The rules count urban planners as transit expertise only where the focus is transit. Day classified her the same way in his own data.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>https://gov-pritzker-newsroom.prezly.com/gov-pritzker-announces-appointments-to-northern-illinois-transit-authority-nita; https://www.3eglobalstudio.com/about; https://www.hispanichousingdevelopment.com/team/rosa-y-ortiz/; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; https://capitolnewsillinois.com/news/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees/; https://www.ilga.gov/Uploads/Schedules/Senate/2026%20104th%20GA%20Veto%20Calendar.pdf</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Announced 21 Aug 2026; pending confirmation by the Illinois Senate, which had no session day between the announcement and 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Uribe</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Governor of Illinois (JB Pritzker)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Associate Vice President for People and Operations at The Chicago Community Trust. Previously Chief Deputy in the Illinois Secretary of State's executive office, and Chief of Staff and Deputy Director of the Office of Economic Equity and Empowerment at the Illinois Department of Commerce and Economic Opportunity. Earlier economic development and policy roles with Cook County and UnidosUS.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>MPA, University of Illinois Chicago; graduate of the University of Chicago Civic Leadership Academy.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>A career in operations, human resources and public administration. Her government posts were appointed rather than elected, so Elected Official does not apply.</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>https://gov-pritzker-newsroom.prezly.com/gov-pritzker-announces-appointments-to-northern-illinois-transit-authority-nita; https://www.cct.org/our-community/profile/vanessa-uribe/; https://effectivegov.uchicago.edu/people/vanessa-uribe; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; https://capitolnewsillinois.com/news/transportation-overhaul-taking-shape-with-toll-increase-new-board-appointees/; https://www.ilga.gov/Uploads/Schedules/Senate/2026%20104th%20GA%20Veto%20Calendar.pdf</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Announced 21 Aug 2026; pending confirmation by the Illinois Senate, which had no session day between the announcement and 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Tom Kotarac</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Director (also CTA board)</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Cook County Board President (Toni Preckwinkle)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Senior Vice President of the Civic Committee of the Commercial Club of Chicago, leading its transportation work, and a sitting RTA board member. Previously Deputy Executive Director of the Chicago Metropolitan Agency for Planning. Spent more than 12 years in the Illinois congressional delegation, as senior policy advisor and projects director for Senator Dick Durbin and senior legislative assistant to Representative Luis Gutierrez. Day describes him as a driving force behind the NITA reforms.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>University of Illinois; his employer's biography names no degree or field.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Transportation policy and regional planning rather than transit operations or capital delivery. Day classified him the same way in his own data.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.masstransitmag.com/management/news/55389315/il-cook-county-board-president-toni-preckwinkle-proposes-new-transit-board-members; https://www.masstransitmag.com/management/news/55391612/il-toni-preckwinkle-backs-red-line-extension-connections-wins-approval-for-transit-picks; https://www.hfchronicle.com/2026/07/19/preckwinkle-appoints-leaders-to-nita-and-transit-service-boards/; https://civiccommittee.org/tom-kotarac/; https://www.lwvcookcounty.org/cook-county-board-observer-reports/new-cfo-and-transit-agencies-appointments-approved</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Cook County Board, 16 July 2026; seat effective 1 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Diane Williams</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Cook County Board President (Toni Preckwinkle)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>President and CEO of the Safer Foundation from 1996 for 18 years, and President Emeritus since 2014; the foundation is one of the largest US nonprofit providers of employment placement and job-readiness training for people with criminal records. Serves on the boards of the Southland Development Authority and the Chicago Metropolitan Agency for Planning. Has consulted for the US Departments of Labor, Justice, Health and Human Services, and Housing and Urban Development. Separately, she was an elected Trustee of the Village of Flossmoor for 16 years, through spring 2021.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>MBA, Kellogg School of Management, Northwestern University; undergraduate degree in education, Chicago State University.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Two readings compete. Sixteen years as an elected trustee could support Elected Official, and running a community-serving nonprofit could support Community Advocate. Counted on her executive record. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>An executive career running a large nonprofit. The Elected Official category covers current or recently-retired officeholders without other qualifying experience; her village trusteeship ended five years ago and sat alongside that executive career.</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.masstransitmag.com/management/news/55389315/il-cook-county-board-president-toni-preckwinkle-proposes-new-transit-board-members; https://www.masstransitmag.com/management/news/55391612/il-toni-preckwinkle-backs-red-line-extension-connections-wins-approval-for-transit-picks; https://www.hfchronicle.com/2026/07/19/preckwinkle-appoints-leaders-to-nita-and-transit-service-boards/; https://counciloncj.org/team/diane-williams/; https://southlanddevelopment.org/our-people; https://www.lwvcookcounty.org/cook-county-board-observer-reports/new-cfo-and-transit-agencies-appointments-approved; https://static1.squarespace.com/static/5c991a3f3dab3e000178c991/t/5e1ce3a7618a501203ddf26a/1578951592459/SDA+Board+Key+Staff+Bios.pdf; https://www.hfchronicle.com/2021/03/01/trustee-diane-williams-reflects-years-flossmoor-service-collaboration/</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Cook County Board, 16 July 2026; seat effective 1 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Romayne Brown</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Cook County Board President (Toni Preckwinkle)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>A professional transit manager with more than 31 years at the CTA. She started as a rail conductor in 1978 and finished her CTA career in 2010 as Vice President of Rail Operations, a post in which she oversaw a $1.3bn budget and rail service to 550,000 customers a day, having held roles including Director of Rail Operations, General Manager of Rail Operations and Administrative Manager of the Red Line. Appointed to the Metra board in 2013, its Vice Chair 2016-2020 and its Chair 2020-2024.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Chicago Transit Authority Transit Management Program at Harold Washington College (1999); classes at South Suburban College. No academic degree is listed in her official biography.</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Three decades of direct rail operations management at a major transit agency, rising from rail conductor to Vice President of Rail Operations with a $1.3bn budget. The clearest transit-operations credential on the board, and the only one that is unambiguous under either reading of Day's categories. Day classified her the same way in his own data.</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.masstransitmag.com/management/news/55389315/il-cook-county-board-president-toni-preckwinkle-proposes-new-transit-board-members; https://www.masstransitmag.com/management/news/55391612/il-toni-preckwinkle-backs-red-line-extension-connections-wins-approval-for-transit-picks; https://www.hfchronicle.com/2026/07/19/preckwinkle-appoints-leaders-to-nita-and-transit-service-boards/; https://metra.com/leadership/romayne-c-brown; https://www.cookcountyil.gov/news/president-preckwinkle-nominates-romayne-brown-metra-board-directors; https://www.lwvcookcounty.org/cook-county-board-observer-reports/new-cfo-and-transit-agencies-appointments-approved</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Cook County Board, 16 July 2026; seat effective 1 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Luis Montgomery</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Cook County Board President (Toni Preckwinkle)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>A civil engineer who leads national transportation market development for an infrastructure consultancy, and described by the county board observer record as a long-time user of public transport. The consultancy is not named in any source that also names him as the appointee, and his employer, education and residence could not be established.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Transit Ops/Management</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Decided the other way from the strict reading. The rules exclude general civil engineers unless they have worked in transit, and nothing establishes employment at a transit operator — his work is transportation infrastructure consulting rather than running transit. His employer could not be established from any source that also names him as the appointee, so it is recorded as unknown rather than guessed. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>A civil engineer whose practice is transportation infrastructure, leading national transportation market development for an infrastructure consultancy. Counted as transit expertise on the engineering background and the transport-sector career.</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.masstransitmag.com/management/news/55389315/il-cook-county-board-president-toni-preckwinkle-proposes-new-transit-board-members; https://www.masstransitmag.com/management/news/55391612/il-toni-preckwinkle-backs-red-line-extension-connections-wins-approval-for-transit-picks; https://www.hfchronicle.com/2026/07/19/preckwinkle-appoints-leaders-to-nita-and-transit-service-boards/; https://www.lwvcookcounty.org/cook-county-board-observer-reports/new-cfo-and-transit-agencies-appointments-approved; https://www.2imgroup.com/meet-the-team</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Cook County Board, 16 July 2026; seat effective 1 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Rory Hoskins</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Cook County Board President (Toni Preckwinkle)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of the Village of Forest Park, first elected in 2019 and the village's first Black mayor. An attorney; sources describe him variously as supporting state insurance regulation and as having a background in social services and mental health, and no current legal employer is named. Day notes he took an active part in the NITA negotiations. The Pace seat he fills is reserved for sitting or former mayors.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>A sitting mayor. Under the rule settled on 2026-08-27, holding the seat by virtue of an appointment does not exempt a serving politician.</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.masstransitmag.com/management/news/55389315/il-cook-county-board-president-toni-preckwinkle-proposes-new-transit-board-members; https://www.masstransitmag.com/management/news/55391612/il-toni-preckwinkle-backs-red-line-extension-connections-wins-approval-for-transit-picks; https://www.hfchronicle.com/2026/07/19/preckwinkle-appoints-leaders-to-nita-and-transit-service-boards/; https://www.forestparkreview.com/2026/07/28/hoskins-appointed-to-nita-board/; https://www.lwvcookcounty.org/cook-county-board-observer-reports/new-cfo-and-transit-agencies-appointments-approved</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Cook County Board, 16 July 2026; seat effective 1 Sept 2026. NITA term is five years from 1 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Oswaldo Alvarez</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Director (also CTA board)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of Chicago (Brandon Johnson)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director of the Illinois Legislative Latino Caucus Foundation, leading statewide policy strategy and coalition-building. Served as Illinois' Statewide Census Director for the 2020 Census, managing a $47m operation and coordinating more than 400 community organisations. Around 20 years across the nonprofit, government and philanthropic sectors. Approved by the Chicago City Council as an RTA director on 16 October 2025 and serving there since.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>MA in social policy, University of Chicago; BA in economics and political science, University of Wisconsin-Madison.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>He heads an organisation representing a demographic group, which is inside the Community Advocate definition, and his census work was coalition-building with community organisations. Counted on his policy and administrative record. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Policy strategy and large-programme administration, most clearly the statewide census operation. Government-affairs work rather than rider or community advocacy.</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chicago.gov/city/en/depts/mayor/press_room/press_releases/2026/july/nita-board-appointments.html; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2026/July/CITY%20COUNCIL%20CONFIRMS%20MAYOR%20BRANDON%20JOHNSON%E2%80%99S%20APPOINTMENTS%20TO%20THE%20NORTHERN%20ILLINOIS%20TRANSIT%20AUTHORITY%20AND%20TRANSIT%20AGENCY%20BOARDS%20OF%20DIRECTORS.pdf; https://www.rtachicago.org/about-rta/boards-and-committees/board-of-directors; https://chi.streetsblog.org/2026/07/15/johnsons-transit-board-picks-advance-after-advocates-pack-city-hall-hearing; https://chicago.councilmatic.org/legislation/a2025-0019893/</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Chicago City Council, 15 July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Natasha Jenkins</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of Chicago (Brandon Johnson)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>A labour and employment attorney with more than a decade representing clients in transportation, aviation and government. Senior Attorney at Clark Hill; previously General Counsel of Teamsters Local 700, Senior Attorney for the CTA, labour and employment counsel for Illinois Central Management Services, and an Assistant Attorney General of Illinois. Also served at Littler Mendelson and United Airlines. The 108th President of the Cook County Bar Association. A sitting RTA director since October 2024.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>JD, UIC Law School (2012); BA, Hamilton College (2007).</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Day classifies her as Transit Ops/Management in his own data, on the strength of her CTA employment. Under this site's stated rules a senior attorney at a transit agency is management, not operations. Counted as management, with Day's own call recorded. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>A practising attorney. Her CTA role was in-house legal work, not operations or capital delivery, and her union role was as outside counsel rather than a designated labour seat.</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chicago.gov/city/en/depts/mayor/press_room/press_releases/2026/july/nita-board-appointments.html; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2026/July/CITY%20COUNCIL%20CONFIRMS%20MAYOR%20BRANDON%20JOHNSON%E2%80%99S%20APPOINTMENTS%20TO%20THE%20NORTHERN%20ILLINOIS%20TRANSIT%20AUTHORITY%20AND%20TRANSIT%20AGENCY%20BOARDS%20OF%20DIRECTORS.pdf; https://www.rtachicago.org/about-rta/boards-and-committees/board-of-directors; https://chi.streetsblog.org/2026/07/15/johnsons-transit-board-picks-advance-after-advocates-pack-city-hall-hearing</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Chicago City Council, 15 July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Dennis Mondero</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of Chicago (Brandon Johnson)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>General Counsel for AKIRA, a Chicago retailer. At the CTA he served as Senior Vice President and Chief Administrative Officer, and as Deputy Chief of Staff; the dates of that tenure could not be established. Previously Executive Director of the Chinese Mutual Aid Association, which he grew from a $4m to a $15m budget, and Deputy Buildings Commissioner for the City of Chicago. Past President of the Asian American Bar Association of Greater Chicago. A sitting RTA director since October 2024.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>LLM in real estate, University of Illinois Chicago; JD, Indiana University Bloomington; BA in English, University of Illinois Urbana-Champaign.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Day classifies him as Transit Ops/Management in his own data. This is the same tension as the Voltarelli call on the Sao Paulo board: a senior back-office role at a transit operator. Counted as management here, with Day's own call recorded. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>His CTA roles were administrative and executive-staff posts rather than operations or capital delivery, which places him in management under the stated rules.</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chicago.gov/city/en/depts/mayor/press_room/press_releases/2026/july/nita-board-appointments.html; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2026/July/CITY%20COUNCIL%20CONFIRMS%20MAYOR%20BRANDON%20JOHNSON%E2%80%99S%20APPOINTMENTS%20TO%20THE%20NORTHERN%20ILLINOIS%20TRANSIT%20AUTHORITY%20AND%20TRANSIT%20AGENCY%20BOARDS%20OF%20DIRECTORS.pdf; https://www.rtachicago.org/about-rta/boards-and-committees/board-of-directors; https://chi.streetsblog.org/2026/07/15/johnsons-transit-board-picks-advance-after-advocates-pack-city-hall-hearing</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Chicago City Council, 15 July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Dee Atkins</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of Chicago (Brandon Johnson)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Chief of Community Engagement and Equity at Thresholds, one of Illinois' largest community-based mental health and substance use treatment providers. More than 20 years in strategic partnerships and community engagement, with senior roles at Marillac St. Vincent Family Services and Mercy Home for Boys &amp; Girls. Participates in Chicago's Community Violence Intervention Collaborative and sits on the Community Advisory Council of West Side United.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>MS in journalism and integrated marketing, Roosevelt University; BA in communications, East-West University Chicago.</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Community Advocate</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Community Advocate rather than Other Management/Policy. She is a senior nonprofit executive, and the two comparable calls on this board — Nedra Sims Fears and Oswaldo Alvarez — were decided the other way. She is counted as an advocate because, unlike them, there is no separate profession beneath the community work: her whole career is community engagement and social services. She is the board's only community advocate under the headline reading, so this single call carries a headline figure. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Her entire career is community engagement and social services, with no other profession underneath it. The only member of this board classified as a community advocate.</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chicago.gov/city/en/depts/mayor/press_room/press_releases/2026/july/nita-board-appointments.html; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2026/July/CITY%20COUNCIL%20CONFIRMS%20MAYOR%20BRANDON%20JOHNSON%E2%80%99S%20APPOINTMENTS%20TO%20THE%20NORTHERN%20ILLINOIS%20TRANSIT%20AUTHORITY%20AND%20TRANSIT%20AGENCY%20BOARDS%20OF%20DIRECTORS.pdf; https://chi.streetsblog.org/2026/07/15/johnsons-transit-board-picks-advance-after-advocates-pack-city-hall-hearing; https://www.thresholds.org/on-martin-luther-king-jr-day</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Chicago City Council, 15 July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lester Barclay</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Director (also CTA board)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of Chicago (Brandon Johnson)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>A family law attorney and senior partner at The Barclay Law Group, with over three decades of practice. Chairman of the Chicago Transit Board since 2021; before that he chaired the CTA Citizens Advisory Board, an advisory body distinct from the governing board. Named a Henry Luce Scholar in 1986. Day notes he is one of six Johnson appointees who previously served on a transit board, and that he opposed key parts of the NITA reforms before telling the City Council he supports the NITA Act.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>JD, Case Western Reserve University; BA, Oberlin College.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Day classifies him as Community Advocate in his own data. Under this site's stated rules his primary background is the law. Counted as management, with Day's own call recorded. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Classified on primary background, which is three decades of legal practice as a law firm principal.</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.chicago.gov/city/en/depts/mayor/press_room/press_releases/2026/july/nita-board-appointments.html; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2026/July/CITY%20COUNCIL%20CONFIRMS%20MAYOR%20BRANDON%20JOHNSON%E2%80%99S%20APPOINTMENTS%20TO%20THE%20NORTHERN%20ILLINOIS%20TRANSIT%20AUTHORITY%20AND%20TRANSIT%20AGENCY%20BOARDS%20OF%20DIRECTORS.pdf; https://chi.streetsblog.org/2026/07/15/johnsons-transit-board-picks-advance-after-advocates-pack-city-hall-hearing; https://chi.streetsblog.org/2026/08/24/after-pritzker-named-his-nita-board-picks-the-agencys-leadership-is-largely-decided-will-they-use-their-power-for-good; https://www.chicago.gov/content/dam/city/depts/mayor/Press%20Room/Press%20Releases/2021/April/LesterBarclayCTABoardChair.pdf</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Chicago City Council, 15 July 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>John Noak</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Will County Executive (Jennifer Bertino-Tarrant)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of the Village of Romeoville since 2008. A Pace director representing Will County since 2022. Sits on the CMAP Executive Board, was 2025-26 Chair of the Metropolitan Mayors Caucus, is President of the Will County Governmental League, and serves on the US Conference of Mayors' Transportation Committee. No private-sector career was found. Day notes he publicly opposed the NITA reforms.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>A sitting mayor of 18 years. Day classified him the same way in his own data.</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pacebus.com/person/john-d-noak; https://www.shawlocal.com/the-herald-news/2026/07/17/romeoville-mayor-named-to-new-regional-transit-board/; https://patch.com/illinois/romeoville/amp/34466582/mayor-noak-appointed-to-new-northern-illinois-transit-authority-nita-board; https://www.dupagecounty.gov/government/county_board/nita.php</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Appointed by the Will County Executive; no county board confirmation vote was found as of 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Gary Gordon</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Lake County Board Chair (Sandy Hart)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Chief Financial and Administrative Officer of the Shedd Aquarium, and Lake County's representative on the Metra board since March 2025. Before joining the Shedd in 2018 he spent 15 years as director of finance and administrative services for Lake County, overseeing a budget of roughly $500m. Previously director of the Office of Management and Budget for the Chicago Park District, and assistant budget director and director of capital programs for the City of Chicago. No elected office.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Other Management/Policy</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>A career public-finance executive. His capital programs role was city-wide rather than transit. Day classified him the same way in his own data.</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>https://content.govdelivery.com/accounts/ILLAKE/bulletins/40d6ba7; https://www.lakecountyil.gov/m/newsflash/Home/Detail/4796; https://www.shawlocal.com/lake-county-journal/2026/06/25/gordon-appointed-to-nita-board-of-directors/; https://chicagocfo.org/gary-gordon/; https://www.shawlocal.com/lake-county-journal/2025/03/20/lake-county-appoints-gary-gordon-to-metra-board-of-directors/; https://www.masstransitmag.com/management/news/55398318/il-whos-on-first-at-metra-directors-coming-and-going-as-transit-reforms-gel</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Appointed by the Lake County Board Chair, announced 10 June 2026; no county board confirmation vote was found as of 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Brian Sager</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Metra board)</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>McHenry County</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>A sitting McHenry County Board member for District 7, elected in November 2022 with a term ending December 2026; he lost the March 2026 primary and will not return. Mayor of the City of Woodstock from 2005 to 2021, and a Woodstock councilman before that. McHenry County's RTA board representative since May 2018. Earlier a professor at McHenry County College for 18 years, later its Vice President of Academic and Student Affairs and Acting President, and Provost of Rock Valley College until 2015.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Holds a doctorate; Day's data records a PhD in international development.</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>A sitting county board member and a former mayor of 16 years. Day classified him the same way in his own data, though as a former mayor rather than a current officeholder.</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>https://rtachicago.org/index.php/about-us/leadership/board-directors/brian-sager-director; https://www.shawlocal.com/northwest-herald/2026/02/10/2026-election-questionnaire-brian-sager-mchenry-county-board-district-7/; https://www.mchenrycountyil.gov/departments/county-board/meet-your-county-board-members; https://pub-countyofmchenry.escribemeetings.com/filestream.ashx?DocumentId=162162; https://www.mchenrycountyblog.com/2026/04/05/with-100-of-precincts-in-mchenry-county-board-district-7-8-challengers-jeff-schwartz-and-marty-mohr-defeat-brian-sager-larry-smith/; https://www.masstransitmag.com/management/news/55398318/il-whos-on-first-at-metra-directors-coming-and-going-as-transit-reforms-gel</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>The appointing official could not be established, and no McHenry County Board confirmation vote was found as of 27 Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Brian Dahl</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Kane County Board</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>President of the Fox Valley Building and Construction Trades Council, previously its Vice President, and formerly membership director and fiduciary trustee for Painters District Council 30. A former Kane County Board member for District 6: appointed in 2015, elected in 2016, and resigned in April 2018 after moving out of the district.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Labor Representative</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>This site's stated rule requires an explicitly designated union seat, and NITA has none, which would place him in Other Management/Policy. Day's applied practice classifies union officials on their background instead, and that reading was adopted here for both readings. Adjudicated by Steffany Bahamon.</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>A building-trades council president, classified on his union leadership. This follows Day, who places union officials on the RTA board in this category even though that board has no designated labour seat.</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kanecountyil.gov/Documents/Press%20Releases/Kane%20County%20Names%20Brian%20Dahl%20to%20Northern%20Illinois%20Transit%20Authority%20and%20Pace%20Suburban%20Bus%20Board,%20Reappoints%20Joe%20McMahon%20to%20Metra%20Board.pdf; https://kanecountyconnects.com/article/KaneCounty-NITA-METRA-2026; https://www.shawlocal.com/2016/11/05/dahl-of-north-aurora-wins-kane-county-board-district-6-seat/al0efo3/</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by the Kane County Board; seat effective September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Northern Illinois Transit Authority (NITA)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>David Pileski</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Director (also Pace board)</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>DuPage County Board Chair (Deborah Conroy)</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Mayor of the Village of Roselle, elected in 2021 and re-elected in 2025, having previously served as a village trustee from 2017 and on the zoning board of appeals. A supply chain senior manager at W.W. Grainger, responsible for purchasing operations and automation technology solutions. Was 2025-26 President of the DuPage Mayors and Managers Conference. Day notes he publicly opposed the NITA reforms.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Elected Official</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>A sitting mayor. His private-sector role in supply chain management is not transit experience.</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dupagecounty.gov/government/county_board/nita.php; https://www.roselle.il.us/54/Mayor; https://rosellestrong.com/about; https://igpa.uillinois.edu/in-the-news/edgar-fellows-program-welcomes-13th-class; https://dmmc-cog.org/2025/06/02/roselle-mayor-david-pileski-elected-2025-2026-president-of-the-dupage-mayors-and-managers-conference/</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Approved by the DuPage County Board in mid-July 2026, on the County Board Chair's selection.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3648,19 +5383,19 @@
       <c r="D2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3693,19 +5428,19 @@
       <c r="D3" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="11" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="10" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="12" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="13" t="n">
         <v>0.1818181818181818</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3738,19 +5473,19 @@
       <c r="D4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="13" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3783,19 +5518,19 @@
       <c r="D5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3828,19 +5563,19 @@
       <c r="D6" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
